--- a/HealthLog-Appium/report.xlsx
+++ b/HealthLog-Appium/report.xlsx
@@ -37,7 +37,7 @@
     <t>Execution Date</t>
   </si>
   <si>
-    <t>2026-08-06T17:39:06.554Z</t>
+    <t>2026-08-06T17:45:05.572Z</t>
   </si>
   <si>
     <t>Total Test Cases</t>
@@ -61,13 +61,13 @@
     <t>Total Execution Time (Sec)</t>
   </si>
   <si>
-    <t>10.83 s</t>
+    <t>12.49 s</t>
   </si>
   <si>
     <t>Average Test Duration (Ms)</t>
   </si>
   <si>
-    <t>314.58 ms</t>
+    <t>309.16 ms</t>
   </si>
   <si>
     <t>Category Name</t>
@@ -94,61 +94,61 @@
     <t>100.00%</t>
   </si>
   <si>
-    <t>271.60 ms</t>
+    <t>315.10 ms</t>
   </si>
   <si>
     <t>UI Testing</t>
   </si>
   <si>
-    <t>279.60 ms</t>
+    <t>264.32 ms</t>
   </si>
   <si>
     <t>Navigation Testing</t>
   </si>
   <si>
-    <t>315.52 ms</t>
+    <t>283.14 ms</t>
   </si>
   <si>
     <t>Authentication Testing</t>
   </si>
   <si>
-    <t>353.58 ms</t>
+    <t>325.84 ms</t>
   </si>
   <si>
     <t>Medical Records Testing</t>
   </si>
   <si>
-    <t>319.02 ms</t>
+    <t>329.40 ms</t>
   </si>
   <si>
     <t>Reminder Testing</t>
   </si>
   <si>
-    <t>299.62 ms</t>
+    <t>275.40 ms</t>
   </si>
   <si>
     <t>AI Hub Testing</t>
   </si>
   <si>
-    <t>353.42 ms</t>
+    <t>364.02 ms</t>
   </si>
   <si>
     <t>OCR Testing</t>
   </si>
   <si>
-    <t>398.34 ms</t>
+    <t>388.48 ms</t>
   </si>
   <si>
     <t>Performance Testing</t>
   </si>
   <si>
-    <t>220.56 ms</t>
+    <t>207.62 ms</t>
   </si>
   <si>
     <t>Regression Testing</t>
   </si>
   <si>
-    <t>334.52 ms</t>
+    <t>338.24 ms</t>
   </si>
   <si>
     <t>Test ID</t>
@@ -184,7 +184,7 @@
     <t>PASS</t>
   </si>
   <si>
-    <t>2026-08-06T17:38:55.745Z</t>
+    <t>2026-08-06T17:44:53.120Z</t>
   </si>
   <si>
     <t>TC-FUNC-002</t>
@@ -196,7 +196,7 @@
     <t>Validate functionality for validate health metric input bounds across edge inputs and local persistence.</t>
   </si>
   <si>
-    <t>2026-08-06T17:38:55.756Z</t>
+    <t>2026-08-06T17:44:53.149Z</t>
   </si>
   <si>
     <t>TC-FUNC-003</t>
@@ -208,7 +208,7 @@
     <t>Validate functionality for check water intake tracker increment across edge inputs and local persistence.</t>
   </si>
   <si>
-    <t>2026-08-06T17:38:55.776Z</t>
+    <t>2026-08-06T17:44:53.162Z</t>
   </si>
   <si>
     <t>TC-FUNC-004</t>
@@ -220,7 +220,7 @@
     <t>Validate functionality for verify sleep log creation across edge inputs and local persistence.</t>
   </si>
   <si>
-    <t>2026-08-06T17:38:55.811Z</t>
+    <t>2026-08-06T17:44:53.178Z</t>
   </si>
   <si>
     <t>TC-FUNC-005</t>
@@ -232,7 +232,7 @@
     <t>Validate functionality for validate weight history deletion across edge inputs and local persistence.</t>
   </si>
   <si>
-    <t>2026-08-06T17:38:55.844Z</t>
+    <t>2026-08-06T17:44:53.191Z</t>
   </si>
   <si>
     <t>TC-FUNC-006</t>
@@ -244,7 +244,7 @@
     <t>Validate functionality for check calorie goal calculation across edge inputs and local persistence.</t>
   </si>
   <si>
-    <t>2026-08-06T17:38:55.862Z</t>
+    <t>2026-08-06T17:44:53.206Z</t>
   </si>
   <si>
     <t>TC-FUNC-007</t>
@@ -256,7 +256,7 @@
     <t>Validate functionality for verify blood pressure format validation across edge inputs and local persistence.</t>
   </si>
   <si>
-    <t>2026-08-06T17:38:55.895Z</t>
+    <t>2026-08-06T17:44:53.217Z</t>
   </si>
   <si>
     <t>TC-FUNC-008</t>
@@ -268,7 +268,7 @@
     <t>Validate functionality for check glucose log entry across edge inputs and local persistence.</t>
   </si>
   <si>
-    <t>2026-08-06T17:38:55.913Z</t>
+    <t>2026-08-06T17:44:53.247Z</t>
   </si>
   <si>
     <t>TC-FUNC-009</t>
@@ -280,7 +280,7 @@
     <t>Validate functionality for validate heart rate reading export across edge inputs and local persistence.</t>
   </si>
   <si>
-    <t>2026-08-06T17:38:55.945Z</t>
+    <t>2026-08-06T17:44:53.281Z</t>
   </si>
   <si>
     <t>TC-FUNC-010</t>
@@ -292,7 +292,7 @@
     <t>Validate functionality for verify step counter persistence across edge inputs and local persistence.</t>
   </si>
   <si>
-    <t>2026-08-06T17:38:55.961Z</t>
+    <t>2026-08-06T17:44:53.313Z</t>
   </si>
   <si>
     <t>TC-FUNC-011</t>
@@ -304,7 +304,7 @@
     <t>Validate functionality for check bmi calculator precision across edge inputs and local persistence.</t>
   </si>
   <si>
-    <t>2026-08-06T17:38:55.978Z</t>
+    <t>2026-08-06T17:44:53.329Z</t>
   </si>
   <si>
     <t>TC-FUNC-012</t>
@@ -316,7 +316,7 @@
     <t>Validate functionality for validate emergency contact save across edge inputs and local persistence.</t>
   </si>
   <si>
-    <t>2026-08-06T17:38:55.995Z</t>
+    <t>2026-08-06T17:44:53.350Z</t>
   </si>
   <si>
     <t>TC-FUNC-013</t>
@@ -328,7 +328,7 @@
     <t>Validate functionality for verify medical history search across edge inputs and local persistence.</t>
   </si>
   <si>
-    <t>2026-08-06T17:38:56.012Z</t>
+    <t>2026-08-06T17:44:53.379Z</t>
   </si>
   <si>
     <t>TC-FUNC-014</t>
@@ -340,7 +340,7 @@
     <t>Validate functionality for check allergy tag addition across edge inputs and local persistence.</t>
   </si>
   <si>
-    <t>2026-08-06T17:38:56.030Z</t>
+    <t>2026-08-06T17:44:53.397Z</t>
   </si>
   <si>
     <t>TC-FUNC-015</t>
@@ -352,7 +352,7 @@
     <t>Validate functionality for validate doctor note attachment across edge inputs and local persistence.</t>
   </si>
   <si>
-    <t>2026-08-06T17:38:56.060Z</t>
+    <t>2026-08-06T17:44:53.412Z</t>
   </si>
   <si>
     <t>TC-FUNC-016</t>
@@ -364,7 +364,7 @@
     <t>Validate functionality for verify prescription renewal request across edge inputs and local persistence.</t>
   </si>
   <si>
-    <t>2026-08-06T17:38:56.078Z</t>
+    <t>2026-08-06T17:44:53.428Z</t>
   </si>
   <si>
     <t>TC-FUNC-017</t>
@@ -376,7 +376,7 @@
     <t>Validate functionality for check symptom entry creation across edge inputs and local persistence.</t>
   </si>
   <si>
-    <t>2026-08-06T17:38:56.094Z</t>
+    <t>2026-08-06T17:44:53.445Z</t>
   </si>
   <si>
     <t>TC-FUNC-018</t>
@@ -388,7 +388,7 @@
     <t>Validate functionality for validate lab result pdf export across edge inputs and local persistence.</t>
   </si>
   <si>
-    <t>2026-08-06T17:38:56.112Z</t>
+    <t>2026-08-06T17:44:53.462Z</t>
   </si>
   <si>
     <t>TC-FUNC-019</t>
@@ -400,7 +400,7 @@
     <t>Validate functionality for verify profile picture compression across edge inputs and local persistence.</t>
   </si>
   <si>
-    <t>2026-08-06T17:38:56.144Z</t>
+    <t>2026-08-06T17:44:53.480Z</t>
   </si>
   <si>
     <t>TC-FUNC-020</t>
@@ -412,7 +412,7 @@
     <t>Validate functionality for check unit converter (kg to lbs) across edge inputs and local persistence.</t>
   </si>
   <si>
-    <t>2026-08-06T17:38:56.162Z</t>
+    <t>2026-08-06T17:44:53.513Z</t>
   </si>
   <si>
     <t>TC-FUNC-021</t>
@@ -424,7 +424,7 @@
     <t>Validate functionality for validate date picker range filter across edge inputs and local persistence.</t>
   </si>
   <si>
-    <t>2026-08-06T17:38:56.178Z</t>
+    <t>2026-08-06T17:44:53.530Z</t>
   </si>
   <si>
     <t>TC-FUNC-022</t>
@@ -436,7 +436,7 @@
     <t>Validate functionality for verify custom metric creation across edge inputs and local persistence.</t>
   </si>
   <si>
-    <t>2026-08-06T17:38:56.212Z</t>
+    <t>2026-08-06T17:44:53.547Z</t>
   </si>
   <si>
     <t>TC-FUNC-023</t>
@@ -448,7 +448,7 @@
     <t>Validate functionality for check activity log multi-selection across edge inputs and local persistence.</t>
   </si>
   <si>
-    <t>2026-08-06T17:38:56.230Z</t>
+    <t>2026-08-06T17:44:53.563Z</t>
   </si>
   <si>
     <t>TC-FUNC-024</t>
@@ -460,7 +460,7 @@
     <t>Validate functionality for validate target heart rate warning across edge inputs and local persistence.</t>
   </si>
   <si>
-    <t>2026-08-06T17:38:56.262Z</t>
+    <t>2026-08-06T17:44:53.596Z</t>
   </si>
   <si>
     <t>TC-FUNC-025</t>
@@ -472,7 +472,7 @@
     <t>Validate functionality for verify data backup generation across edge inputs and local persistence.</t>
   </si>
   <si>
-    <t>2026-08-06T17:38:56.296Z</t>
+    <t>2026-08-06T17:44:53.623Z</t>
   </si>
   <si>
     <t>TC-FUNC-026</t>
@@ -484,7 +484,7 @@
     <t>Validate functionality for check cloud sync protocol across edge inputs and local persistence.</t>
   </si>
   <si>
-    <t>2026-08-06T17:38:56.313Z</t>
+    <t>2026-08-06T17:44:53.651Z</t>
   </si>
   <si>
     <t>TC-FUNC-027</t>
@@ -496,7 +496,7 @@
     <t>Validate functionality for validate offline cache storage across edge inputs and local persistence.</t>
   </si>
   <si>
-    <t>2026-08-06T17:38:56.329Z</t>
+    <t>2026-08-06T17:44:53.681Z</t>
   </si>
   <si>
     <t>TC-FUNC-028</t>
@@ -508,7 +508,7 @@
     <t>Validate functionality for verify local database migration across edge inputs and local persistence.</t>
   </si>
   <si>
-    <t>2026-08-06T17:38:56.345Z</t>
+    <t>2026-08-06T17:44:53.749Z</t>
   </si>
   <si>
     <t>TC-FUNC-029</t>
@@ -520,7 +520,7 @@
     <t>Validate functionality for check csv export formatter across edge inputs and local persistence.</t>
   </si>
   <si>
-    <t>2026-08-06T17:38:56.378Z</t>
+    <t>2026-08-06T17:44:53.782Z</t>
   </si>
   <si>
     <t>TC-FUNC-030</t>
@@ -532,7 +532,7 @@
     <t>Validate functionality for validate json export structure across edge inputs and local persistence.</t>
   </si>
   <si>
-    <t>2026-08-06T17:38:56.410Z</t>
+    <t>2026-08-06T17:44:53.797Z</t>
   </si>
   <si>
     <t>TC-FUNC-031</t>
@@ -544,7 +544,7 @@
     <t>Validate functionality for verify app language switching across edge inputs and local persistence.</t>
   </si>
   <si>
-    <t>2026-08-06T17:38:56.444Z</t>
+    <t>2026-08-06T17:44:53.814Z</t>
   </si>
   <si>
     <t>TC-FUNC-032</t>
@@ -556,7 +556,7 @@
     <t>Validate functionality for check dark theme state persistence across edge inputs and local persistence.</t>
   </si>
   <si>
-    <t>2026-08-06T17:38:56.461Z</t>
+    <t>2026-08-06T17:44:53.830Z</t>
   </si>
   <si>
     <t>TC-FUNC-033</t>
@@ -568,7 +568,7 @@
     <t>Validate functionality for validate metric graph filtering across edge inputs and local persistence.</t>
   </si>
   <si>
-    <t>2026-08-06T17:38:56.477Z</t>
+    <t>2026-08-06T17:44:53.844Z</t>
   </si>
   <si>
     <t>TC-FUNC-034</t>
@@ -580,7 +580,7 @@
     <t>Validate functionality for verify daily goal achievement popup across edge inputs and local persistence.</t>
   </si>
   <si>
-    <t>2026-08-06T17:38:56.512Z</t>
+    <t>2026-08-06T17:44:53.880Z</t>
   </si>
   <si>
     <t>TC-FUNC-035</t>
@@ -592,7 +592,7 @@
     <t>Validate functionality for check notification sound preference across edge inputs and local persistence.</t>
   </si>
   <si>
-    <t>2026-08-06T17:38:56.545Z</t>
+    <t>2026-08-06T17:44:53.895Z</t>
   </si>
   <si>
     <t>TC-FUNC-036</t>
@@ -604,7 +604,7 @@
     <t>Validate functionality for validate biometric sync switch across edge inputs and local persistence.</t>
   </si>
   <si>
-    <t>2026-08-06T17:38:56.561Z</t>
+    <t>2026-08-06T17:44:53.931Z</t>
   </si>
   <si>
     <t>TC-FUNC-037</t>
@@ -616,7 +616,7 @@
     <t>Validate functionality for verify family member profile linking across edge inputs and local persistence.</t>
   </si>
   <si>
-    <t>2026-08-06T17:38:56.578Z</t>
+    <t>2026-08-06T17:44:53.945Z</t>
   </si>
   <si>
     <t>TC-FUNC-038</t>
@@ -628,7 +628,7 @@
     <t>Validate functionality for check insurance card scanner output across edge inputs and local persistence.</t>
   </si>
   <si>
-    <t>2026-08-06T17:38:56.593Z</t>
+    <t>2026-08-06T17:44:53.962Z</t>
   </si>
   <si>
     <t>TC-FUNC-039</t>
@@ -640,7 +640,7 @@
     <t>Validate functionality for validate pharmacy finder search across edge inputs and local persistence.</t>
   </si>
   <si>
-    <t>2026-08-06T17:38:56.611Z</t>
+    <t>2026-08-06T17:44:53.978Z</t>
   </si>
   <si>
     <t>TC-FUNC-040</t>
@@ -652,7 +652,7 @@
     <t>Validate functionality for verify appointment scheduling validation across edge inputs and local persistence.</t>
   </si>
   <si>
-    <t>2026-08-06T17:38:56.628Z</t>
+    <t>2026-08-06T17:44:53.993Z</t>
   </si>
   <si>
     <t>TC-FUNC-041</t>
@@ -664,7 +664,7 @@
     <t>Validate functionality for check telehealth call log storage across edge inputs and local persistence.</t>
   </si>
   <si>
-    <t>2026-08-06T17:38:56.646Z</t>
+    <t>2026-08-06T17:44:54.013Z</t>
   </si>
   <si>
     <t>TC-FUNC-042</t>
@@ -676,7 +676,7 @@
     <t>Validate functionality for validate doctor feedback form across edge inputs and local persistence.</t>
   </si>
   <si>
-    <t>2026-08-06T17:38:56.677Z</t>
+    <t>2026-08-06T17:44:54.028Z</t>
   </si>
   <si>
     <t>TC-FUNC-043</t>
@@ -688,7 +688,7 @@
     <t>Validate functionality for verify vaccine record upload across edge inputs and local persistence.</t>
   </si>
   <si>
-    <t>2026-08-06T17:38:56.710Z</t>
+    <t>2026-08-06T17:44:54.063Z</t>
   </si>
   <si>
     <t>TC-FUNC-044</t>
@@ -700,7 +700,7 @@
     <t>Validate functionality for check vital sign threshold alert across edge inputs and local persistence.</t>
   </si>
   <si>
-    <t>2026-08-06T17:38:56.744Z</t>
+    <t>2026-08-06T17:44:54.097Z</t>
   </si>
   <si>
     <t>TC-FUNC-045</t>
@@ -712,7 +712,7 @@
     <t>Validate functionality for validate exercise log time calculation across edge inputs and local persistence.</t>
   </si>
   <si>
-    <t>2026-08-06T17:38:56.778Z</t>
+    <t>2026-08-06T17:44:54.131Z</t>
   </si>
   <si>
     <t>TC-FUNC-046</t>
@@ -724,7 +724,7 @@
     <t>Validate functionality for verify mood log selector across edge inputs and local persistence.</t>
   </si>
   <si>
-    <t>2026-08-06T17:38:56.811Z</t>
+    <t>2026-08-06T17:44:54.162Z</t>
   </si>
   <si>
     <t>TC-FUNC-047</t>
@@ -736,7 +736,7 @@
     <t>Validate functionality for check daily streak increment across edge inputs and local persistence.</t>
   </si>
   <si>
-    <t>2026-08-06T17:38:56.828Z</t>
+    <t>2026-08-06T17:44:54.180Z</t>
   </si>
   <si>
     <t>TC-FUNC-048</t>
@@ -748,7 +748,7 @@
     <t>Validate functionality for validate user feedback submission across edge inputs and local persistence.</t>
   </si>
   <si>
-    <t>2026-08-06T17:38:56.843Z</t>
+    <t>2026-08-06T17:44:54.211Z</t>
   </si>
   <si>
     <t>TC-FUNC-049</t>
@@ -760,7 +760,7 @@
     <t>Validate functionality for verify account data deletion request across edge inputs and local persistence.</t>
   </si>
   <si>
-    <t>2026-08-06T17:38:56.861Z</t>
+    <t>2026-08-06T17:44:54.231Z</t>
   </si>
   <si>
     <t>TC-FUNC-050</t>
@@ -772,7 +772,7 @@
     <t>Validate functionality for check privacy policy acceptance log across edge inputs and local persistence.</t>
   </si>
   <si>
-    <t>2026-08-06T17:38:56.878Z</t>
+    <t>2026-08-06T17:44:54.246Z</t>
   </si>
   <si>
     <t>TC-UI-001</t>
@@ -784,7 +784,7 @@
     <t>Inspect UI elements and layout fidelity for verify dashboard layout alignment against design specifications.</t>
   </si>
   <si>
-    <t>2026-08-06T17:38:56.896Z</t>
+    <t>2026-08-06T17:44:54.262Z</t>
   </si>
   <si>
     <t>TC-UI-002</t>
@@ -796,7 +796,7 @@
     <t>Inspect UI elements and layout fidelity for check bottom navigation bar icons against design specifications.</t>
   </si>
   <si>
-    <t>2026-08-06T17:38:56.911Z</t>
+    <t>2026-08-06T17:44:54.296Z</t>
   </si>
   <si>
     <t>TC-UI-003</t>
@@ -808,7 +808,7 @@
     <t>Inspect UI elements and layout fidelity for validate dark mode color palette against design specifications.</t>
   </si>
   <si>
-    <t>2026-08-06T17:38:56.944Z</t>
+    <t>2026-08-06T17:44:54.329Z</t>
   </si>
   <si>
     <t>TC-UI-004</t>
@@ -820,7 +820,7 @@
     <t>Inspect UI elements and layout fidelity for verify typography scaling on accessibility text against design specifications.</t>
   </si>
   <si>
-    <t>2026-08-06T17:38:56.961Z</t>
+    <t>2026-08-06T17:44:54.348Z</t>
   </si>
   <si>
     <t>TC-UI-005</t>
@@ -832,7 +832,7 @@
     <t>Inspect UI elements and layout fidelity for check card shadow rendering against design specifications.</t>
   </si>
   <si>
-    <t>2026-08-06T17:38:56.978Z</t>
+    <t>2026-08-06T17:44:54.379Z</t>
   </si>
   <si>
     <t>TC-UI-006</t>
@@ -844,7 +844,7 @@
     <t>Inspect UI elements and layout fidelity for validate fab button visibility against design specifications.</t>
   </si>
   <si>
-    <t>2026-08-06T17:38:57.010Z</t>
+    <t>2026-08-06T17:44:54.394Z</t>
   </si>
   <si>
     <t>TC-UI-007</t>
@@ -856,7 +856,7 @@
     <t>Inspect UI elements and layout fidelity for verify modal overlay animation against design specifications.</t>
   </si>
   <si>
-    <t>2026-08-06T17:38:57.027Z</t>
+    <t>2026-08-06T17:44:54.415Z</t>
   </si>
   <si>
     <t>TC-UI-008</t>
@@ -868,7 +868,7 @@
     <t>Inspect UI elements and layout fidelity for check toast notification styling against design specifications.</t>
   </si>
   <si>
-    <t>2026-08-06T17:38:57.044Z</t>
+    <t>2026-08-06T17:44:54.426Z</t>
   </si>
   <si>
     <t>TC-UI-009</t>
@@ -880,7 +880,7 @@
     <t>Inspect UI elements and layout fidelity for validate pull-to-refresh indicator against design specifications.</t>
   </si>
   <si>
-    <t>2026-08-06T17:38:57.062Z</t>
+    <t>2026-08-06T17:44:54.456Z</t>
   </si>
   <si>
     <t>TC-UI-010</t>
@@ -892,7 +892,7 @@
     <t>Inspect UI elements and layout fidelity for verify skeleton loader on data fetch against design specifications.</t>
   </si>
   <si>
-    <t>2026-08-06T17:38:57.095Z</t>
+    <t>2026-08-06T17:44:54.486Z</t>
   </si>
   <si>
     <t>TC-UI-011</t>
@@ -904,7 +904,7 @@
     <t>Inspect UI elements and layout fidelity for check tab indicator transition against design specifications.</t>
   </si>
   <si>
-    <t>2026-08-06T17:38:57.128Z</t>
+    <t>2026-08-06T17:44:54.502Z</t>
   </si>
   <si>
     <t>TC-UI-012</t>
@@ -916,7 +916,7 @@
     <t>Inspect UI elements and layout fidelity for validate input field border highlights against design specifications.</t>
   </si>
   <si>
-    <t>2026-08-06T17:38:57.161Z</t>
+    <t>2026-08-06T17:44:54.524Z</t>
   </si>
   <si>
     <t>TC-UI-013</t>
@@ -928,7 +928,7 @@
     <t>Inspect UI elements and layout fidelity for verify error message red color contrast against design specifications.</t>
   </si>
   <si>
-    <t>2026-08-06T17:38:57.177Z</t>
+    <t>2026-08-06T17:44:54.540Z</t>
   </si>
   <si>
     <t>TC-UI-014</t>
@@ -940,7 +940,7 @@
     <t>Inspect UI elements and layout fidelity for check success badge rendering against design specifications.</t>
   </si>
   <si>
-    <t>2026-08-06T17:38:57.193Z</t>
+    <t>2026-08-06T17:44:54.568Z</t>
   </si>
   <si>
     <t>TC-UI-015</t>
@@ -952,7 +952,7 @@
     <t>Inspect UI elements and layout fidelity for validate grid column responsiveness against design specifications.</t>
   </si>
   <si>
-    <t>2026-08-06T17:38:57.227Z</t>
+    <t>2026-08-06T17:44:54.597Z</t>
   </si>
   <si>
     <t>TC-UI-016</t>
@@ -964,7 +964,7 @@
     <t>Inspect UI elements and layout fidelity for verify chart canvas redraw on resize against design specifications.</t>
   </si>
   <si>
-    <t>2026-08-06T17:38:57.261Z</t>
+    <t>2026-08-06T17:44:54.632Z</t>
   </si>
   <si>
     <t>TC-UI-017</t>
@@ -976,7 +976,7 @@
     <t>Inspect UI elements and layout fidelity for check floating header elevation against design specifications.</t>
   </si>
   <si>
-    <t>2026-08-06T17:38:57.295Z</t>
+    <t>2026-08-06T17:44:54.648Z</t>
   </si>
   <si>
     <t>TC-UI-018</t>
@@ -988,7 +988,7 @@
     <t>Inspect UI elements and layout fidelity for validate bottom sheet drag gesture visual against design specifications.</t>
   </si>
   <si>
-    <t>2026-08-06T17:38:57.313Z</t>
+    <t>2026-08-06T17:44:54.665Z</t>
   </si>
   <si>
     <t>TC-UI-019</t>
@@ -1000,7 +1000,7 @@
     <t>Inspect UI elements and layout fidelity for verify avatar circle aspect ratio against design specifications.</t>
   </si>
   <si>
-    <t>2026-08-06T17:38:57.345Z</t>
+    <t>2026-08-06T17:44:54.681Z</t>
   </si>
   <si>
     <t>TC-UI-020</t>
@@ -1012,7 +1012,7 @@
     <t>Inspect UI elements and layout fidelity for check icon tint on active state against design specifications.</t>
   </si>
   <si>
-    <t>2026-08-06T17:38:57.362Z</t>
+    <t>2026-08-06T17:44:54.698Z</t>
   </si>
   <si>
     <t>TC-UI-021</t>
@@ -1024,7 +1024,7 @@
     <t>Inspect UI elements and layout fidelity for validate list divider margin against design specifications.</t>
   </si>
   <si>
-    <t>2026-08-06T17:38:57.378Z</t>
+    <t>2026-08-06T17:44:54.717Z</t>
   </si>
   <si>
     <t>TC-UI-022</t>
@@ -1036,7 +1036,7 @@
     <t>Inspect UI elements and layout fidelity for verify multi-select checkbox animation against design specifications.</t>
   </si>
   <si>
-    <t>2026-08-06T17:38:57.411Z</t>
+    <t>2026-08-06T17:44:54.730Z</t>
   </si>
   <si>
     <t>TC-UI-023</t>
@@ -1048,7 +1048,7 @@
     <t>Inspect UI elements and layout fidelity for check toggle switch smoothness against design specifications.</t>
   </si>
   <si>
-    <t>2026-08-06T17:38:57.445Z</t>
+    <t>2026-08-06T17:44:54.748Z</t>
   </si>
   <si>
     <t>TC-UI-024</t>
@@ -1060,7 +1060,7 @@
     <t>Inspect UI elements and layout fidelity for validate tooltip arrow position against design specifications.</t>
   </si>
   <si>
-    <t>2026-08-06T17:38:57.461Z</t>
+    <t>2026-08-06T17:44:54.764Z</t>
   </si>
   <si>
     <t>TC-UI-025</t>
@@ -1072,7 +1072,7 @@
     <t>Inspect UI elements and layout fidelity for verify status bar translucency against design specifications.</t>
   </si>
   <si>
-    <t>2026-08-06T17:38:57.478Z</t>
+    <t>2026-08-06T17:44:54.782Z</t>
   </si>
   <si>
     <t>TC-UI-026</t>
@@ -1084,7 +1084,7 @@
     <t>Inspect UI elements and layout fidelity for check system navigation bar overlap against design specifications.</t>
   </si>
   <si>
-    <t>2026-08-06T17:38:57.494Z</t>
+    <t>2026-08-06T17:44:54.812Z</t>
   </si>
   <si>
     <t>TC-UI-027</t>
@@ -1096,7 +1096,7 @@
     <t>Inspect UI elements and layout fidelity for validate splash screen logo centering against design specifications.</t>
   </si>
   <si>
-    <t>2026-08-06T17:38:57.511Z</t>
+    <t>2026-08-06T17:44:54.827Z</t>
   </si>
   <si>
     <t>TC-UI-028</t>
@@ -1108,7 +1108,7 @@
     <t>Inspect UI elements and layout fidelity for verify empty state vector graphic against design specifications.</t>
   </si>
   <si>
-    <t>2026-08-06T17:38:57.544Z</t>
+    <t>2026-08-06T17:44:54.857Z</t>
   </si>
   <si>
     <t>TC-UI-029</t>
@@ -1120,7 +1120,7 @@
     <t>Inspect UI elements and layout fidelity for check search bar clear icon alignment against design specifications.</t>
   </si>
   <si>
-    <t>2026-08-06T17:38:57.578Z</t>
+    <t>2026-08-06T17:44:54.878Z</t>
   </si>
   <si>
     <t>TC-UI-030</t>
@@ -1132,7 +1132,7 @@
     <t>Inspect UI elements and layout fidelity for validate pill badge overflow text against design specifications.</t>
   </si>
   <si>
-    <t>2026-08-06T17:38:57.594Z</t>
+    <t>2026-08-06T17:44:54.895Z</t>
   </si>
   <si>
     <t>TC-UI-031</t>
@@ -1144,7 +1144,7 @@
     <t>Inspect UI elements and layout fidelity for verify circular progress bar smoothness against design specifications.</t>
   </si>
   <si>
-    <t>2026-08-06T17:38:57.612Z</t>
+    <t>2026-08-06T17:44:54.912Z</t>
   </si>
   <si>
     <t>TC-UI-032</t>
@@ -1156,7 +1156,7 @@
     <t>Inspect UI elements and layout fidelity for check wave animation on loading against design specifications.</t>
   </si>
   <si>
-    <t>2026-08-06T17:38:57.644Z</t>
+    <t>2026-08-06T17:44:54.945Z</t>
   </si>
   <si>
     <t>TC-UI-033</t>
@@ -1168,7 +1168,7 @@
     <t>Inspect UI elements and layout fidelity for validate custom calendar view cells against design specifications.</t>
   </si>
   <si>
-    <t>2026-08-06T17:38:57.661Z</t>
+    <t>2026-08-06T17:44:54.962Z</t>
   </si>
   <si>
     <t>TC-UI-034</t>
@@ -1180,7 +1180,7 @@
     <t>Inspect UI elements and layout fidelity for verify dialog box button spacing against design specifications.</t>
   </si>
   <si>
-    <t>2026-08-06T17:38:57.678Z</t>
+    <t>2026-08-06T17:44:54.986Z</t>
   </si>
   <si>
     <t>TC-UI-035</t>
@@ -1192,7 +1192,7 @@
     <t>Inspect UI elements and layout fidelity for check swipe-to-delete background red tint against design specifications.</t>
   </si>
   <si>
-    <t>2026-08-06T17:38:57.711Z</t>
+    <t>2026-08-06T17:44:55.016Z</t>
   </si>
   <si>
     <t>TC-UI-036</t>
@@ -1204,7 +1204,7 @@
     <t>Inspect UI elements and layout fidelity for validate accordion menu arrow rotation against design specifications.</t>
   </si>
   <si>
-    <t>2026-08-06T17:38:57.728Z</t>
+    <t>2026-08-06T17:44:55.045Z</t>
   </si>
   <si>
     <t>TC-UI-037</t>
@@ -1216,7 +1216,7 @@
     <t>Inspect UI elements and layout fidelity for verify segmented control active state against design specifications.</t>
   </si>
   <si>
-    <t>2026-08-06T17:38:57.744Z</t>
+    <t>2026-08-06T17:44:55.082Z</t>
   </si>
   <si>
     <t>TC-UI-038</t>
@@ -1228,7 +1228,7 @@
     <t>Inspect UI elements and layout fidelity for check rating star fill animation against design specifications.</t>
   </si>
   <si>
-    <t>2026-08-06T17:38:57.761Z</t>
+    <t>2026-08-06T17:44:55.112Z</t>
   </si>
   <si>
     <t>TC-UI-039</t>
@@ -1240,7 +1240,7 @@
     <t>Inspect UI elements and layout fidelity for validate slider knob drag shadow against design specifications.</t>
   </si>
   <si>
-    <t>2026-08-06T17:38:57.795Z</t>
+    <t>2026-08-06T17:44:55.129Z</t>
   </si>
   <si>
     <t>TC-UI-040</t>
@@ -1252,7 +1252,7 @@
     <t>Inspect UI elements and layout fidelity for verify badge counter dot position against design specifications.</t>
   </si>
   <si>
-    <t>2026-08-06T17:38:57.827Z</t>
+    <t>2026-08-06T17:44:55.146Z</t>
   </si>
   <si>
     <t>TC-UI-041</t>
@@ -1264,7 +1264,7 @@
     <t>Inspect UI elements and layout fidelity for check chip selector margin against design specifications.</t>
   </si>
   <si>
-    <t>2026-08-06T17:38:57.844Z</t>
+    <t>2026-08-06T17:44:55.161Z</t>
   </si>
   <si>
     <t>TC-UI-042</t>
@@ -1276,7 +1276,7 @@
     <t>Inspect UI elements and layout fidelity for validate step tracker progress arc against design specifications.</t>
   </si>
   <si>
-    <t>2026-08-06T17:38:57.878Z</t>
+    <t>2026-08-06T17:44:55.177Z</t>
   </si>
   <si>
     <t>TC-UI-043</t>
@@ -1288,7 +1288,7 @@
     <t>Inspect UI elements and layout fidelity for verify horizontal scroll view edge glow against design specifications.</t>
   </si>
   <si>
-    <t>2026-08-06T17:38:57.911Z</t>
+    <t>2026-08-06T17:44:55.212Z</t>
   </si>
   <si>
     <t>TC-UI-044</t>
@@ -1300,7 +1300,7 @@
     <t>Inspect UI elements and layout fidelity for check sticky header snap effect against design specifications.</t>
   </si>
   <si>
-    <t>2026-08-06T17:38:57.928Z</t>
+    <t>2026-08-06T17:44:55.229Z</t>
   </si>
   <si>
     <t>TC-UI-045</t>
@@ -1312,7 +1312,7 @@
     <t>Inspect UI elements and layout fidelity for validate floating action button label against design specifications.</t>
   </si>
   <si>
-    <t>2026-08-06T17:38:57.944Z</t>
+    <t>2026-08-06T17:44:55.260Z</t>
   </si>
   <si>
     <t>TC-UI-046</t>
@@ -1324,7 +1324,7 @@
     <t>Inspect UI elements and layout fidelity for verify form input label floating effect against design specifications.</t>
   </si>
   <si>
-    <t>2026-08-06T17:38:57.961Z</t>
+    <t>2026-08-06T17:44:55.279Z</t>
   </si>
   <si>
     <t>TC-UI-047</t>
@@ -1336,7 +1336,7 @@
     <t>Inspect UI elements and layout fidelity for check dropdown menu transition against design specifications.</t>
   </si>
   <si>
-    <t>2026-08-06T17:38:57.980Z</t>
+    <t>2026-08-06T17:44:55.309Z</t>
   </si>
   <si>
     <t>TC-UI-048</t>
@@ -1348,7 +1348,7 @@
     <t>Inspect UI elements and layout fidelity for validate image crop overlay visual against design specifications.</t>
   </si>
   <si>
-    <t>2026-08-06T17:38:58.011Z</t>
+    <t>2026-08-06T17:44:55.323Z</t>
   </si>
   <si>
     <t>TC-UI-049</t>
@@ -1360,7 +1360,7 @@
     <t>Inspect UI elements and layout fidelity for verify screen transition fade in/out against design specifications.</t>
   </si>
   <si>
-    <t>2026-08-06T17:38:58.027Z</t>
+    <t>2026-08-06T17:44:55.348Z</t>
   </si>
   <si>
     <t>TC-UI-050</t>
@@ -1372,7 +1372,7 @@
     <t>Inspect UI elements and layout fidelity for check layout balance across aspect ratios against design specifications.</t>
   </si>
   <si>
-    <t>2026-08-06T17:38:58.044Z</t>
+    <t>2026-08-06T17:44:55.381Z</t>
   </si>
   <si>
     <t>TC-NAV-001</t>
@@ -1384,7 +1384,7 @@
     <t>Test navigation path, backstack state, and router transitions for verify dashboard to medical records route.</t>
   </si>
   <si>
-    <t>2026-08-06T17:38:58.078Z</t>
+    <t>2026-08-06T17:44:55.412Z</t>
   </si>
   <si>
     <t>TC-NAV-002</t>
@@ -1396,7 +1396,7 @@
     <t>Test navigation path, backstack state, and router transitions for check tab switch from vitals to reminders.</t>
   </si>
   <si>
-    <t>2026-08-06T17:38:58.102Z</t>
+    <t>2026-08-06T17:44:55.426Z</t>
   </si>
   <si>
     <t>TC-NAV-003</t>
@@ -1408,7 +1408,7 @@
     <t>Test navigation path, backstack state, and router transitions for validate back button stack behavior.</t>
   </si>
   <si>
-    <t>2026-08-06T17:38:58.127Z</t>
+    <t>2026-08-06T17:44:55.453Z</t>
   </si>
   <si>
     <t>TC-NAV-004</t>
@@ -1420,7 +1420,7 @@
     <t>Test navigation path, backstack state, and router transitions for verify deep link routing for medication alert.</t>
   </si>
   <si>
-    <t>2026-08-06T17:38:58.159Z</t>
+    <t>2026-08-06T17:44:55.469Z</t>
   </si>
   <si>
     <t>TC-NAV-005</t>
@@ -1432,7 +1432,7 @@
     <t>Test navigation path, backstack state, and router transitions for check bottom bar selection state on swipe.</t>
   </si>
   <si>
-    <t>2026-08-06T17:38:58.178Z</t>
+    <t>2026-08-06T17:44:55.499Z</t>
   </si>
   <si>
     <t>TC-NAV-006</t>
@@ -1444,7 +1444,7 @@
     <t>Test navigation path, backstack state, and router transitions for validate profile screen nav transition.</t>
   </si>
   <si>
-    <t>2026-08-06T17:38:58.194Z</t>
+    <t>2026-08-06T17:44:55.522Z</t>
   </si>
   <si>
     <t>TC-NAV-007</t>
@@ -1456,7 +1456,7 @@
     <t>Test navigation path, backstack state, and router transitions for verify settings nested submenu route.</t>
   </si>
   <si>
-    <t>2026-08-06T17:38:58.211Z</t>
+    <t>2026-08-06T17:44:55.554Z</t>
   </si>
   <si>
     <t>TC-NAV-008</t>
@@ -1468,7 +1468,7 @@
     <t>Test navigation path, backstack state, and router transitions for check exit confirmation dialog on back press.</t>
   </si>
   <si>
-    <t>2026-08-06T17:38:58.229Z</t>
+    <t>2026-08-06T17:44:55.579Z</t>
   </si>
   <si>
     <t>TC-NAV-009</t>
@@ -1480,7 +1480,7 @@
     <t>Test navigation path, backstack state, and router transitions for validate breadcrumb trail in records archive.</t>
   </si>
   <si>
-    <t>2026-08-06T17:38:58.261Z</t>
+    <t>2026-08-06T17:44:55.603Z</t>
   </si>
   <si>
     <t>TC-NAV-010</t>
@@ -1492,7 +1492,7 @@
     <t>Test navigation path, backstack state, and router transitions for verify push notification tap destination.</t>
   </si>
   <si>
-    <t>2026-08-06T17:38:58.277Z</t>
+    <t>2026-08-06T17:44:55.618Z</t>
   </si>
   <si>
     <t>TC-NAV-011</t>
@@ -1504,7 +1504,7 @@
     <t>Test navigation path, backstack state, and router transitions for check quick action shortcut route.</t>
   </si>
   <si>
-    <t>2026-08-06T17:38:58.294Z</t>
+    <t>2026-08-06T17:44:55.650Z</t>
   </si>
   <si>
     <t>TC-NAV-012</t>
@@ -1516,7 +1516,7 @@
     <t>Test navigation path, backstack state, and router transitions for validate unsaved changes nav guard.</t>
   </si>
   <si>
-    <t>2026-08-06T17:38:58.311Z</t>
+    <t>2026-08-06T17:44:55.671Z</t>
   </si>
   <si>
     <t>TC-NAV-013</t>
@@ -1528,7 +1528,7 @@
     <t>Test navigation path, backstack state, and router transitions for verify ai hub screen launch from home.</t>
   </si>
   <si>
-    <t>2026-08-06T17:38:58.328Z</t>
+    <t>2026-08-06T17:44:55.687Z</t>
   </si>
   <si>
     <t>TC-NAV-014</t>
@@ -1540,7 +1540,7 @@
     <t>Test navigation path, backstack state, and router transitions for check ocr camera screen navigation.</t>
   </si>
   <si>
-    <t>2026-08-06T17:38:58.362Z</t>
+    <t>2026-08-06T17:44:55.703Z</t>
   </si>
   <si>
     <t>TC-NAV-015</t>
@@ -1552,7 +1552,7 @@
     <t>Test navigation path, backstack state, and router transitions for validate prescription detail modal push.</t>
   </si>
   <si>
-    <t>2026-08-06T17:38:58.378Z</t>
+    <t>2026-08-06T17:44:55.718Z</t>
   </si>
   <si>
     <t>TC-NAV-016</t>
@@ -1564,7 +1564,7 @@
     <t>Test navigation path, backstack state, and router transitions for verify doctor chat screen route.</t>
   </si>
   <si>
-    <t>2026-08-06T17:38:58.395Z</t>
+    <t>2026-08-06T17:44:55.743Z</t>
   </si>
   <si>
     <t>TC-NAV-017</t>
@@ -1576,7 +1576,7 @@
     <t>Test navigation path, backstack state, and router transitions for check analytics sub-tab navigation.</t>
   </si>
   <si>
-    <t>2026-08-06T17:38:58.411Z</t>
+    <t>2026-08-06T17:44:55.759Z</t>
   </si>
   <si>
     <t>TC-NAV-018</t>
@@ -1588,7 +1588,7 @@
     <t>Test navigation path, backstack state, and router transitions for validate cross-feature link from vital to doctor.</t>
   </si>
   <si>
-    <t>2026-08-06T17:38:58.428Z</t>
+    <t>2026-08-06T17:44:55.785Z</t>
   </si>
   <si>
     <t>TC-NAV-019</t>
@@ -1600,7 +1600,7 @@
     <t>Test navigation path, backstack state, and router transitions for verify drawer menu screen navigation.</t>
   </si>
   <si>
-    <t>2026-08-06T17:38:58.462Z</t>
+    <t>2026-08-06T17:44:55.801Z</t>
   </si>
   <si>
     <t>TC-NAV-020</t>
@@ -1612,7 +1612,7 @@
     <t>Test navigation path, backstack state, and router transitions for check back stack clear on logout.</t>
   </si>
   <si>
-    <t>2026-08-06T17:38:58.478Z</t>
+    <t>2026-08-06T17:44:55.828Z</t>
   </si>
   <si>
     <t>TC-NAV-021</t>
@@ -1624,7 +1624,7 @@
     <t>Test navigation path, backstack state, and router transitions for validate re-authentication nav intercept.</t>
   </si>
   <si>
-    <t>2026-08-06T17:38:58.495Z</t>
+    <t>2026-08-06T17:44:55.849Z</t>
   </si>
   <si>
     <t>TC-NAV-022</t>
@@ -1636,7 +1636,7 @@
     <t>Test navigation path, backstack state, and router transitions for verify home screen return on app resume.</t>
   </si>
   <si>
-    <t>2026-08-06T17:38:58.528Z</t>
+    <t>2026-08-06T17:44:55.865Z</t>
   </si>
   <si>
     <t>TC-NAV-023</t>
@@ -1648,7 +1648,7 @@
     <t>Test navigation path, backstack state, and router transitions for check external link handling (privacy policy).</t>
   </si>
   <si>
-    <t>2026-08-06T17:38:58.560Z</t>
+    <t>2026-08-06T17:44:55.880Z</t>
   </si>
   <si>
     <t>TC-NAV-024</t>
@@ -1660,7 +1660,7 @@
     <t>Test navigation path, backstack state, and router transitions for validate help &amp; support webview navigation.</t>
   </si>
   <si>
-    <t>2026-08-06T17:38:58.594Z</t>
+    <t>2026-08-06T17:44:55.912Z</t>
   </si>
   <si>
     <t>TC-NAV-025</t>
@@ -1672,7 +1672,7 @@
     <t>Test navigation path, backstack state, and router transitions for verify appointment detail screen route.</t>
   </si>
   <si>
-    <t>2026-08-06T17:38:58.611Z</t>
+    <t>2026-08-06T17:44:55.930Z</t>
   </si>
   <si>
     <t>TC-NAV-026</t>
@@ -1684,7 +1684,7 @@
     <t>Test navigation path, backstack state, and router transitions for check category filter deep linking.</t>
   </si>
   <si>
-    <t>2026-08-06T17:38:58.628Z</t>
+    <t>2026-08-06T17:44:55.962Z</t>
   </si>
   <si>
     <t>TC-NAV-027</t>
@@ -1696,7 +1696,7 @@
     <t>Test navigation path, backstack state, and router transitions for validate multi-step form screen forward route.</t>
   </si>
   <si>
-    <t>2026-08-06T17:38:58.644Z</t>
+    <t>2026-08-06T17:44:55.981Z</t>
   </si>
   <si>
     <t>TC-NAV-028</t>
@@ -1708,7 +1708,7 @@
     <t>Test navigation path, backstack state, and router transitions for verify multi-step form screen backward route.</t>
   </si>
   <si>
-    <t>2026-08-06T17:38:58.661Z</t>
+    <t>2026-08-06T17:44:55.997Z</t>
   </si>
   <si>
     <t>TC-NAV-029</t>
@@ -1720,7 +1720,7 @@
     <t>Test navigation path, backstack state, and router transitions for check tab restoration after orientation change.</t>
   </si>
   <si>
-    <t>2026-08-06T17:38:58.678Z</t>
+    <t>2026-08-06T17:44:56.013Z</t>
   </si>
   <si>
     <t>TC-NAV-030</t>
@@ -1732,7 +1732,7 @@
     <t>Test navigation path, backstack state, and router transitions for validate search result item tap destination.</t>
   </si>
   <si>
-    <t>2026-08-06T17:38:58.712Z</t>
+    <t>2026-08-06T17:44:56.030Z</t>
   </si>
   <si>
     <t>TC-NAV-031</t>
@@ -1744,7 +1744,7 @@
     <t>Test navigation path, backstack state, and router transitions for verify notification history list nav.</t>
   </si>
   <si>
-    <t>2026-08-06T17:38:58.728Z</t>
+    <t>2026-08-06T17:44:56.046Z</t>
   </si>
   <si>
     <t>TC-NAV-032</t>
@@ -1756,7 +1756,7 @@
     <t>Test navigation path, backstack state, and router transitions for check emergency contact call intent launch.</t>
   </si>
   <si>
-    <t>2026-08-06T17:38:58.745Z</t>
+    <t>2026-08-06T17:44:56.063Z</t>
   </si>
   <si>
     <t>TC-NAV-033</t>
@@ -1768,7 +1768,7 @@
     <t>Test navigation path, backstack state, and router transitions for validate pharmacy map screen route.</t>
   </si>
   <si>
-    <t>2026-08-06T17:38:58.762Z</t>
+    <t>2026-08-06T17:44:56.079Z</t>
   </si>
   <si>
     <t>TC-NAV-034</t>
@@ -1780,7 +1780,7 @@
     <t>Test navigation path, backstack state, and router transitions for verify diagnostic test list routing.</t>
   </si>
   <si>
-    <t>2026-08-06T17:38:58.778Z</t>
+    <t>2026-08-06T17:44:56.095Z</t>
   </si>
   <si>
     <t>TC-NAV-035</t>
@@ -1792,7 +1792,7 @@
     <t>Test navigation path, backstack state, and router transitions for check lab report download screen route.</t>
   </si>
   <si>
-    <t>2026-08-06T17:38:58.795Z</t>
+    <t>2026-08-06T17:44:56.112Z</t>
   </si>
   <si>
     <t>TC-NAV-036</t>
@@ -1804,7 +1804,7 @@
     <t>Test navigation path, backstack state, and router transitions for validate family member profile switch route.</t>
   </si>
   <si>
-    <t>2026-08-06T17:38:58.811Z</t>
+    <t>2026-08-06T17:44:56.145Z</t>
   </si>
   <si>
     <t>TC-NAV-037</t>
@@ -1816,7 +1816,7 @@
     <t>Test navigation path, backstack state, and router transitions for verify symptom checker wizard steps.</t>
   </si>
   <si>
-    <t>2026-08-06T17:38:58.828Z</t>
+    <t>2026-08-06T17:44:56.160Z</t>
   </si>
   <si>
     <t>TC-NAV-038</t>
@@ -1828,7 +1828,7 @@
     <t>Test navigation path, backstack state, and router transitions for check device connection screen route.</t>
   </si>
   <si>
-    <t>2026-08-06T17:38:58.861Z</t>
+    <t>2026-08-06T17:44:56.178Z</t>
   </si>
   <si>
     <t>TC-NAV-039</t>
@@ -1840,7 +1840,7 @@
     <t>Test navigation path, backstack state, and router transitions for validate bluetooth pair setup navigation.</t>
   </si>
   <si>
-    <t>2026-08-06T17:38:58.876Z</t>
+    <t>2026-08-06T17:44:56.198Z</t>
   </si>
   <si>
     <t>TC-NAV-040</t>
@@ -1852,7 +1852,7 @@
     <t>Test navigation path, backstack state, and router transitions for verify account security sub-menu route.</t>
   </si>
   <si>
-    <t>2026-08-06T17:38:58.895Z</t>
+    <t>2026-08-06T17:44:56.214Z</t>
   </si>
   <si>
     <t>TC-NAV-041</t>
@@ -1864,7 +1864,7 @@
     <t>Test navigation path, backstack state, and router transitions for verify activity log history route.</t>
   </si>
   <si>
-    <t>2026-08-06T17:38:58.911Z</t>
+    <t>2026-08-06T17:44:56.246Z</t>
   </si>
   <si>
     <t>TC-NAV-042</t>
@@ -1876,7 +1876,7 @@
     <t>Test navigation path, backstack state, and router transitions for check data export wizard navigation.</t>
   </si>
   <si>
-    <t>2026-08-06T17:38:58.928Z</t>
+    <t>2026-08-06T17:44:56.279Z</t>
   </si>
   <si>
     <t>TC-NAV-043</t>
@@ -1888,7 +1888,7 @@
     <t>Test navigation path, backstack state, and router transitions for validate billing &amp; subscription screen route.</t>
   </si>
   <si>
-    <t>2026-08-06T17:38:58.962Z</t>
+    <t>2026-08-06T17:44:56.295Z</t>
   </si>
   <si>
     <t>TC-NAV-044</t>
@@ -1900,7 +1900,7 @@
     <t>Test navigation path, backstack state, and router transitions for verify feedback form screen launch.</t>
   </si>
   <si>
-    <t>2026-08-06T17:38:58.994Z</t>
+    <t>2026-08-06T17:44:56.312Z</t>
   </si>
   <si>
     <t>TC-NAV-045</t>
@@ -1912,7 +1912,7 @@
     <t>Test navigation path, backstack state, and router transitions for check faq accordion nav scroll.</t>
   </si>
   <si>
-    <t>2026-08-06T17:38:59.028Z</t>
+    <t>2026-08-06T17:44:56.345Z</t>
   </si>
   <si>
     <t>TC-NAV-046</t>
@@ -1924,7 +1924,7 @@
     <t>Test navigation path, backstack state, and router transitions for validate offline notice screen redirection.</t>
   </si>
   <si>
-    <t>2026-08-06T17:38:59.045Z</t>
+    <t>2026-08-06T17:44:56.364Z</t>
   </si>
   <si>
     <t>TC-NAV-047</t>
@@ -1936,7 +1936,7 @@
     <t>Test navigation path, backstack state, and router transitions for verify server error screen retry navigation.</t>
   </si>
   <si>
-    <t>2026-08-06T17:38:59.077Z</t>
+    <t>2026-08-06T17:44:56.399Z</t>
   </si>
   <si>
     <t>TC-NAV-048</t>
@@ -1948,7 +1948,7 @@
     <t>Test navigation path, backstack state, and router transitions for check session timeout redirect to login.</t>
   </si>
   <si>
-    <t>2026-08-06T17:38:59.095Z</t>
+    <t>2026-08-06T17:44:56.413Z</t>
   </si>
   <si>
     <t>TC-NAV-049</t>
@@ -1960,7 +1960,7 @@
     <t>Test navigation path, backstack state, and router transitions for validate deep link schema healthlog://record/123.</t>
   </si>
   <si>
-    <t>2026-08-06T17:38:59.111Z</t>
+    <t>2026-08-06T17:44:56.433Z</t>
   </si>
   <si>
     <t>TC-NAV-050</t>
@@ -1972,7 +1972,7 @@
     <t>Test navigation path, backstack state, and router transitions for verify deep link schema healthlog://reminder/456.</t>
   </si>
   <si>
-    <t>2026-08-06T17:38:59.127Z</t>
+    <t>2026-08-06T17:44:56.447Z</t>
   </si>
   <si>
     <t>TC-AUTH-001</t>
@@ -1984,7 +1984,7 @@
     <t>Test authentication flows, biometric security, and session management for verify login with valid credentials.</t>
   </si>
   <si>
-    <t>2026-08-06T17:38:59.144Z</t>
+    <t>2026-08-06T17:44:56.462Z</t>
   </si>
   <si>
     <t>TC-AUTH-002</t>
@@ -1996,7 +1996,7 @@
     <t>Test authentication flows, biometric security, and session management for validate login failure with wrong password.</t>
   </si>
   <si>
-    <t>2026-08-06T17:38:59.161Z</t>
+    <t>2026-08-06T17:44:56.483Z</t>
   </si>
   <si>
     <t>TC-AUTH-003</t>
@@ -2008,7 +2008,7 @@
     <t>Test authentication flows, biometric security, and session management for check email format validation on login.</t>
   </si>
   <si>
-    <t>2026-08-06T17:38:59.176Z</t>
+    <t>2026-08-06T17:44:56.511Z</t>
   </si>
   <si>
     <t>TC-AUTH-004</t>
@@ -2020,7 +2020,7 @@
     <t>Test authentication flows, biometric security, and session management for verify registration with new user data.</t>
   </si>
   <si>
-    <t>2026-08-06T17:38:59.211Z</t>
+    <t>2026-08-06T17:44:56.532Z</t>
   </si>
   <si>
     <t>TC-AUTH-005</t>
@@ -2032,7 +2032,7 @@
     <t>Test authentication flows, biometric security, and session management for check password strength indicator.</t>
   </si>
   <si>
-    <t>2026-08-06T17:38:59.228Z</t>
+    <t>2026-08-06T17:44:56.562Z</t>
   </si>
   <si>
     <t>TC-AUTH-006</t>
@@ -2044,7 +2044,7 @@
     <t>Test authentication flows, biometric security, and session management for validate duplicate email signup error.</t>
   </si>
   <si>
-    <t>2026-08-06T17:38:59.245Z</t>
+    <t>2026-08-06T17:44:56.580Z</t>
   </si>
   <si>
     <t>TC-AUTH-007</t>
@@ -2056,7 +2056,7 @@
     <t>Test authentication flows, biometric security, and session management for verify otp generation for password reset.</t>
   </si>
   <si>
-    <t>2026-08-06T17:38:59.261Z</t>
+    <t>2026-08-06T17:44:56.611Z</t>
   </si>
   <si>
     <t>TC-AUTH-008</t>
@@ -2068,7 +2068,7 @@
     <t>Test authentication flows, biometric security, and session management for check otp expiration timer.</t>
   </si>
   <si>
-    <t>2026-08-06T17:38:59.277Z</t>
+    <t>2026-08-06T17:44:56.626Z</t>
   </si>
   <si>
     <t>TC-AUTH-009</t>
@@ -2080,7 +2080,7 @@
     <t>Test authentication flows, biometric security, and session management for validate otp verification success.</t>
   </si>
   <si>
-    <t>2026-08-06T17:38:59.294Z</t>
+    <t>2026-08-06T17:44:56.662Z</t>
   </si>
   <si>
     <t>TC-AUTH-010</t>
@@ -2092,7 +2092,7 @@
     <t>Test authentication flows, biometric security, and session management for verify fingerprint biometric unlock.</t>
   </si>
   <si>
-    <t>2026-08-06T17:38:59.328Z</t>
+    <t>2026-08-06T17:44:56.689Z</t>
   </si>
   <si>
     <t>TC-AUTH-011</t>
@@ -2104,7 +2104,7 @@
     <t>Test authentication flows, biometric security, and session management for check faceid authentication trigger.</t>
   </si>
   <si>
-    <t>2026-08-06T17:38:59.361Z</t>
+    <t>2026-08-06T17:44:56.711Z</t>
   </si>
   <si>
     <t>TC-AUTH-012</t>
@@ -2116,7 +2116,7 @@
     <t>Test authentication flows, biometric security, and session management for validate fallback to pin on biometric fail.</t>
   </si>
   <si>
-    <t>2026-08-06T17:38:59.378Z</t>
+    <t>2026-08-06T17:44:56.727Z</t>
   </si>
   <si>
     <t>TC-AUTH-013</t>
@@ -2128,7 +2128,7 @@
     <t>Test authentication flows, biometric security, and session management for verify jwt access token storage.</t>
   </si>
   <si>
-    <t>2026-08-06T17:38:59.411Z</t>
+    <t>2026-08-06T17:44:56.744Z</t>
   </si>
   <si>
     <t>TC-AUTH-014</t>
@@ -2140,7 +2140,7 @@
     <t>Test authentication flows, biometric security, and session management for check refresh token rotation.</t>
   </si>
   <si>
-    <t>2026-08-06T17:38:59.445Z</t>
+    <t>2026-08-06T17:44:56.765Z</t>
   </si>
   <si>
     <t>TC-AUTH-015</t>
@@ -2152,7 +2152,7 @@
     <t>Test authentication flows, biometric security, and session management for validate automatic token renewal on 401.</t>
   </si>
   <si>
-    <t>2026-08-06T17:38:59.461Z</t>
+    <t>2026-08-06T17:44:56.797Z</t>
   </si>
   <si>
     <t>TC-AUTH-016</t>
@@ -2164,7 +2164,7 @@
     <t>Test authentication flows, biometric security, and session management for verify remember me checkbox logic.</t>
   </si>
   <si>
-    <t>2026-08-06T17:38:59.478Z</t>
+    <t>2026-08-06T17:44:56.828Z</t>
   </si>
   <si>
     <t>TC-AUTH-017</t>
@@ -2176,7 +2176,7 @@
     <t>Test authentication flows, biometric security, and session management for check logout token invalidation.</t>
   </si>
   <si>
-    <t>2026-08-06T17:38:59.512Z</t>
+    <t>2026-08-06T17:44:56.860Z</t>
   </si>
   <si>
     <t>TC-AUTH-018</t>
@@ -2188,7 +2188,7 @@
     <t>Test authentication flows, biometric security, and session management for validate multi-device active sessions list.</t>
   </si>
   <si>
-    <t>2026-08-06T17:38:59.528Z</t>
+    <t>2026-08-06T17:44:56.894Z</t>
   </si>
   <si>
     <t>TC-AUTH-019</t>
@@ -2200,7 +2200,7 @@
     <t>Test authentication flows, biometric security, and session management for verify remote device revocation.</t>
   </si>
   <si>
-    <t>2026-08-06T17:38:59.544Z</t>
+    <t>2026-08-06T17:44:56.914Z</t>
   </si>
   <si>
     <t>TC-AUTH-020</t>
@@ -2212,7 +2212,7 @@
     <t>Test authentication flows, biometric security, and session management for check account lockout after 5 failed logins.</t>
   </si>
   <si>
-    <t>2026-08-06T17:38:59.561Z</t>
+    <t>2026-08-06T17:44:56.931Z</t>
   </si>
   <si>
     <t>TC-AUTH-021</t>
@@ -2224,7 +2224,7 @@
     <t>Test authentication flows, biometric security, and session management for validate lockout countdown timer.</t>
   </si>
   <si>
-    <t>2026-08-06T17:38:59.594Z</t>
+    <t>2026-08-06T17:44:56.945Z</t>
   </si>
   <si>
     <t>TC-AUTH-022</t>
@@ -2236,7 +2236,7 @@
     <t>Test authentication flows, biometric security, and session management for verify social auth (google sign-in).</t>
   </si>
   <si>
-    <t>2026-08-06T17:38:59.611Z</t>
+    <t>2026-08-06T17:44:56.962Z</t>
   </si>
   <si>
     <t>TC-AUTH-023</t>
@@ -2248,7 +2248,7 @@
     <t>Test authentication flows, biometric security, and session management for check social auth (apple id sign-in).</t>
   </si>
   <si>
-    <t>2026-08-06T17:38:59.628Z</t>
+    <t>2026-08-06T17:44:56.978Z</t>
   </si>
   <si>
     <t>TC-AUTH-024</t>
@@ -2260,7 +2260,7 @@
     <t>Test authentication flows, biometric security, and session management for validate oauth callback token handling.</t>
   </si>
   <si>
-    <t>2026-08-06T17:38:59.643Z</t>
+    <t>2026-08-06T17:44:57.009Z</t>
   </si>
   <si>
     <t>TC-AUTH-025</t>
@@ -2272,7 +2272,7 @@
     <t>Test authentication flows, biometric security, and session management for verify two-factor authentication setup.</t>
   </si>
   <si>
-    <t>2026-08-06T17:38:59.660Z</t>
+    <t>2026-08-06T17:44:57.029Z</t>
   </si>
   <si>
     <t>TC-AUTH-026</t>
@@ -2284,7 +2284,7 @@
     <t>Test authentication flows, biometric security, and session management for check 2fa authenticator app secret key.</t>
   </si>
   <si>
-    <t>2026-08-06T17:38:59.679Z</t>
+    <t>2026-08-06T17:44:57.048Z</t>
   </si>
   <si>
     <t>TC-AUTH-027</t>
@@ -2296,7 +2296,7 @@
     <t>Test authentication flows, biometric security, and session management for validate backup recovery codes generation.</t>
   </si>
   <si>
-    <t>2026-08-06T17:38:59.695Z</t>
+    <t>2026-08-06T17:44:57.062Z</t>
   </si>
   <si>
     <t>TC-AUTH-028</t>
@@ -2308,7 +2308,7 @@
     <t>Test authentication flows, biometric security, and session management for verify password change verification.</t>
   </si>
   <si>
-    <t>2026-08-06T17:38:59.728Z</t>
+    <t>2026-08-06T17:44:57.078Z</t>
   </si>
   <si>
     <t>TC-AUTH-029</t>
@@ -2320,7 +2320,7 @@
     <t>Test authentication flows, biometric security, and session management for check security question answer hash.</t>
   </si>
   <si>
-    <t>2026-08-06T17:38:59.745Z</t>
+    <t>2026-08-06T17:44:57.113Z</t>
   </si>
   <si>
     <t>TC-AUTH-030</t>
@@ -2332,7 +2332,7 @@
     <t>Test authentication flows, biometric security, and session management for validate phone number verification sms.</t>
   </si>
   <si>
-    <t>2026-08-06T17:38:59.761Z</t>
+    <t>2026-08-06T17:44:57.129Z</t>
   </si>
   <si>
     <t>TC-AUTH-031</t>
@@ -2344,7 +2344,7 @@
     <t>Test authentication flows, biometric security, and session management for verify pin setup on first launch.</t>
   </si>
   <si>
-    <t>2026-08-06T17:38:59.778Z</t>
+    <t>2026-08-06T17:44:57.161Z</t>
   </si>
   <si>
     <t>TC-AUTH-032</t>
@@ -2356,7 +2356,7 @@
     <t>Test authentication flows, biometric security, and session management for check pin change sequence.</t>
   </si>
   <si>
-    <t>2026-08-06T17:38:59.812Z</t>
+    <t>2026-08-06T17:44:57.179Z</t>
   </si>
   <si>
     <t>TC-AUTH-033</t>
@@ -2368,7 +2368,7 @@
     <t>Test authentication flows, biometric security, and session management for validate session timeout after inactivity.</t>
   </si>
   <si>
-    <t>2026-08-06T17:38:59.828Z</t>
+    <t>2026-08-06T17:44:57.199Z</t>
   </si>
   <si>
     <t>TC-AUTH-034</t>
@@ -2380,7 +2380,7 @@
     <t>Test authentication flows, biometric security, and session management for verify backgrounding lock trigger.</t>
   </si>
   <si>
-    <t>2026-08-06T17:38:59.845Z</t>
+    <t>2026-08-06T17:44:57.216Z</t>
   </si>
   <si>
     <t>TC-AUTH-035</t>
@@ -2392,7 +2392,7 @@
     <t>Test authentication flows, biometric security, and session management for check app re-entry security gate.</t>
   </si>
   <si>
-    <t>2026-08-06T17:38:59.862Z</t>
+    <t>2026-08-06T17:44:57.237Z</t>
   </si>
   <si>
     <t>TC-AUTH-036</t>
@@ -2404,7 +2404,7 @@
     <t>Test authentication flows, biometric security, and session management for validate encrypted shared preferences security.</t>
   </si>
   <si>
-    <t>2026-08-06T17:38:59.878Z</t>
+    <t>2026-08-06T17:44:57.254Z</t>
   </si>
   <si>
     <t>TC-AUTH-037</t>
@@ -2416,7 +2416,7 @@
     <t>Test authentication flows, biometric security, and session management for verify guest mode restrictions.</t>
   </si>
   <si>
-    <t>2026-08-06T17:38:59.895Z</t>
+    <t>2026-08-06T17:44:57.270Z</t>
   </si>
   <si>
     <t>TC-AUTH-038</t>
@@ -2428,7 +2428,7 @@
     <t>Test authentication flows, biometric security, and session management for check upgrade guest to registered account.</t>
   </si>
   <si>
-    <t>2026-08-06T17:38:59.911Z</t>
+    <t>2026-08-06T17:44:57.285Z</t>
   </si>
   <si>
     <t>TC-AUTH-039</t>
@@ -2440,7 +2440,7 @@
     <t>Test authentication flows, biometric security, and session management for validate data privacy consent check.</t>
   </si>
   <si>
-    <t>2026-08-06T17:38:59.927Z</t>
+    <t>2026-08-06T17:44:57.293Z</t>
   </si>
   <si>
     <t>TC-AUTH-040</t>
@@ -2452,7 +2452,7 @@
     <t>Test authentication flows, biometric security, and session management for verify terms of service accept gate.</t>
   </si>
   <si>
-    <t>2026-08-06T17:38:59.944Z</t>
+    <t>2026-08-06T17:44:57.329Z</t>
   </si>
   <si>
     <t>TC-AUTH-041</t>
@@ -2464,7 +2464,7 @@
     <t>Test authentication flows, biometric security, and session management for check user role permissions (patient vs doctor).</t>
   </si>
   <si>
-    <t>2026-08-06T17:38:59.977Z</t>
+    <t>2026-08-06T17:44:57.366Z</t>
   </si>
   <si>
     <t>TC-AUTH-042</t>
@@ -2476,7 +2476,7 @@
     <t>Test authentication flows, biometric security, and session management for validate admin portal access restrict.</t>
   </si>
   <si>
-    <t>2026-08-06T17:38:59.986Z</t>
+    <t>2026-08-06T17:44:57.389Z</t>
   </si>
   <si>
     <t>TC-AUTH-043</t>
@@ -2488,7 +2488,7 @@
     <t>Test authentication flows, biometric security, and session management for verify account recovery via security email.</t>
   </si>
   <si>
-    <t>2026-08-06T17:39:00.011Z</t>
+    <t>2026-08-06T17:44:57.399Z</t>
   </si>
   <si>
     <t>TC-AUTH-044</t>
@@ -2500,7 +2500,7 @@
     <t>Test authentication flows, biometric security, and session management for check identity verification document upload.</t>
   </si>
   <si>
-    <t>2026-08-06T17:39:00.045Z</t>
+    <t>2026-08-06T17:44:57.422Z</t>
   </si>
   <si>
     <t>TC-AUTH-045</t>
@@ -2512,7 +2512,7 @@
     <t>Test authentication flows, biometric security, and session management for validate passkey login prompt.</t>
   </si>
   <si>
-    <t>2026-08-06T17:39:00.061Z</t>
+    <t>2026-08-06T17:44:57.434Z</t>
   </si>
   <si>
     <t>TC-AUTH-046</t>
@@ -2524,7 +2524,7 @@
     <t>Test authentication flows, biometric security, and session management for verify biometric prompt cancellation handling.</t>
   </si>
   <si>
-    <t>2026-08-06T17:39:00.094Z</t>
+    <t>2026-08-06T17:44:57.454Z</t>
   </si>
   <si>
     <t>TC-AUTH-047</t>
@@ -2536,7 +2536,7 @@
     <t>Test authentication flows, biometric security, and session management for check token cleared on app uninstall/reinstall.</t>
   </si>
   <si>
-    <t>2026-08-06T17:39:00.112Z</t>
+    <t>2026-08-06T17:44:57.468Z</t>
   </si>
   <si>
     <t>TC-AUTH-048</t>
@@ -2548,7 +2548,7 @@
     <t>Test authentication flows, biometric security, and session management for validate auth header injection.</t>
   </si>
   <si>
-    <t>2026-08-06T17:39:00.144Z</t>
+    <t>2026-08-06T17:44:57.489Z</t>
   </si>
   <si>
     <t>TC-AUTH-049</t>
@@ -2560,7 +2560,7 @@
     <t>Test authentication flows, biometric security, and session management for verify ssl pinning gate on auth endpoint.</t>
   </si>
   <si>
-    <t>2026-08-06T17:39:00.161Z</t>
+    <t>2026-08-06T17:44:57.503Z</t>
   </si>
   <si>
     <t>TC-AUTH-050</t>
@@ -2572,7 +2572,7 @@
     <t>Test authentication flows, biometric security, and session management for check rate limiting warning on auth api.</t>
   </si>
   <si>
-    <t>2026-08-06T17:39:00.176Z</t>
+    <t>2026-08-06T17:44:57.532Z</t>
   </si>
   <si>
     <t>TC-MED-001</t>
@@ -2584,7 +2584,7 @@
     <t>Test health record management, EHR integrations, and data validation for verify add new prescription record.</t>
   </si>
   <si>
-    <t>2026-08-06T17:39:00.195Z</t>
+    <t>2026-08-06T17:44:57.549Z</t>
   </si>
   <si>
     <t>TC-MED-002</t>
@@ -2596,7 +2596,7 @@
     <t>Test health record management, EHR integrations, and data validation for validate prescription dosage unit selector.</t>
   </si>
   <si>
-    <t>2026-08-06T17:39:00.218Z</t>
+    <t>2026-08-06T17:44:57.571Z</t>
   </si>
   <si>
     <t>TC-MED-003</t>
@@ -2608,7 +2608,7 @@
     <t>Test health record management, EHR integrations, and data validation for check doctor name search autocomplete.</t>
   </si>
   <si>
-    <t>2026-08-06T17:39:00.234Z</t>
+    <t>2026-08-06T17:44:57.589Z</t>
   </si>
   <si>
     <t>TC-MED-004</t>
@@ -2620,7 +2620,7 @@
     <t>Test health record management, EHR integrations, and data validation for verify edit existing medical note.</t>
   </si>
   <si>
-    <t>2026-08-06T17:39:00.261Z</t>
+    <t>2026-08-06T17:44:57.616Z</t>
   </si>
   <si>
     <t>TC-MED-005</t>
@@ -2632,7 +2632,7 @@
     <t>Test health record management, EHR integrations, and data validation for check delete record confirmation modal.</t>
   </si>
   <si>
-    <t>2026-08-06T17:39:00.278Z</t>
+    <t>2026-08-06T17:44:57.636Z</t>
   </si>
   <si>
     <t>TC-MED-006</t>
@@ -2644,7 +2644,7 @@
     <t>Test health record management, EHR integrations, and data validation for validate lab test result value validation.</t>
   </si>
   <si>
-    <t>2026-08-06T17:39:00.294Z</t>
+    <t>2026-08-06T17:44:57.650Z</t>
   </si>
   <si>
     <t>TC-MED-007</t>
@@ -2656,7 +2656,7 @@
     <t>Test health record management, EHR integrations, and data validation for verify blood pressure reading log (systolic/diastolic).</t>
   </si>
   <si>
-    <t>2026-08-06T17:39:00.311Z</t>
+    <t>2026-08-06T17:44:57.688Z</t>
   </si>
   <si>
     <t>TC-MED-008</t>
@@ -2668,7 +2668,7 @@
     <t>Test health record management, EHR integrations, and data validation for check glucose level tag (fasting vs post-meal).</t>
   </si>
   <si>
-    <t>2026-08-06T17:39:00.341Z</t>
+    <t>2026-08-06T17:44:57.721Z</t>
   </si>
   <si>
     <t>TC-MED-009</t>
@@ -2680,7 +2680,7 @@
     <t>Test health record management, EHR integrations, and data validation for validate cholesterol sub-types (hdl/ldl).</t>
   </si>
   <si>
-    <t>2026-08-06T17:39:00.366Z</t>
+    <t>2026-08-06T17:44:57.748Z</t>
   </si>
   <si>
     <t>TC-MED-010</t>
@@ -2692,7 +2692,7 @@
     <t>Test health record management, EHR integrations, and data validation for verify heart rate ecg graph generation.</t>
   </si>
   <si>
-    <t>2026-08-06T17:39:00.382Z</t>
+    <t>2026-08-06T17:44:57.781Z</t>
   </si>
   <si>
     <t>TC-MED-011</t>
@@ -2704,7 +2704,7 @@
     <t>Test health record management, EHR integrations, and data validation for check body temperature scale toggle (c/f).</t>
   </si>
   <si>
-    <t>2026-08-06T17:39:00.399Z</t>
+    <t>2026-08-06T17:44:57.810Z</t>
   </si>
   <si>
     <t>TC-MED-012</t>
@@ -2716,7 +2716,7 @@
     <t>Test health record management, EHR integrations, and data validation for validate oxygen saturation (spo2) range warning.</t>
   </si>
   <si>
-    <t>2026-08-06T17:39:00.414Z</t>
+    <t>2026-08-06T17:44:57.844Z</t>
   </si>
   <si>
     <t>TC-MED-013</t>
@@ -2728,7 +2728,7 @@
     <t>Test health record management, EHR integrations, and data validation for verify medical attachment file upload (pdf).</t>
   </si>
   <si>
-    <t>2026-08-06T17:39:00.444Z</t>
+    <t>2026-08-06T17:44:57.877Z</t>
   </si>
   <si>
     <t>TC-MED-014</t>
@@ -2740,7 +2740,7 @@
     <t>Test health record management, EHR integrations, and data validation for check medical attachment image preview.</t>
   </si>
   <si>
-    <t>2026-08-06T17:39:00.461Z</t>
+    <t>2026-08-06T17:44:57.896Z</t>
   </si>
   <si>
     <t>TC-MED-015</t>
@@ -2752,7 +2752,7 @@
     <t>Test health record management, EHR integrations, and data validation for validate pdf encryption key generation.</t>
   </si>
   <si>
-    <t>2026-08-06T17:39:00.483Z</t>
+    <t>2026-08-06T17:44:57.926Z</t>
   </si>
   <si>
     <t>TC-MED-016</t>
@@ -2764,7 +2764,7 @@
     <t>Test health record management, EHR integrations, and data validation for verify record date sorting (newest first).</t>
   </si>
   <si>
-    <t>2026-08-06T17:39:00.498Z</t>
+    <t>2026-08-06T17:44:57.947Z</t>
   </si>
   <si>
     <t>TC-MED-017</t>
@@ -2776,7 +2776,7 @@
     <t>Test health record management, EHR integrations, and data validation for check category filter (cardiology, neurology, etc.).</t>
   </si>
   <si>
-    <t>2026-08-06T17:39:00.515Z</t>
+    <t>2026-08-06T17:44:57.964Z</t>
   </si>
   <si>
     <t>TC-MED-018</t>
@@ -2788,7 +2788,7 @@
     <t>Test health record management, EHR integrations, and data validation for validate full-text record keyword search.</t>
   </si>
   <si>
-    <t>2026-08-06T17:39:00.533Z</t>
+    <t>2026-08-06T17:44:57.997Z</t>
   </si>
   <si>
     <t>TC-MED-019</t>
@@ -2800,7 +2800,7 @@
     <t>Test health record management, EHR integrations, and data validation for verify export health summary to pdf.</t>
   </si>
   <si>
-    <t>2026-08-06T17:39:00.549Z</t>
+    <t>2026-08-06T17:44:58.027Z</t>
   </si>
   <si>
     <t>TC-MED-020</t>
@@ -2812,7 +2812,7 @@
     <t>Test health record management, EHR integrations, and data validation for check export record data to encrypted zip.</t>
   </si>
   <si>
-    <t>2026-08-06T17:39:00.583Z</t>
+    <t>2026-08-06T17:44:58.049Z</t>
   </si>
   <si>
     <t>TC-MED-021</t>
@@ -2824,7 +2824,7 @@
     <t>Test health record management, EHR integrations, and data validation for validate share record via secure doctor portal.</t>
   </si>
   <si>
-    <t>2026-08-06T17:39:00.609Z</t>
+    <t>2026-08-06T17:44:58.062Z</t>
   </si>
   <si>
     <t>TC-MED-022</t>
@@ -2836,7 +2836,7 @@
     <t>Test health record management, EHR integrations, and data validation for verify medical history timeline visualization.</t>
   </si>
   <si>
-    <t>2026-08-06T17:39:00.633Z</t>
+    <t>2026-08-06T17:44:58.080Z</t>
   </si>
   <si>
     <t>TC-MED-023</t>
@@ -2848,7 +2848,7 @@
     <t>Test health record management, EHR integrations, and data validation for check chronic condition tagging.</t>
   </si>
   <si>
-    <t>2026-08-06T17:39:00.664Z</t>
+    <t>2026-08-06T17:44:58.108Z</t>
   </si>
   <si>
     <t>TC-MED-024</t>
@@ -2860,7 +2860,7 @@
     <t>Test health record management, EHR integrations, and data validation for validate surgical history entry.</t>
   </si>
   <si>
-    <t>2026-08-06T17:39:00.683Z</t>
+    <t>2026-08-06T17:44:58.133Z</t>
   </si>
   <si>
     <t>TC-MED-025</t>
@@ -2872,7 +2872,7 @@
     <t>Test health record management, EHR integrations, and data validation for verify vaccination passport qr code generator.</t>
   </si>
   <si>
-    <t>2026-08-06T17:39:00.695Z</t>
+    <t>2026-08-06T17:44:58.166Z</t>
   </si>
   <si>
     <t>TC-MED-026</t>
@@ -2884,7 +2884,7 @@
     <t>Test health record management, EHR integrations, and data validation for check allergy severity classification.</t>
   </si>
   <si>
-    <t>2026-08-06T17:39:00.718Z</t>
+    <t>2026-08-06T17:44:58.201Z</t>
   </si>
   <si>
     <t>TC-MED-027</t>
@@ -2896,7 +2896,7 @@
     <t>Test health record management, EHR integrations, and data validation for validate family medical history tree input.</t>
   </si>
   <si>
-    <t>2026-08-06T17:39:00.749Z</t>
+    <t>2026-08-06T17:44:58.227Z</t>
   </si>
   <si>
     <t>TC-MED-028</t>
@@ -2908,7 +2908,7 @@
     <t>Test health record management, EHR integrations, and data validation for verify vital signs normal range indicators.</t>
   </si>
   <si>
-    <t>2026-08-06T17:39:00.779Z</t>
+    <t>2026-08-06T17:44:58.247Z</t>
   </si>
   <si>
     <t>TC-MED-029</t>
@@ -2920,7 +2920,7 @@
     <t>Test health record management, EHR integrations, and data validation for check abnormal test value highlight (red flag).</t>
   </si>
   <si>
-    <t>2026-08-06T17:39:00.795Z</t>
+    <t>2026-08-06T17:44:58.263Z</t>
   </si>
   <si>
     <t>TC-MED-030</t>
@@ -2932,7 +2932,7 @@
     <t>Test health record management, EHR integrations, and data validation for validate provider npi identifier lookup.</t>
   </si>
   <si>
-    <t>2026-08-06T17:39:00.832Z</t>
+    <t>2026-08-06T17:44:58.283Z</t>
   </si>
   <si>
     <t>TC-MED-031</t>
@@ -2944,7 +2944,7 @@
     <t>Test health record management, EHR integrations, and data validation for verify pharmacy contact detail association.</t>
   </si>
   <si>
-    <t>2026-08-06T17:39:00.850Z</t>
+    <t>2026-08-06T17:44:58.312Z</t>
   </si>
   <si>
     <t>TC-MED-032</t>
@@ -2956,7 +2956,7 @@
     <t>Test health record management, EHR integrations, and data validation for check refill request history tracker.</t>
   </si>
   <si>
-    <t>2026-08-06T17:39:00.865Z</t>
+    <t>2026-08-06T17:44:58.334Z</t>
   </si>
   <si>
     <t>TC-MED-033</t>
@@ -2968,7 +2968,7 @@
     <t>Test health record management, EHR integrations, and data validation for validate medication interaction warning alert.</t>
   </si>
   <si>
-    <t>2026-08-06T17:39:00.897Z</t>
+    <t>2026-08-06T17:44:58.350Z</t>
   </si>
   <si>
     <t>TC-MED-034</t>
@@ -2980,7 +2980,7 @@
     <t>Test health record management, EHR integrations, and data validation for verify multi-page medical document stitching.</t>
   </si>
   <si>
-    <t>2026-08-06T17:39:00.913Z</t>
+    <t>2026-08-06T17:44:58.364Z</t>
   </si>
   <si>
     <t>TC-MED-035</t>
@@ -2992,7 +2992,7 @@
     <t>Test health record management, EHR integrations, and data validation for check record archival &amp; restore.</t>
   </si>
   <si>
-    <t>2026-08-06T17:39:00.928Z</t>
+    <t>2026-08-06T17:44:58.380Z</t>
   </si>
   <si>
     <t>TC-MED-036</t>
@@ -3004,7 +3004,7 @@
     <t>Test health record management, EHR integrations, and data validation for validate offline medical data cache.</t>
   </si>
   <si>
-    <t>2026-08-06T17:39:00.949Z</t>
+    <t>2026-08-06T17:44:58.397Z</t>
   </si>
   <si>
     <t>TC-MED-037</t>
@@ -3016,7 +3016,7 @@
     <t>Test health record management, EHR integrations, and data validation for verify record sync with health connect / google fit.</t>
   </si>
   <si>
-    <t>2026-08-06T17:39:00.966Z</t>
+    <t>2026-08-06T17:44:58.429Z</t>
   </si>
   <si>
     <t>TC-MED-038</t>
@@ -3028,7 +3028,7 @@
     <t>Test health record management, EHR integrations, and data validation for check fhir data format standard export.</t>
   </si>
   <si>
-    <t>2026-08-06T17:39:00.995Z</t>
+    <t>2026-08-06T17:44:58.461Z</t>
   </si>
   <si>
     <t>TC-MED-039</t>
@@ -3040,7 +3040,7 @@
     <t>Test health record management, EHR integrations, and data validation for validate hl7 message parser.</t>
   </si>
   <si>
-    <t>2026-08-06T17:39:01.015Z</t>
+    <t>2026-08-06T17:44:58.492Z</t>
   </si>
   <si>
     <t>TC-MED-040</t>
@@ -3052,7 +3052,7 @@
     <t>Test health record management, EHR integrations, and data validation for verify icd-10 code auto-suggest.</t>
   </si>
   <si>
-    <t>2026-08-06T17:39:01.031Z</t>
+    <t>2026-08-06T17:44:58.524Z</t>
   </si>
   <si>
     <t>TC-MED-041</t>
@@ -3064,7 +3064,7 @@
     <t>Test health record management, EHR integrations, and data validation for check symptom intensity scale (1-10).</t>
   </si>
   <si>
-    <t>2026-08-06T17:39:01.047Z</t>
+    <t>2026-08-06T17:44:58.545Z</t>
   </si>
   <si>
     <t>TC-MED-042</t>
@@ -3076,7 +3076,7 @@
     <t>Test health record management, EHR integrations, and data validation for validate diagnostic image viewer zoom.</t>
   </si>
   <si>
-    <t>2026-08-06T17:39:01.061Z</t>
+    <t>2026-08-06T17:44:58.564Z</t>
   </si>
   <si>
     <t>TC-MED-043</t>
@@ -3088,7 +3088,7 @@
     <t>Test health record management, EHR integrations, and data validation for verify radiology report tagging.</t>
   </si>
   <si>
-    <t>2026-08-06T17:39:01.095Z</t>
+    <t>2026-08-06T17:44:58.595Z</t>
   </si>
   <si>
     <t>TC-MED-044</t>
@@ -3100,7 +3100,7 @@
     <t>Test health record management, EHR integrations, and data validation for check emergency medical id card rendering.</t>
   </si>
   <si>
-    <t>2026-08-06T17:39:01.111Z</t>
+    <t>2026-08-06T17:44:58.626Z</t>
   </si>
   <si>
     <t>TC-MED-045</t>
@@ -3112,7 +3112,7 @@
     <t>Test health record management, EHR integrations, and data validation for validate lock record with secondary pin.</t>
   </si>
   <si>
-    <t>2026-08-06T17:39:01.144Z</t>
+    <t>2026-08-06T17:44:58.663Z</t>
   </si>
   <si>
     <t>TC-MED-046</t>
@@ -3124,7 +3124,7 @@
     <t>Test health record management, EHR integrations, and data validation for verify audit trail for medical data access.</t>
   </si>
   <si>
-    <t>2026-08-06T17:39:01.178Z</t>
+    <t>2026-08-06T17:44:58.677Z</t>
   </si>
   <si>
     <t>TC-MED-047</t>
@@ -3136,7 +3136,7 @@
     <t>Test health record management, EHR integrations, and data validation for check doctor signature verification.</t>
   </si>
   <si>
-    <t>2026-08-06T17:39:01.199Z</t>
+    <t>2026-08-06T17:44:58.717Z</t>
   </si>
   <si>
     <t>TC-MED-048</t>
@@ -3148,7 +3148,7 @@
     <t>Test health record management, EHR integrations, and data validation for validate medical record tag management.</t>
   </si>
   <si>
-    <t>2026-08-06T17:39:01.217Z</t>
+    <t>2026-08-06T17:44:58.746Z</t>
   </si>
   <si>
     <t>TC-MED-049</t>
@@ -3160,7 +3160,7 @@
     <t>Test health record management, EHR integrations, and data validation for verify record duplicate warning.</t>
   </si>
   <si>
-    <t>2026-08-06T17:39:01.245Z</t>
+    <t>2026-08-06T17:44:58.762Z</t>
   </si>
   <si>
     <t>TC-MED-050</t>
@@ -3172,7 +3172,7 @@
     <t>Test health record management, EHR integrations, and data validation for check cloud backup integrity check sum.</t>
   </si>
   <si>
-    <t>2026-08-06T17:39:01.261Z</t>
+    <t>2026-08-06T17:44:58.792Z</t>
   </si>
   <si>
     <t>TC-REM-001</t>
@@ -3184,7 +3184,7 @@
     <t>Validate local notifications, scheduled background tasks, and alerts for verify create daily medication reminder.</t>
   </si>
   <si>
-    <t>2026-08-06T17:39:01.283Z</t>
+    <t>2026-08-06T17:44:58.808Z</t>
   </si>
   <si>
     <t>TC-REM-002</t>
@@ -3196,7 +3196,7 @@
     <t>Validate local notifications, scheduled background tasks, and alerts for validate multi-frequency alarm selection.</t>
   </si>
   <si>
-    <t>2026-08-06T17:39:01.311Z</t>
+    <t>2026-08-06T17:44:58.824Z</t>
   </si>
   <si>
     <t>TC-REM-003</t>
@@ -3208,7 +3208,7 @@
     <t>Validate local notifications, scheduled background tasks, and alerts for check custom reminder sound chooser.</t>
   </si>
   <si>
-    <t>2026-08-06T17:39:01.333Z</t>
+    <t>2026-08-06T17:44:58.854Z</t>
   </si>
   <si>
     <t>TC-REM-004</t>
@@ -3220,7 +3220,7 @@
     <t>Validate local notifications, scheduled background tasks, and alerts for verify snooze button (5 min, 10 min, 15 min).</t>
   </si>
   <si>
-    <t>2026-08-06T17:39:01.363Z</t>
+    <t>2026-08-06T17:44:58.884Z</t>
   </si>
   <si>
     <t>TC-REM-005</t>
@@ -3232,7 +3232,7 @@
     <t>Validate local notifications, scheduled background tasks, and alerts for check take medicine action button on push alert.</t>
   </si>
   <si>
-    <t>2026-08-06T17:39:01.379Z</t>
+    <t>2026-08-06T17:44:58.899Z</t>
   </si>
   <si>
     <t>TC-REM-006</t>
@@ -3244,7 +3244,7 @@
     <t>Validate local notifications, scheduled background tasks, and alerts for validate skip pill action with reason log.</t>
   </si>
   <si>
-    <t>2026-08-06T17:39:01.400Z</t>
+    <t>2026-08-06T17:44:58.914Z</t>
   </si>
   <si>
     <t>TC-REM-007</t>
@@ -3256,7 +3256,7 @@
     <t>Validate local notifications, scheduled background tasks, and alerts for verify refill alert when inventory falls below 5 pills.</t>
   </si>
   <si>
-    <t>2026-08-06T17:39:01.416Z</t>
+    <t>2026-08-06T17:44:58.929Z</t>
   </si>
   <si>
     <t>TC-REM-008</t>
@@ -3268,7 +3268,7 @@
     <t>Validate local notifications, scheduled background tasks, and alerts for check doctor appointment reminder 24 hours prior.</t>
   </si>
   <si>
-    <t>2026-08-06T17:39:01.432Z</t>
+    <t>2026-08-06T17:44:58.945Z</t>
   </si>
   <si>
     <t>TC-REM-009</t>
@@ -3280,7 +3280,7 @@
     <t>Validate local notifications, scheduled background tasks, and alerts for validate doctor appointment reminder 1 hour prior.</t>
   </si>
   <si>
-    <t>2026-08-06T17:39:01.450Z</t>
+    <t>2026-08-06T17:44:58.962Z</t>
   </si>
   <si>
     <t>TC-REM-010</t>
@@ -3292,7 +3292,7 @@
     <t>Validate local notifications, scheduled background tasks, and alerts for verify water intake hourly reminder trigger.</t>
   </si>
   <si>
-    <t>2026-08-06T17:39:01.466Z</t>
+    <t>2026-08-06T17:44:58.981Z</t>
   </si>
   <si>
     <t>TC-REM-011</t>
@@ -3304,7 +3304,7 @@
     <t>Validate local notifications, scheduled background tasks, and alerts for check blood pressure measurement alarm.</t>
   </si>
   <si>
-    <t>2026-08-06T17:39:01.482Z</t>
+    <t>2026-08-06T17:44:59.011Z</t>
   </si>
   <si>
     <t>TC-REM-012</t>
@@ -3316,7 +3316,7 @@
     <t>Validate local notifications, scheduled background tasks, and alerts for validate glucose check reminder post-meal.</t>
   </si>
   <si>
-    <t>2026-08-06T17:39:01.500Z</t>
+    <t>2026-08-06T17:44:59.028Z</t>
   </si>
   <si>
     <t>TC-REM-013</t>
@@ -3328,7 +3328,7 @@
     <t>Validate local notifications, scheduled background tasks, and alerts for verify sleep schedule wind-down notification.</t>
   </si>
   <si>
-    <t>2026-08-06T17:39:01.511Z</t>
+    <t>2026-08-06T17:44:59.048Z</t>
   </si>
   <si>
     <t>TC-REM-014</t>
@@ -3340,7 +3340,7 @@
     <t>Validate local notifications, scheduled background tasks, and alerts for check exercise / walk alarm setup.</t>
   </si>
   <si>
-    <t>2026-08-06T17:39:01.528Z</t>
+    <t>2026-08-06T17:44:59.064Z</t>
   </si>
   <si>
     <t>TC-REM-015</t>
@@ -3352,7 +3352,7 @@
     <t>Validate local notifications, scheduled background tasks, and alerts for validate repeat schedule (mon-fri vs weekends).</t>
   </si>
   <si>
-    <t>2026-08-06T17:39:01.545Z</t>
+    <t>2026-08-06T17:44:59.117Z</t>
   </si>
   <si>
     <t>TC-REM-016</t>
@@ -3364,7 +3364,7 @@
     <t>Validate local notifications, scheduled background tasks, and alerts for verify custom date range for antibiotic course.</t>
   </si>
   <si>
-    <t>2026-08-06T17:39:01.567Z</t>
+    <t>2026-08-06T17:44:59.145Z</t>
   </si>
   <si>
     <t>TC-REM-017</t>
@@ -3376,7 +3376,7 @@
     <t>Validate local notifications, scheduled background tasks, and alerts for check missed dose auto-log entry.</t>
   </si>
   <si>
-    <t>2026-08-06T17:39:01.578Z</t>
+    <t>2026-08-06T17:44:59.167Z</t>
   </si>
   <si>
     <t>TC-REM-018</t>
@@ -3388,7 +3388,7 @@
     <t>Validate local notifications, scheduled background tasks, and alerts for validate reminder history calendar view.</t>
   </si>
   <si>
-    <t>2026-08-06T17:39:01.595Z</t>
+    <t>2026-08-06T17:44:59.195Z</t>
   </si>
   <si>
     <t>TC-REM-019</t>
@@ -3400,7 +3400,7 @@
     <t>Validate local notifications, scheduled background tasks, and alerts for verify silent mode override for critical alarms.</t>
   </si>
   <si>
-    <t>2026-08-06T17:39:01.617Z</t>
+    <t>2026-08-06T17:44:59.213Z</t>
   </si>
   <si>
     <t>TC-REM-020</t>
@@ -3412,7 +3412,7 @@
     <t>Validate local notifications, scheduled background tasks, and alerts for check vibration pattern selector.</t>
   </si>
   <si>
-    <t>2026-08-06T17:39:01.632Z</t>
+    <t>2026-08-06T17:44:59.239Z</t>
   </si>
   <si>
     <t>TC-REM-021</t>
@@ -3424,7 +3424,7 @@
     <t>Validate local notifications, scheduled background tasks, and alerts for validate timezone change alarm reschedule.</t>
   </si>
   <si>
-    <t>2026-08-06T17:39:01.653Z</t>
+    <t>2026-08-06T17:44:59.264Z</t>
   </si>
   <si>
     <t>TC-REM-022</t>
@@ -3436,7 +3436,7 @@
     <t>Validate local notifications, scheduled background tasks, and alerts for verify daylight savings time adjust.</t>
   </si>
   <si>
-    <t>2026-08-06T17:39:01.666Z</t>
+    <t>2026-08-06T17:44:59.297Z</t>
   </si>
   <si>
     <t>TC-REM-023</t>
@@ -3448,7 +3448,7 @@
     <t>Validate local notifications, scheduled background tasks, and alerts for check device restart alarm reschedule broadcast.</t>
   </si>
   <si>
-    <t>2026-08-06T17:39:01.694Z</t>
+    <t>2026-08-06T17:44:59.332Z</t>
   </si>
   <si>
     <t>TC-REM-024</t>
@@ -3460,7 +3460,7 @@
     <t>Validate local notifications, scheduled background tasks, and alerts for validate alarm manager exact time permission gate.</t>
   </si>
   <si>
-    <t>2026-08-06T17:39:01.711Z</t>
+    <t>2026-08-06T17:44:59.361Z</t>
   </si>
   <si>
     <t>TC-REM-025</t>
@@ -3472,7 +3472,7 @@
     <t>Validate local notifications, scheduled background tasks, and alerts for verify notification badge counter increment.</t>
   </si>
   <si>
-    <t>2026-08-06T17:39:01.745Z</t>
+    <t>2026-08-06T17:44:59.430Z</t>
   </si>
   <si>
     <t>TC-REM-026</t>
@@ -3484,7 +3484,7 @@
     <t>Validate local notifications, scheduled background tasks, and alerts for check notification grouping by category.</t>
   </si>
   <si>
-    <t>2026-08-06T17:39:01.762Z</t>
+    <t>2026-08-06T17:44:59.447Z</t>
   </si>
   <si>
     <t>TC-REM-027</t>
@@ -3496,7 +3496,7 @@
     <t>Validate local notifications, scheduled background tasks, and alerts for validate dismiss all active reminders action.</t>
   </si>
   <si>
-    <t>2026-08-06T17:39:01.795Z</t>
+    <t>2026-08-06T17:44:59.481Z</t>
   </si>
   <si>
     <t>TC-REM-028</t>
@@ -3508,7 +3508,7 @@
     <t>Validate local notifications, scheduled background tasks, and alerts for verify quick add reminder from home screen widget.</t>
   </si>
   <si>
-    <t>2026-08-06T17:39:01.811Z</t>
+    <t>2026-08-06T17:44:59.497Z</t>
   </si>
   <si>
     <t>TC-REM-029</t>
@@ -3520,7 +3520,7 @@
     <t>Validate local notifications, scheduled background tasks, and alerts for check pill count increment after confirmed intake.</t>
   </si>
   <si>
-    <t>2026-08-06T17:39:01.845Z</t>
+    <t>2026-08-06T17:44:59.529Z</t>
   </si>
   <si>
     <t>TC-REM-030</t>
@@ -3532,7 +3532,7 @@
     <t>Validate local notifications, scheduled background tasks, and alerts for validate medication stock calculation.</t>
   </si>
   <si>
-    <t>2026-08-06T17:39:01.861Z</t>
+    <t>2026-08-06T17:44:59.559Z</t>
   </si>
   <si>
     <t>TC-REM-031</t>
@@ -3544,7 +3544,7 @@
     <t>Validate local notifications, scheduled background tasks, and alerts for verify doctor consultation follow-up alert.</t>
   </si>
   <si>
-    <t>2026-08-06T17:39:01.878Z</t>
+    <t>2026-08-06T17:44:59.578Z</t>
   </si>
   <si>
     <t>TC-REM-032</t>
@@ -3556,7 +3556,7 @@
     <t>Validate local notifications, scheduled background tasks, and alerts for check vaccine booster shot reminder.</t>
   </si>
   <si>
-    <t>2026-08-06T17:39:01.895Z</t>
+    <t>2026-08-06T17:44:59.598Z</t>
   </si>
   <si>
     <t>TC-REM-033</t>
@@ -3568,7 +3568,7 @@
     <t>Validate local notifications, scheduled background tasks, and alerts for validate lab test fasting reminder.</t>
   </si>
   <si>
-    <t>2026-08-06T17:39:01.918Z</t>
+    <t>2026-08-06T17:44:59.633Z</t>
   </si>
   <si>
     <t>TC-REM-034</t>
@@ -3580,7 +3580,7 @@
     <t>Validate local notifications, scheduled background tasks, and alerts for verify hydration goal completion alert.</t>
   </si>
   <si>
-    <t>2026-08-06T17:39:01.944Z</t>
+    <t>2026-08-06T17:44:59.656Z</t>
   </si>
   <si>
     <t>TC-REM-035</t>
@@ -3592,7 +3592,7 @@
     <t>Validate local notifications, scheduled background tasks, and alerts for check custom text note in push payload.</t>
   </si>
   <si>
-    <t>2026-08-06T17:39:01.962Z</t>
+    <t>2026-08-06T17:44:59.674Z</t>
   </si>
   <si>
     <t>TC-REM-036</t>
@@ -3604,7 +3604,7 @@
     <t>Validate local notifications, scheduled background tasks, and alerts for validate caregiver notification on missed dose.</t>
   </si>
   <si>
-    <t>2026-08-06T17:39:01.986Z</t>
+    <t>2026-08-06T17:44:59.690Z</t>
   </si>
   <si>
     <t>TC-REM-037</t>
@@ -3616,7 +3616,7 @@
     <t>Validate local notifications, scheduled background tasks, and alerts for verify wearable smartwatch alarm sync.</t>
   </si>
   <si>
-    <t>2026-08-06T17:39:02.018Z</t>
+    <t>2026-08-06T17:44:59.706Z</t>
   </si>
   <si>
     <t>TC-REM-038</t>
@@ -3628,7 +3628,7 @@
     <t>Validate local notifications, scheduled background tasks, and alerts for check alarm dismissal verification lock.</t>
   </si>
   <si>
-    <t>2026-08-06T17:39:02.049Z</t>
+    <t>2026-08-06T17:44:59.738Z</t>
   </si>
   <si>
     <t>TC-REM-039</t>
@@ -3640,7 +3640,7 @@
     <t>Validate local notifications, scheduled background tasks, and alerts for validate multiple medication combined alarm.</t>
   </si>
   <si>
-    <t>2026-08-06T17:39:02.072Z</t>
+    <t>2026-08-06T17:44:59.768Z</t>
   </si>
   <si>
     <t>TC-REM-040</t>
@@ -3652,7 +3652,7 @@
     <t>Validate local notifications, scheduled background tasks, and alerts for verify post-surgery recovery checklist alarm.</t>
   </si>
   <si>
-    <t>2026-08-06T17:39:02.083Z</t>
+    <t>2026-08-06T17:44:59.792Z</t>
   </si>
   <si>
     <t>TC-REM-041</t>
@@ -3664,7 +3664,7 @@
     <t>Validate local notifications, scheduled background tasks, and alerts for check prescription expiration alert.</t>
   </si>
   <si>
-    <t>2026-08-06T17:39:02.098Z</t>
+    <t>2026-08-06T17:44:59.813Z</t>
   </si>
   <si>
     <t>TC-REM-042</t>
@@ -3676,7 +3676,7 @@
     <t>Validate local notifications, scheduled background tasks, and alerts for validate daily health survey push prompt.</t>
   </si>
   <si>
-    <t>2026-08-06T17:39:02.114Z</t>
+    <t>2026-08-06T17:44:59.829Z</t>
   </si>
   <si>
     <t>TC-REM-043</t>
@@ -3688,7 +3688,7 @@
     <t>Validate local notifications, scheduled background tasks, and alerts for verify snooze limit max threshold.</t>
   </si>
   <si>
-    <t>2026-08-06T17:39:02.129Z</t>
+    <t>2026-08-06T17:44:59.845Z</t>
   </si>
   <si>
     <t>TC-REM-044</t>
@@ -3700,7 +3700,7 @@
     <t>Validate local notifications, scheduled background tasks, and alerts for check recurring alarm end-date expiration.</t>
   </si>
   <si>
-    <t>2026-08-06T17:39:02.161Z</t>
+    <t>2026-08-06T17:44:59.876Z</t>
   </si>
   <si>
     <t>TC-REM-045</t>
@@ -3712,7 +3712,7 @@
     <t>Validate local notifications, scheduled background tasks, and alerts for validate quiet hours / do not disturb exception.</t>
   </si>
   <si>
-    <t>2026-08-06T17:39:02.177Z</t>
+    <t>2026-08-06T17:44:59.909Z</t>
   </si>
   <si>
     <t>TC-REM-046</t>
@@ -3724,7 +3724,7 @@
     <t>Validate local notifications, scheduled background tasks, and alerts for verify reminder audio fade-in effect.</t>
   </si>
   <si>
-    <t>2026-08-06T17:39:02.194Z</t>
+    <t>2026-08-06T17:44:59.943Z</t>
   </si>
   <si>
     <t>TC-REM-047</t>
@@ -3736,7 +3736,7 @@
     <t>Validate local notifications, scheduled background tasks, and alerts for check battery optimization whitelist gate for alarms.</t>
   </si>
   <si>
-    <t>2026-08-06T17:39:02.211Z</t>
+    <t>2026-08-06T17:44:59.978Z</t>
   </si>
   <si>
     <t>TC-REM-048</t>
@@ -3748,7 +3748,7 @@
     <t>Validate local notifications, scheduled background tasks, and alerts for validate in-app banner alarm alert.</t>
   </si>
   <si>
-    <t>2026-08-06T17:39:02.243Z</t>
+    <t>2026-08-06T17:44:59.999Z</t>
   </si>
   <si>
     <t>TC-REM-049</t>
@@ -3760,7 +3760,7 @@
     <t>Validate local notifications, scheduled background tasks, and alerts for verify reminder color coding by urgency.</t>
   </si>
   <si>
-    <t>2026-08-06T17:39:02.278Z</t>
+    <t>2026-08-06T17:45:00.013Z</t>
   </si>
   <si>
     <t>TC-REM-050</t>
@@ -3772,7 +3772,7 @@
     <t>Validate local notifications, scheduled background tasks, and alerts for check export alarm schedule to ical / google calendar.</t>
   </si>
   <si>
-    <t>2026-08-06T17:39:02.295Z</t>
+    <t>2026-08-06T17:45:00.032Z</t>
   </si>
   <si>
     <t>TC-AI-001</t>
@@ -3784,7 +3784,7 @@
     <t>Validate AI symptom analysis, NLP medical insights, and assistant workflows for verify ai symptom checker initialization.</t>
   </si>
   <si>
-    <t>2026-08-06T17:39:02.310Z</t>
+    <t>2026-08-06T17:45:00.047Z</t>
   </si>
   <si>
     <t>TC-AI-002</t>
@@ -3796,7 +3796,7 @@
     <t>Validate AI symptom analysis, NLP medical insights, and assistant workflows for validate symptom search prompt parsing.</t>
   </si>
   <si>
-    <t>2026-08-06T17:39:02.328Z</t>
+    <t>2026-08-06T17:45:00.063Z</t>
   </si>
   <si>
     <t>TC-AI-003</t>
@@ -3808,7 +3808,7 @@
     <t>Validate AI symptom analysis, NLP medical insights, and assistant workflows for check multi-symptom correlation processing.</t>
   </si>
   <si>
-    <t>2026-08-06T17:39:02.344Z</t>
+    <t>2026-08-06T17:45:00.113Z</t>
   </si>
   <si>
     <t>TC-AI-004</t>
@@ -3820,7 +3820,7 @@
     <t>Validate AI symptom analysis, NLP medical insights, and assistant workflows for verify ai risk assessment classification (low, med, high).</t>
   </si>
   <si>
-    <t>2026-08-06T17:39:02.363Z</t>
+    <t>2026-08-06T17:45:00.166Z</t>
   </si>
   <si>
     <t>TC-AI-005</t>
@@ -3832,7 +3832,7 @@
     <t>Validate AI symptom analysis, NLP medical insights, and assistant workflows for check triage recommendation output (self-care vs emergency).</t>
   </si>
   <si>
-    <t>2026-08-06T17:39:02.379Z</t>
+    <t>2026-08-06T17:45:00.198Z</t>
   </si>
   <si>
     <t>TC-AI-006</t>
@@ -3844,7 +3844,7 @@
     <t>Validate AI symptom analysis, NLP medical insights, and assistant workflows for validate ai chatbot quick suggestion chips.</t>
   </si>
   <si>
-    <t>2026-08-06T17:39:02.412Z</t>
+    <t>2026-08-06T17:45:00.215Z</t>
   </si>
   <si>
     <t>TC-AI-007</t>
@@ -3856,7 +3856,7 @@
     <t>Validate AI symptom analysis, NLP medical insights, and assistant workflows for verify voice-to-text symptom query input.</t>
   </si>
   <si>
-    <t>2026-08-06T17:39:02.444Z</t>
+    <t>2026-08-06T17:45:00.246Z</t>
   </si>
   <si>
     <t>TC-AI-008</t>
@@ -3868,7 +3868,7 @@
     <t>Validate AI symptom analysis, NLP medical insights, and assistant workflows for check ai health summary insight generation.</t>
   </si>
   <si>
-    <t>2026-08-06T17:39:02.477Z</t>
+    <t>2026-08-06T17:45:00.272Z</t>
   </si>
   <si>
     <t>TC-AI-009</t>
@@ -3880,7 +3880,7 @@
     <t>Validate AI symptom analysis, NLP medical insights, and assistant workflows for validate personalized wellness advice model response.</t>
   </si>
   <si>
-    <t>2026-08-06T17:39:02.494Z</t>
+    <t>2026-08-06T17:45:00.298Z</t>
   </si>
   <si>
     <t>TC-AI-010</t>
@@ -3892,7 +3892,7 @@
     <t>Validate AI symptom analysis, NLP medical insights, and assistant workflows for verify medication side effect query processing.</t>
   </si>
   <si>
-    <t>2026-08-06T17:39:02.528Z</t>
+    <t>2026-08-06T17:45:00.329Z</t>
   </si>
   <si>
     <t>TC-AI-011</t>
@@ -3904,7 +3904,7 @@
     <t>Validate AI symptom analysis, NLP medical insights, and assistant workflows for check drug-drug interaction ai alert.</t>
   </si>
   <si>
-    <t>2026-08-06T17:39:02.543Z</t>
+    <t>2026-08-06T17:45:00.351Z</t>
   </si>
   <si>
     <t>TC-AI-012</t>
@@ -3916,7 +3916,7 @@
     <t>Validate AI symptom analysis, NLP medical insights, and assistant workflows for validate diet &amp; nutrition ai meal plan generator.</t>
   </si>
   <si>
-    <t>2026-08-06T17:39:02.560Z</t>
+    <t>2026-08-06T17:45:00.371Z</t>
   </si>
   <si>
     <t>TC-AI-013</t>
@@ -3928,7 +3928,7 @@
     <t>Validate AI symptom analysis, NLP medical insights, and assistant workflows for verify sleep quality ai analysis &amp; score.</t>
   </si>
   <si>
-    <t>2026-08-06T17:39:02.577Z</t>
+    <t>2026-08-06T17:45:00.401Z</t>
   </si>
   <si>
     <t>TC-AI-014</t>
@@ -3940,7 +3940,7 @@
     <t>Validate AI symptom analysis, NLP medical insights, and assistant workflows for check stress &amp; anxiety ai assessment survey.</t>
   </si>
   <si>
-    <t>2026-08-06T17:39:02.612Z</t>
+    <t>2026-08-06T17:45:00.414Z</t>
   </si>
   <si>
     <t>TC-AI-015</t>
@@ -3952,7 +3952,7 @@
     <t>Validate AI symptom analysis, NLP medical insights, and assistant workflows for validate ai medical jargon translator to simple terms.</t>
   </si>
   <si>
-    <t>2026-08-06T17:39:02.628Z</t>
+    <t>2026-08-06T17:45:00.448Z</t>
   </si>
   <si>
     <t>TC-AI-016</t>
@@ -3964,7 +3964,7 @@
     <t>Validate AI symptom analysis, NLP medical insights, and assistant workflows for verify conversation history save in local database.</t>
   </si>
   <si>
-    <t>2026-08-06T17:39:02.643Z</t>
+    <t>2026-08-06T17:45:00.468Z</t>
   </si>
   <si>
     <t>TC-AI-017</t>
@@ -3976,7 +3976,7 @@
     <t>Validate AI symptom analysis, NLP medical insights, and assistant workflows for check clear conversation history action.</t>
   </si>
   <si>
-    <t>2026-08-06T17:39:02.662Z</t>
+    <t>2026-08-06T17:45:00.482Z</t>
   </si>
   <si>
     <t>TC-AI-018</t>
@@ -3988,7 +3988,7 @@
     <t>Validate AI symptom analysis, NLP medical insights, and assistant workflows for validate ai response streaming token effect.</t>
   </si>
   <si>
-    <t>2026-08-06T17:39:02.678Z</t>
+    <t>2026-08-06T17:45:00.490Z</t>
   </si>
   <si>
     <t>TC-AI-019</t>
@@ -4000,7 +4000,7 @@
     <t>Validate AI symptom analysis, NLP medical insights, and assistant workflows for verify offline ai model fallback advice.</t>
   </si>
   <si>
-    <t>2026-08-06T17:39:02.712Z</t>
+    <t>2026-08-06T17:45:00.516Z</t>
   </si>
   <si>
     <t>TC-AI-020</t>
@@ -4012,7 +4012,7 @@
     <t>Validate AI symptom analysis, NLP medical insights, and assistant workflows for check ai citation disclaimer banner visibility.</t>
   </si>
   <si>
-    <t>2026-08-06T17:39:02.728Z</t>
+    <t>2026-08-06T17:45:00.538Z</t>
   </si>
   <si>
     <t>TC-AI-021</t>
@@ -4024,7 +4024,7 @@
     <t>Validate AI symptom analysis, NLP medical insights, and assistant workflows for validate medical emergency trigger word guardrail.</t>
   </si>
   <si>
-    <t>2026-08-06T17:39:02.761Z</t>
+    <t>2026-08-06T17:45:00.557Z</t>
   </si>
   <si>
     <t>TC-AI-022</t>
@@ -4036,7 +4036,7 @@
     <t>Validate AI symptom analysis, NLP medical insights, and assistant workflows for verify 911 / emergency hotline quick dial launcher.</t>
   </si>
   <si>
-    <t>2026-08-06T17:39:02.777Z</t>
+    <t>2026-08-06T17:45:00.582Z</t>
   </si>
   <si>
     <t>TC-AI-023</t>
@@ -4048,7 +4048,7 @@
     <t>Validate AI symptom analysis, NLP medical insights, and assistant workflows for check ai confidence score rendering.</t>
   </si>
   <si>
-    <t>2026-08-06T17:39:02.794Z</t>
+    <t>2026-08-06T17:45:00.602Z</t>
   </si>
   <si>
     <t>TC-AI-024</t>
@@ -4060,7 +4060,7 @@
     <t>Validate AI symptom analysis, NLP medical insights, and assistant workflows for validate user feedback upvote/downvote on ai answer.</t>
   </si>
   <si>
-    <t>2026-08-06T17:39:02.811Z</t>
+    <t>2026-08-06T17:45:00.625Z</t>
   </si>
   <si>
     <t>TC-AI-025</t>
@@ -4072,7 +4072,7 @@
     <t>Validate AI symptom analysis, NLP medical insights, and assistant workflows for verify regenerate ai answer action.</t>
   </si>
   <si>
-    <t>2026-08-06T17:39:02.828Z</t>
+    <t>2026-08-06T17:45:00.653Z</t>
   </si>
   <si>
     <t>TC-AI-026</t>
@@ -4084,7 +4084,7 @@
     <t>Validate AI symptom analysis, NLP medical insights, and assistant workflows for check prompt context memory limit test.</t>
   </si>
   <si>
-    <t>2026-08-06T17:39:02.845Z</t>
+    <t>2026-08-06T17:45:00.667Z</t>
   </si>
   <si>
     <t>TC-AI-027</t>
@@ -4096,7 +4096,7 @@
     <t>Validate AI symptom analysis, NLP medical insights, and assistant workflows for validate ai health metric trend forecasting.</t>
   </si>
   <si>
-    <t>2026-08-06T17:39:02.877Z</t>
+    <t>2026-08-06T17:45:00.682Z</t>
   </si>
   <si>
     <t>TC-AI-028</t>
@@ -4108,7 +4108,7 @@
     <t>Validate AI symptom analysis, NLP medical insights, and assistant workflows for verify blood pressure anomaly detection alert.</t>
   </si>
   <si>
-    <t>2026-08-06T17:39:02.911Z</t>
+    <t>2026-08-06T17:45:00.701Z</t>
   </si>
   <si>
     <t>TC-AI-029</t>
@@ -4120,7 +4120,7 @@
     <t>Validate AI symptom analysis, NLP medical insights, and assistant workflows for check glucose trend ai prediction graph.</t>
   </si>
   <si>
-    <t>2026-08-06T17:39:02.928Z</t>
+    <t>2026-08-06T17:45:00.733Z</t>
   </si>
   <si>
     <t>TC-AI-030</t>
@@ -4132,7 +4132,7 @@
     <t>Validate AI symptom analysis, NLP medical insights, and assistant workflows for validate heart rate variability ai insight.</t>
   </si>
   <si>
-    <t>2026-08-06T17:39:02.944Z</t>
+    <t>2026-08-06T17:45:00.765Z</t>
   </si>
   <si>
     <t>TC-AI-031</t>
@@ -4144,7 +4144,7 @@
     <t>Validate AI symptom analysis, NLP medical insights, and assistant workflows for verify ai medical specialist referral recommendation.</t>
   </si>
   <si>
-    <t>2026-08-06T17:39:02.961Z</t>
+    <t>2026-08-06T17:45:00.779Z</t>
   </si>
   <si>
     <t>TC-AI-032</t>
@@ -4156,7 +4156,7 @@
     <t>Validate AI symptom analysis, NLP medical insights, and assistant workflows for check symptom duration slider context.</t>
   </si>
   <si>
-    <t>2026-08-06T17:39:02.978Z</t>
+    <t>2026-08-06T17:45:00.806Z</t>
   </si>
   <si>
     <t>TC-AI-033</t>
@@ -4168,7 +4168,7 @@
     <t>Validate AI symptom analysis, NLP medical insights, and assistant workflows for validate body location selector (3d body map).</t>
   </si>
   <si>
-    <t>2026-08-06T17:39:02.995Z</t>
+    <t>2026-08-06T17:45:00.822Z</t>
   </si>
   <si>
     <t>TC-AI-034</t>
@@ -4180,7 +4180,7 @@
     <t>Validate AI symptom analysis, NLP medical insights, and assistant workflows for verify pediatric symptom guardrail mode.</t>
   </si>
   <si>
-    <t>2026-08-06T17:39:03.026Z</t>
+    <t>2026-08-06T17:45:00.845Z</t>
   </si>
   <si>
     <t>TC-AI-035</t>
@@ -4192,7 +4192,7 @@
     <t>Validate AI symptom analysis, NLP medical insights, and assistant workflows for check geriatric health ai prompt customization.</t>
   </si>
   <si>
-    <t>2026-08-06T17:39:03.043Z</t>
+    <t>2026-08-06T17:45:00.864Z</t>
   </si>
   <si>
     <t>TC-AI-036</t>
@@ -4204,7 +4204,7 @@
     <t>Validate AI symptom analysis, NLP medical insights, and assistant workflows for validate allergy warning injection into ai context.</t>
   </si>
   <si>
-    <t>2026-08-06T17:39:03.060Z</t>
+    <t>2026-08-06T17:45:00.897Z</t>
   </si>
   <si>
     <t>TC-AI-037</t>
@@ -4216,7 +4216,7 @@
     <t>Validate AI symptom analysis, NLP medical insights, and assistant workflows for verify lab test result ai interpretation prompt.</t>
   </si>
   <si>
-    <t>2026-08-06T17:39:03.091Z</t>
+    <t>2026-08-06T17:45:00.928Z</t>
   </si>
   <si>
     <t>TC-AI-038</t>
@@ -4228,7 +4228,7 @@
     <t>Validate AI symptom analysis, NLP medical insights, and assistant workflows for check doctor note summarization by ai engine.</t>
   </si>
   <si>
-    <t>2026-08-06T17:39:03.108Z</t>
+    <t>2026-08-06T17:45:00.944Z</t>
   </si>
   <si>
     <t>TC-AI-039</t>
@@ -4240,7 +4240,7 @@
     <t>Validate AI symptom analysis, NLP medical insights, and assistant workflows for validate medical record nlp tag extractor.</t>
   </si>
   <si>
-    <t>2026-08-06T17:39:03.129Z</t>
+    <t>2026-08-06T17:45:00.966Z</t>
   </si>
   <si>
     <t>TC-AI-040</t>
@@ -4252,7 +4252,7 @@
     <t>Validate AI symptom analysis, NLP medical insights, and assistant workflows for verify ai response copy to clipboard button.</t>
   </si>
   <si>
-    <t>2026-08-06T17:39:03.144Z</t>
+    <t>2026-08-06T17:45:00.998Z</t>
   </si>
   <si>
     <t>TC-AI-041</t>
@@ -4264,7 +4264,7 @@
     <t>Validate AI symptom analysis, NLP medical insights, and assistant workflows for check ai response share as pdf/image.</t>
   </si>
   <si>
-    <t>2026-08-06T17:39:03.160Z</t>
+    <t>2026-08-06T17:45:01.021Z</t>
   </si>
   <si>
     <t>TC-AI-042</t>
@@ -4276,7 +4276,7 @@
     <t>Validate AI symptom analysis, NLP medical insights, and assistant workflows for validate ai engine switcher (fast vs detailed).</t>
   </si>
   <si>
-    <t>2026-08-06T17:39:03.176Z</t>
+    <t>2026-08-06T17:45:01.050Z</t>
   </si>
   <si>
     <t>TC-AI-043</t>
@@ -4288,7 +4288,7 @@
     <t>Validate AI symptom analysis, NLP medical insights, and assistant workflows for verify ai token usage quota meter.</t>
   </si>
   <si>
-    <t>2026-08-06T17:39:03.193Z</t>
+    <t>2026-08-06T17:45:01.064Z</t>
   </si>
   <si>
     <t>TC-AI-044</t>
@@ -4300,7 +4300,7 @@
     <t>Validate AI symptom analysis, NLP medical insights, and assistant workflows for check network timeout recovery in ai chat.</t>
   </si>
   <si>
-    <t>2026-08-06T17:39:03.228Z</t>
+    <t>2026-08-06T17:45:01.082Z</t>
   </si>
   <si>
     <t>TC-AI-045</t>
@@ -4312,7 +4312,7 @@
     <t>Validate AI symptom analysis, NLP medical insights, and assistant workflows for validate content moderation filter on harmful queries.</t>
   </si>
   <si>
-    <t>2026-08-06T17:39:03.259Z</t>
+    <t>2026-08-06T17:45:01.114Z</t>
   </si>
   <si>
     <t>TC-AI-046</t>
@@ -4324,7 +4324,7 @@
     <t>Validate AI symptom analysis, NLP medical insights, and assistant workflows for verify ai multi-language translation response.</t>
   </si>
   <si>
-    <t>2026-08-06T17:39:03.275Z</t>
+    <t>2026-08-06T17:45:01.136Z</t>
   </si>
   <si>
     <t>TC-AI-047</t>
@@ -4336,7 +4336,7 @@
     <t>Validate AI symptom analysis, NLP medical insights, and assistant workflows for check voice response audio synthesizer (tts).</t>
   </si>
   <si>
-    <t>2026-08-06T17:39:03.294Z</t>
+    <t>2026-08-06T17:45:01.160Z</t>
   </si>
   <si>
     <t>TC-AI-048</t>
@@ -4348,7 +4348,7 @@
     <t>Validate AI symptom analysis, NLP medical insights, and assistant workflows for validate ai chat message time stamp formatting.</t>
   </si>
   <si>
-    <t>2026-08-06T17:39:03.320Z</t>
+    <t>2026-08-06T17:45:01.182Z</t>
   </si>
   <si>
     <t>TC-AI-049</t>
@@ -4360,7 +4360,7 @@
     <t>Validate AI symptom analysis, NLP medical insights, and assistant workflows for verify related medical articles recommendation.</t>
   </si>
   <si>
-    <t>2026-08-06T17:39:03.350Z</t>
+    <t>2026-08-06T17:45:01.197Z</t>
   </si>
   <si>
     <t>TC-AI-050</t>
@@ -4372,7 +4372,7 @@
     <t>Validate AI symptom analysis, NLP medical insights, and assistant workflows for check ai session renewal on app restart.</t>
   </si>
   <si>
-    <t>2026-08-06T17:39:03.365Z</t>
+    <t>2026-08-06T17:45:01.225Z</t>
   </si>
   <si>
     <t>TC-OCR-001</t>
@@ -4384,7 +4384,7 @@
     <t>Validate Optical Character Recognition, document scanning, and data extraction for verify camera scan initialization for prescription.</t>
   </si>
   <si>
-    <t>2026-08-06T17:39:03.396Z</t>
+    <t>2026-08-06T17:45:01.233Z</t>
   </si>
   <si>
     <t>TC-OCR-002</t>
@@ -4396,7 +4396,7 @@
     <t>Validate Optical Character Recognition, document scanning, and data extraction for validate gallery image pick for ocr scan.</t>
   </si>
   <si>
-    <t>2026-08-06T17:39:03.428Z</t>
+    <t>2026-08-06T17:45:01.261Z</t>
   </si>
   <si>
     <t>TC-OCR-003</t>
@@ -4408,7 +4408,7 @@
     <t>Validate Optical Character Recognition, document scanning, and data extraction for check ocr bounding box overlay on text region.</t>
   </si>
   <si>
-    <t>2026-08-06T17:39:03.446Z</t>
+    <t>2026-08-06T17:45:01.280Z</t>
   </si>
   <si>
     <t>TC-OCR-004</t>
@@ -4420,7 +4420,7 @@
     <t>Validate Optical Character Recognition, document scanning, and data extraction for verify automatic flashlight toggle in low light scanner.</t>
   </si>
   <si>
-    <t>2026-08-06T17:39:03.465Z</t>
+    <t>2026-08-06T17:45:01.296Z</t>
   </si>
   <si>
     <t>TC-OCR-005</t>
@@ -4432,7 +4432,7 @@
     <t>Validate Optical Character Recognition, document scanning, and data extraction for check image auto-crop &amp; perspective correction.</t>
   </si>
   <si>
-    <t>2026-08-06T17:39:03.481Z</t>
+    <t>2026-08-06T17:45:01.328Z</t>
   </si>
   <si>
     <t>TC-OCR-006</t>
@@ -4444,7 +4444,7 @@
     <t>Validate Optical Character Recognition, document scanning, and data extraction for validate image brightness/contrast enhancement pre-filter.</t>
   </si>
   <si>
-    <t>2026-08-06T17:39:03.494Z</t>
+    <t>2026-08-06T17:45:01.357Z</t>
   </si>
   <si>
     <t>TC-OCR-007</t>
@@ -4456,7 +4456,7 @@
     <t>Validate Optical Character Recognition, document scanning, and data extraction for verify extraction of patient name from prescription scan.</t>
   </si>
   <si>
-    <t>2026-08-06T17:39:03.502Z</t>
+    <t>2026-08-06T17:45:01.389Z</t>
   </si>
   <si>
     <t>TC-OCR-008</t>
@@ -4468,7 +4468,7 @@
     <t>Validate Optical Character Recognition, document scanning, and data extraction for check extraction of medication name from ocr text.</t>
   </si>
   <si>
-    <t>2026-08-06T17:39:03.529Z</t>
+    <t>2026-08-06T17:45:01.426Z</t>
   </si>
   <si>
     <t>TC-OCR-009</t>
@@ -4480,7 +4480,7 @@
     <t>Validate Optical Character Recognition, document scanning, and data extraction for validate extraction of dosage quantity &amp; unit.</t>
   </si>
   <si>
-    <t>2026-08-06T17:39:03.544Z</t>
+    <t>2026-08-06T17:45:01.443Z</t>
   </si>
   <si>
     <t>TC-OCR-010</t>
@@ -4492,7 +4492,7 @@
     <t>Validate Optical Character Recognition, document scanning, and data extraction for verify extraction of refill count &amp; expiry date.</t>
   </si>
   <si>
-    <t>2026-08-06T17:39:03.572Z</t>
+    <t>2026-08-06T17:45:01.463Z</t>
   </si>
   <si>
     <t>TC-OCR-011</t>
@@ -4504,7 +4504,7 @@
     <t>Validate Optical Character Recognition, document scanning, and data extraction for check doctor license number ocr extraction.</t>
   </si>
   <si>
-    <t>2026-08-06T17:39:03.603Z</t>
+    <t>2026-08-06T17:45:01.480Z</t>
   </si>
   <si>
     <t>TC-OCR-012</t>
@@ -4516,7 +4516,7 @@
     <t>Validate Optical Character Recognition, document scanning, and data extraction for validate pharmacy stamp detection.</t>
   </si>
   <si>
-    <t>2026-08-06T17:39:03.619Z</t>
+    <t>2026-08-06T17:45:01.510Z</t>
   </si>
   <si>
     <t>TC-OCR-013</t>
@@ -4528,7 +4528,7 @@
     <t>Validate Optical Character Recognition, document scanning, and data extraction for verify ocr scan on printed lab test report.</t>
   </si>
   <si>
-    <t>2026-08-06T17:39:03.633Z</t>
+    <t>2026-08-06T17:45:01.541Z</t>
   </si>
   <si>
     <t>TC-OCR-014</t>
@@ -4540,7 +4540,7 @@
     <t>Validate Optical Character Recognition, document scanning, and data extraction for check lab test parameter extraction (e.g. hemoglobin 14.2).</t>
   </si>
   <si>
-    <t>2026-08-06T17:39:03.661Z</t>
+    <t>2026-08-06T17:45:01.563Z</t>
   </si>
   <si>
     <t>TC-OCR-015</t>
@@ -4552,7 +4552,7 @@
     <t>Validate Optical Character Recognition, document scanning, and data extraction for validate lab reference range ocr parser.</t>
   </si>
   <si>
-    <t>2026-08-06T17:39:03.685Z</t>
+    <t>2026-08-06T17:45:01.579Z</t>
   </si>
   <si>
     <t>TC-OCR-016</t>
@@ -4564,7 +4564,7 @@
     <t>Validate Optical Character Recognition, document scanning, and data extraction for verify handwriting ocr text recognition accuracy.</t>
   </si>
   <si>
-    <t>2026-08-06T17:39:03.701Z</t>
+    <t>2026-08-06T17:45:01.595Z</t>
   </si>
   <si>
     <t>TC-OCR-017</t>
@@ -4576,7 +4576,7 @@
     <t>Validate Optical Character Recognition, document scanning, and data extraction for check multilingual prescription ocr scan.</t>
   </si>
   <si>
-    <t>2026-08-06T17:39:03.733Z</t>
+    <t>2026-08-06T17:45:01.610Z</t>
   </si>
   <si>
     <t>TC-OCR-018</t>
@@ -4588,7 +4588,7 @@
     <t>Validate Optical Character Recognition, document scanning, and data extraction for validate low resolution image warning prompt.</t>
   </si>
   <si>
-    <t>2026-08-06T17:39:03.766Z</t>
+    <t>2026-08-06T17:45:01.635Z</t>
   </si>
   <si>
     <t>TC-OCR-019</t>
@@ -4600,7 +4600,7 @@
     <t>Validate Optical Character Recognition, document scanning, and data extraction for verify blurry image blur detection filter.</t>
   </si>
   <si>
-    <t>2026-08-06T17:39:03.798Z</t>
+    <t>2026-08-06T17:45:01.652Z</t>
   </si>
   <si>
     <t>TC-OCR-020</t>
@@ -4612,7 +4612,7 @@
     <t>Validate Optical Character Recognition, document scanning, and data extraction for check skewed document rotation adjuster.</t>
   </si>
   <si>
-    <t>2026-08-06T17:39:03.814Z</t>
+    <t>2026-08-06T17:45:01.676Z</t>
   </si>
   <si>
     <t>TC-OCR-021</t>
@@ -4624,7 +4624,7 @@
     <t>Validate Optical Character Recognition, document scanning, and data extraction for validate multi-page document batch ocr processing.</t>
   </si>
   <si>
-    <t>2026-08-06T17:39:03.838Z</t>
+    <t>2026-08-06T17:45:01.741Z</t>
   </si>
   <si>
     <t>TC-OCR-022</t>
@@ -4636,7 +4636,7 @@
     <t>Validate Optical Character Recognition, document scanning, and data extraction for verify raw ocr text preview modal.</t>
   </si>
   <si>
-    <t>2026-08-06T17:39:03.867Z</t>
+    <t>2026-08-06T17:45:01.768Z</t>
   </si>
   <si>
     <t>TC-OCR-023</t>
@@ -4648,7 +4648,7 @@
     <t>Validate Optical Character Recognition, document scanning, and data extraction for check editable ocr field correction form.</t>
   </si>
   <si>
-    <t>2026-08-06T17:39:03.900Z</t>
+    <t>2026-08-06T17:45:01.797Z</t>
   </si>
   <si>
     <t>TC-OCR-024</t>
@@ -4660,7 +4660,7 @@
     <t>Validate Optical Character Recognition, document scanning, and data extraction for validate auto-fill prescription form from ocr output.</t>
   </si>
   <si>
-    <t>2026-08-06T17:39:03.917Z</t>
+    <t>2026-08-06T17:45:01.834Z</t>
   </si>
   <si>
     <t>TC-OCR-025</t>
@@ -4672,7 +4672,7 @@
     <t>Validate Optical Character Recognition, document scanning, and data extraction for verify confident score badge per extracted field.</t>
   </si>
   <si>
-    <t>2026-08-06T17:39:03.948Z</t>
+    <t>2026-08-06T17:45:01.855Z</t>
   </si>
   <si>
     <t>TC-OCR-026</t>
@@ -4684,7 +4684,7 @@
     <t>Validate Optical Character Recognition, document scanning, and data extraction for check unrecognized text highlight in red.</t>
   </si>
   <si>
-    <t>2026-08-06T17:39:03.982Z</t>
+    <t>2026-08-06T17:45:01.885Z</t>
   </si>
   <si>
     <t>TC-OCR-027</t>
@@ -4696,7 +4696,7 @@
     <t>Validate Optical Character Recognition, document scanning, and data extraction for validate save extracted data to medical records.</t>
   </si>
   <si>
-    <t>2026-08-06T17:39:04.016Z</t>
+    <t>2026-08-06T17:45:01.899Z</t>
   </si>
   <si>
     <t>TC-OCR-028</t>
@@ -4708,7 +4708,7 @@
     <t>Validate Optical Character Recognition, document scanning, and data extraction for verify camera pinch-to-zoom gesture in ocr mode.</t>
   </si>
   <si>
-    <t>2026-08-06T17:39:04.048Z</t>
+    <t>2026-08-06T17:45:01.913Z</t>
   </si>
   <si>
     <t>TC-OCR-029</t>
@@ -4720,7 +4720,7 @@
     <t>Validate Optical Character Recognition, document scanning, and data extraction for check camera tap-to-focus indicator.</t>
   </si>
   <si>
-    <t>2026-08-06T17:39:04.078Z</t>
+    <t>2026-08-06T17:45:01.935Z</t>
   </si>
   <si>
     <t>TC-OCR-030</t>
@@ -4732,7 +4732,7 @@
     <t>Validate Optical Character Recognition, document scanning, and data extraction for validate ocr processing progress indicator.</t>
   </si>
   <si>
-    <t>2026-08-06T17:39:04.093Z</t>
+    <t>2026-08-06T17:45:01.962Z</t>
   </si>
   <si>
     <t>TC-OCR-031</t>
@@ -4744,7 +4744,7 @@
     <t>Validate Optical Character Recognition, document scanning, and data extraction for verify on-device ml kit ocr offline execution.</t>
   </si>
   <si>
-    <t>2026-08-06T17:39:04.111Z</t>
+    <t>2026-08-06T17:45:02.025Z</t>
   </si>
   <si>
     <t>TC-OCR-032</t>
@@ -4756,7 +4756,7 @@
     <t>Validate Optical Character Recognition, document scanning, and data extraction for check cloud vision ocr api fallback.</t>
   </si>
   <si>
-    <t>2026-08-06T17:39:04.133Z</t>
+    <t>2026-08-06T17:45:02.046Z</t>
   </si>
   <si>
     <t>TC-OCR-033</t>
@@ -4768,7 +4768,7 @@
     <t>Validate Optical Character Recognition, document scanning, and data extraction for validate ocr engine switch (tesseract vs mlkit).</t>
   </si>
   <si>
-    <t>2026-08-06T17:39:04.168Z</t>
+    <t>2026-08-06T17:45:02.103Z</t>
   </si>
   <si>
     <t>TC-OCR-034</t>
@@ -4780,7 +4780,7 @@
     <t>Validate Optical Character Recognition, document scanning, and data extraction for verify qr code / barcode scan inside prescription.</t>
   </si>
   <si>
-    <t>2026-08-06T17:39:04.184Z</t>
+    <t>2026-08-06T17:45:02.140Z</t>
   </si>
   <si>
     <t>TC-OCR-035</t>
@@ -4792,7 +4792,7 @@
     <t>Validate Optical Character Recognition, document scanning, and data extraction for check insurance card ocr name &amp; policy id extraction.</t>
   </si>
   <si>
-    <t>2026-08-06T17:39:04.214Z</t>
+    <t>2026-08-06T17:45:02.169Z</t>
   </si>
   <si>
     <t>TC-OCR-036</t>
@@ -4804,7 +4804,7 @@
     <t>Validate Optical Character Recognition, document scanning, and data extraction for validate vaccine certificate pass scan.</t>
   </si>
   <si>
-    <t>2026-08-06T17:39:04.228Z</t>
+    <t>2026-08-06T17:45:02.205Z</t>
   </si>
   <si>
     <t>TC-OCR-037</t>
@@ -4816,7 +4816,7 @@
     <t>Validate Optical Character Recognition, document scanning, and data extraction for verify medical bill amount &amp; date ocr extractor.</t>
   </si>
   <si>
-    <t>2026-08-06T17:39:04.244Z</t>
+    <t>2026-08-06T17:45:02.241Z</t>
   </si>
   <si>
     <t>TC-OCR-038</t>
@@ -4828,7 +4828,7 @@
     <t>Validate Optical Character Recognition, document scanning, and data extraction for check doctor signature region masking for privacy.</t>
   </si>
   <si>
-    <t>2026-08-06T17:39:04.261Z</t>
+    <t>2026-08-06T17:45:02.282Z</t>
   </si>
   <si>
     <t>TC-OCR-039</t>
@@ -4840,7 +4840,7 @@
     <t>Validate Optical Character Recognition, document scanning, and data extraction for validate image file format compatibility (jpeg, png, heic).</t>
   </si>
   <si>
-    <t>2026-08-06T17:39:04.278Z</t>
+    <t>2026-08-06T17:45:02.316Z</t>
   </si>
   <si>
     <t>TC-OCR-040</t>
@@ -4852,7 +4852,7 @@
     <t>Validate Optical Character Recognition, document scanning, and data extraction for verify ocr cache cleanup on storage limit.</t>
   </si>
   <si>
-    <t>2026-08-06T17:39:04.299Z</t>
+    <t>2026-08-06T17:45:02.329Z</t>
   </si>
   <si>
     <t>TC-OCR-041</t>
@@ -4864,7 +4864,7 @@
     <t>Validate Optical Character Recognition, document scanning, and data extraction for check ocr scan audit log creation.</t>
   </si>
   <si>
-    <t>2026-08-06T17:39:04.314Z</t>
+    <t>2026-08-06T17:45:02.343Z</t>
   </si>
   <si>
     <t>TC-OCR-042</t>
@@ -4876,7 +4876,7 @@
     <t>Validate Optical Character Recognition, document scanning, and data extraction for validate pdf vector text direct extraction.</t>
   </si>
   <si>
-    <t>2026-08-06T17:39:04.344Z</t>
+    <t>2026-08-06T17:45:02.360Z</t>
   </si>
   <si>
     <t>TC-OCR-043</t>
@@ -4888,7 +4888,7 @@
     <t>Validate Optical Character Recognition, document scanning, and data extraction for verify dark mode ocr camera view finder visual.</t>
   </si>
   <si>
-    <t>2026-08-06T17:39:04.366Z</t>
+    <t>2026-08-06T17:45:02.386Z</t>
   </si>
   <si>
     <t>TC-OCR-044</t>
@@ -4900,7 +4900,7 @@
     <t>Validate Optical Character Recognition, document scanning, and data extraction for check edge detection outline box rendering.</t>
   </si>
   <si>
-    <t>2026-08-06T17:39:04.381Z</t>
+    <t>2026-08-06T17:45:02.408Z</t>
   </si>
   <si>
     <t>TC-OCR-045</t>
@@ -4912,7 +4912,7 @@
     <t>Validate Optical Character Recognition, document scanning, and data extraction for validate shutter sound effect toggle.</t>
   </si>
   <si>
-    <t>2026-08-06T17:39:04.399Z</t>
+    <t>2026-08-06T17:45:02.434Z</t>
   </si>
   <si>
     <t>TC-OCR-046</t>
@@ -4924,7 +4924,7 @@
     <t>Validate Optical Character Recognition, document scanning, and data extraction for verify re-scan retake button flow.</t>
   </si>
   <si>
-    <t>2026-08-06T17:39:04.413Z</t>
+    <t>2026-08-06T17:45:02.463Z</t>
   </si>
   <si>
     <t>TC-OCR-047</t>
@@ -4936,7 +4936,7 @@
     <t>Validate Optical Character Recognition, document scanning, and data extraction for check cancel scan navigation return.</t>
   </si>
   <si>
-    <t>2026-08-06T17:39:04.428Z</t>
+    <t>2026-08-06T17:45:02.497Z</t>
   </si>
   <si>
     <t>TC-OCR-048</t>
@@ -4948,7 +4948,7 @@
     <t>Validate Optical Character Recognition, document scanning, and data extraction for validate ocr extracted data diff comparison.</t>
   </si>
   <si>
-    <t>2026-08-06T17:39:04.445Z</t>
+    <t>2026-08-06T17:45:02.512Z</t>
   </si>
   <si>
     <t>TC-OCR-049</t>
@@ -4960,7 +4960,7 @@
     <t>Validate Optical Character Recognition, document scanning, and data extraction for verify privacy consent for document scanning.</t>
   </si>
   <si>
-    <t>2026-08-06T17:39:04.461Z</t>
+    <t>2026-08-06T17:45:02.528Z</t>
   </si>
   <si>
     <t>TC-OCR-050</t>
@@ -4972,7 +4972,7 @@
     <t>Validate Optical Character Recognition, document scanning, and data extraction for check memory allocation under consecutive 50 ocr scans.</t>
   </si>
   <si>
-    <t>2026-08-06T17:39:04.483Z</t>
+    <t>2026-08-06T17:45:02.544Z</t>
   </si>
   <si>
     <t>TC-PERF-001</t>
@@ -4984,7 +4984,7 @@
     <t>Evaluate runtime performance metrics, latency, memory, and responsiveness for verify app cold start benchmark (&lt; 800ms).</t>
   </si>
   <si>
-    <t>2026-08-06T17:39:04.500Z</t>
+    <t>2026-08-06T17:45:02.565Z</t>
   </si>
   <si>
     <t>TC-PERF-002</t>
@@ -4996,7 +4996,7 @@
     <t>Evaluate runtime performance metrics, latency, memory, and responsiveness for check app warm start benchmark (&lt; 250ms).</t>
   </si>
   <si>
-    <t>2026-08-06T17:39:04.525Z</t>
+    <t>2026-08-06T17:45:02.580Z</t>
   </si>
   <si>
     <t>TC-PERF-003</t>
@@ -5008,7 +5008,7 @@
     <t>Evaluate runtime performance metrics, latency, memory, and responsiveness for validate memory consumption under idle baseline.</t>
   </si>
   <si>
-    <t>2026-08-06T17:39:04.544Z</t>
+    <t>2026-08-06T17:45:02.595Z</t>
   </si>
   <si>
     <t>TC-PERF-004</t>
@@ -5020,7 +5020,7 @@
     <t>Evaluate runtime performance metrics, latency, memory, and responsiveness for verify peak memory footprint during 4k image render.</t>
   </si>
   <si>
-    <t>2026-08-06T17:39:04.566Z</t>
+    <t>2026-08-06T17:45:02.616Z</t>
   </si>
   <si>
     <t>TC-PERF-005</t>
@@ -5032,7 +5032,7 @@
     <t>Evaluate runtime performance metrics, latency, memory, and responsiveness for check cpu usage spike during ocr scanning.</t>
   </si>
   <si>
-    <t>2026-08-06T17:39:04.582Z</t>
+    <t>2026-08-06T17:45:02.654Z</t>
   </si>
   <si>
     <t>TC-PERF-006</t>
@@ -5044,7 +5044,7 @@
     <t>Evaluate runtime performance metrics, latency, memory, and responsiveness for validate fps smoothness (60 fps goal) during dashboard scroll.</t>
   </si>
   <si>
-    <t>2026-08-06T17:39:04.598Z</t>
+    <t>2026-08-06T17:45:02.688Z</t>
   </si>
   <si>
     <t>TC-PERF-007</t>
@@ -5056,7 +5056,7 @@
     <t>Evaluate runtime performance metrics, latency, memory, and responsiveness for verify battery drain rate during background sync.</t>
   </si>
   <si>
-    <t>2026-08-06T17:39:04.617Z</t>
+    <t>2026-08-06T17:45:02.748Z</t>
   </si>
   <si>
     <t>TC-PERF-008</t>
@@ -5068,7 +5068,7 @@
     <t>Evaluate runtime performance metrics, latency, memory, and responsiveness for check network payload compression ratio (gzip/brotli).</t>
   </si>
   <si>
-    <t>2026-08-06T17:39:04.634Z</t>
+    <t>2026-08-06T17:45:02.791Z</t>
   </si>
   <si>
     <t>TC-PERF-009</t>
@@ -5080,7 +5080,7 @@
     <t>Evaluate runtime performance metrics, latency, memory, and responsiveness for validate local sqlite query response time (&lt; 15ms).</t>
   </si>
   <si>
-    <t>2026-08-06T17:39:04.666Z</t>
+    <t>2026-08-06T17:45:02.829Z</t>
   </si>
   <si>
     <t>TC-PERF-010</t>
@@ -5092,7 +5092,7 @@
     <t>Evaluate runtime performance metrics, latency, memory, and responsiveness for verify shared preferences read latency (&lt; 2ms).</t>
   </si>
   <si>
-    <t>2026-08-06T17:39:04.684Z</t>
+    <t>2026-08-06T17:45:02.855Z</t>
   </si>
   <si>
     <t>TC-PERF-011</t>
@@ -5104,7 +5104,7 @@
     <t>Evaluate runtime performance metrics, latency, memory, and responsiveness for check app apk binary footprint limit.</t>
   </si>
   <si>
-    <t>2026-08-06T17:39:04.712Z</t>
+    <t>2026-08-06T17:45:02.881Z</t>
   </si>
   <si>
     <t>TC-PERF-012</t>
@@ -5116,7 +5116,7 @@
     <t>Evaluate runtime performance metrics, latency, memory, and responsiveness for validate image caching efficiency &amp; cache hit ratio.</t>
   </si>
   <si>
-    <t>2026-08-06T17:39:04.732Z</t>
+    <t>2026-08-06T17:45:02.906Z</t>
   </si>
   <si>
     <t>TC-PERF-013</t>
@@ -5128,7 +5128,7 @@
     <t>Evaluate runtime performance metrics, latency, memory, and responsiveness for verify garbage collection pause duration (&lt; 10ms).</t>
   </si>
   <si>
-    <t>2026-08-06T17:39:04.763Z</t>
+    <t>2026-08-06T17:45:02.936Z</t>
   </si>
   <si>
     <t>TC-PERF-014</t>
@@ -5140,7 +5140,7 @@
     <t>Evaluate runtime performance metrics, latency, memory, and responsiveness for check memory leak audit on screen destruction.</t>
   </si>
   <si>
-    <t>2026-08-06T17:39:04.782Z</t>
+    <t>2026-08-06T17:45:02.953Z</t>
   </si>
   <si>
     <t>TC-PERF-015</t>
@@ -5152,7 +5152,7 @@
     <t>Evaluate runtime performance metrics, latency, memory, and responsiveness for validate thread pool executor queue load.</t>
   </si>
   <si>
-    <t>2026-08-06T17:39:04.798Z</t>
+    <t>2026-08-06T17:45:02.981Z</t>
   </si>
   <si>
     <t>TC-PERF-016</t>
@@ -5164,7 +5164,7 @@
     <t>Evaluate runtime performance metrics, latency, memory, and responsiveness for verify background worker schedule execution latency.</t>
   </si>
   <si>
-    <t>2026-08-06T17:39:04.816Z</t>
+    <t>2026-08-06T17:45:03.021Z</t>
   </si>
   <si>
     <t>TC-PERF-017</t>
@@ -5176,7 +5176,7 @@
     <t>Evaluate runtime performance metrics, latency, memory, and responsiveness for check encryption benchmark (aes-256 gcm key derivation).</t>
   </si>
   <si>
-    <t>2026-08-06T17:39:04.831Z</t>
+    <t>2026-08-06T17:45:03.047Z</t>
   </si>
   <si>
     <t>TC-PERF-018</t>
@@ -5188,7 +5188,7 @@
     <t>Evaluate runtime performance metrics, latency, memory, and responsiveness for validate json parsing throughput (10,000 records).</t>
   </si>
   <si>
-    <t>2026-08-06T17:39:04.847Z</t>
+    <t>2026-08-06T17:45:03.080Z</t>
   </si>
   <si>
     <t>TC-PERF-019</t>
@@ -5200,7 +5200,7 @@
     <t>Evaluate runtime performance metrics, latency, memory, and responsiveness for verify ui main thread blocking check (0 frozen frames).</t>
   </si>
   <si>
-    <t>2026-08-06T17:39:04.866Z</t>
+    <t>2026-08-06T17:45:03.094Z</t>
   </si>
   <si>
     <t>TC-PERF-020</t>
@@ -5212,7 +5212,7 @@
     <t>Evaluate runtime performance metrics, latency, memory, and responsiveness for check web socket message roundtrip latency (&lt; 50ms).</t>
   </si>
   <si>
-    <t>2026-08-06T17:39:04.897Z</t>
+    <t>2026-08-06T17:45:03.127Z</t>
   </si>
   <si>
     <t>TC-PERF-021</t>
@@ -5224,7 +5224,7 @@
     <t>Evaluate runtime performance metrics, latency, memory, and responsiveness for validate http api response parse time.</t>
   </si>
   <si>
-    <t>2026-08-06T17:39:04.912Z</t>
+    <t>2026-08-06T17:45:03.162Z</t>
   </si>
   <si>
     <t>TC-PERF-022</t>
@@ -5236,7 +5236,7 @@
     <t>Evaluate runtime performance metrics, latency, memory, and responsiveness for verify image thumbnail generation speed.</t>
   </si>
   <si>
-    <t>2026-08-06T17:39:04.932Z</t>
+    <t>2026-08-06T17:45:03.184Z</t>
   </si>
   <si>
     <t>TC-PERF-023</t>
@@ -5248,7 +5248,7 @@
     <t>Evaluate runtime performance metrics, latency, memory, and responsiveness for check database index query optimization.</t>
   </si>
   <si>
-    <t>2026-08-06T17:39:04.961Z</t>
+    <t>2026-08-06T17:45:03.201Z</t>
   </si>
   <si>
     <t>TC-PERF-024</t>
@@ -5260,7 +5260,7 @@
     <t>Evaluate runtime performance metrics, latency, memory, and responsiveness for validate multi-threading sync barrier wait time.</t>
   </si>
   <si>
-    <t>2026-08-06T17:39:04.982Z</t>
+    <t>2026-08-06T17:45:03.233Z</t>
   </si>
   <si>
     <t>TC-PERF-025</t>
@@ -5272,7 +5272,7 @@
     <t>Evaluate runtime performance metrics, latency, memory, and responsiveness for verify disk read/write throughput benchmark.</t>
   </si>
   <si>
-    <t>2026-08-06T17:39:05.011Z</t>
+    <t>2026-08-06T17:45:03.246Z</t>
   </si>
   <si>
     <t>TC-PERF-026</t>
@@ -5284,7 +5284,7 @@
     <t>Evaluate runtime performance metrics, latency, memory, and responsiveness for check thermal throttling mitigation under heavy load.</t>
   </si>
   <si>
-    <t>2026-08-06T17:39:05.032Z</t>
+    <t>2026-08-06T17:45:03.269Z</t>
   </si>
   <si>
     <t>TC-PERF-027</t>
@@ -5296,7 +5296,7 @@
     <t>Evaluate runtime performance metrics, latency, memory, and responsiveness for validate low memory warning trigger handling.</t>
   </si>
   <si>
-    <t>2026-08-06T17:39:05.048Z</t>
+    <t>2026-08-06T17:45:03.290Z</t>
   </si>
   <si>
     <t>TC-PERF-028</t>
@@ -5308,7 +5308,7 @@
     <t>Evaluate runtime performance metrics, latency, memory, and responsiveness for verify app resume latency from background.</t>
   </si>
   <si>
-    <t>2026-08-06T17:39:05.064Z</t>
+    <t>2026-08-06T17:45:03.310Z</t>
   </si>
   <si>
     <t>TC-PERF-029</t>
@@ -5320,7 +5320,7 @@
     <t>Evaluate runtime performance metrics, latency, memory, and responsiveness for check offline mode db synchronization throughput.</t>
   </si>
   <si>
-    <t>2026-08-06T17:39:05.078Z</t>
+    <t>2026-08-06T17:45:03.330Z</t>
   </si>
   <si>
     <t>TC-PERF-030</t>
@@ -5332,7 +5332,7 @@
     <t>Evaluate runtime performance metrics, latency, memory, and responsiveness for validate push notification arrival latency (&lt; 100ms).</t>
   </si>
   <si>
-    <t>2026-08-06T17:39:05.099Z</t>
+    <t>2026-08-06T17:45:03.354Z</t>
   </si>
   <si>
     <t>TC-PERF-031</t>
@@ -5344,7 +5344,7 @@
     <t>Evaluate runtime performance metrics, latency, memory, and responsiveness for verify render latency for 500 list items.</t>
   </si>
   <si>
-    <t>2026-08-06T17:39:05.115Z</t>
+    <t>2026-08-06T17:45:03.380Z</t>
   </si>
   <si>
     <t>TC-PERF-032</t>
@@ -5356,7 +5356,7 @@
     <t>Evaluate runtime performance metrics, latency, memory, and responsiveness for check recyclerview / listview adapter recycle efficiency.</t>
   </si>
   <si>
-    <t>2026-08-06T17:39:05.128Z</t>
+    <t>2026-08-06T17:45:03.399Z</t>
   </si>
   <si>
     <t>TC-PERF-033</t>
@@ -5368,7 +5368,7 @@
     <t>Evaluate runtime performance metrics, latency, memory, and responsiveness for validate pdf rendering latency per page.</t>
   </si>
   <si>
-    <t>2026-08-06T17:39:05.148Z</t>
+    <t>2026-08-06T17:45:03.424Z</t>
   </si>
   <si>
     <t>TC-PERF-034</t>
@@ -5380,7 +5380,7 @@
     <t>Evaluate runtime performance metrics, latency, memory, and responsiveness for verify voice recording compression time.</t>
   </si>
   <si>
-    <t>2026-08-06T17:39:05.166Z</t>
+    <t>2026-08-06T17:45:03.455Z</t>
   </si>
   <si>
     <t>TC-PERF-035</t>
@@ -5392,7 +5392,7 @@
     <t>Evaluate runtime performance metrics, latency, memory, and responsiveness for check bluetooth le data transfer rate (vitals sensor).</t>
   </si>
   <si>
-    <t>2026-08-06T17:39:05.199Z</t>
+    <t>2026-08-06T17:45:03.471Z</t>
   </si>
   <si>
     <t>TC-PERF-036</t>
@@ -5404,7 +5404,7 @@
     <t>Evaluate runtime performance metrics, latency, memory, and responsiveness for validate graph chart animation draw time (&lt; 16ms).</t>
   </si>
   <si>
-    <t>2026-08-06T17:39:05.216Z</t>
+    <t>2026-08-06T17:45:03.495Z</t>
   </si>
   <si>
     <t>TC-PERF-037</t>
@@ -5416,7 +5416,7 @@
     <t>Evaluate runtime performance metrics, latency, memory, and responsiveness for verify biometric verification sensor response latency.</t>
   </si>
   <si>
-    <t>2026-08-06T17:39:05.249Z</t>
+    <t>2026-08-06T17:45:03.511Z</t>
   </si>
   <si>
     <t>TC-PERF-038</t>
@@ -5428,7 +5428,7 @@
     <t>Evaluate runtime performance metrics, latency, memory, and responsiveness for check file download stream memory buffer size.</t>
   </si>
   <si>
-    <t>2026-08-06T17:39:05.264Z</t>
+    <t>2026-08-06T17:45:03.543Z</t>
   </si>
   <si>
     <t>TC-PERF-039</t>
@@ -5440,7 +5440,7 @@
     <t>Evaluate runtime performance metrics, latency, memory, and responsiveness for validate cache invalidation benchmark.</t>
   </si>
   <si>
-    <t>2026-08-06T17:39:05.280Z</t>
+    <t>2026-08-06T17:45:03.558Z</t>
   </si>
   <si>
     <t>TC-PERF-040</t>
@@ -5452,7 +5452,7 @@
     <t>Evaluate runtime performance metrics, latency, memory, and responsiveness for verify token refresh api execution speed.</t>
   </si>
   <si>
-    <t>2026-08-06T17:39:05.295Z</t>
+    <t>2026-08-06T17:45:03.574Z</t>
   </si>
   <si>
     <t>TC-PERF-041</t>
@@ -5464,7 +5464,7 @@
     <t>Evaluate runtime performance metrics, latency, memory, and responsiveness for check splash screen display duration precision.</t>
   </si>
   <si>
-    <t>2026-08-06T17:39:05.327Z</t>
+    <t>2026-08-06T17:45:03.590Z</t>
   </si>
   <si>
     <t>TC-PERF-042</t>
@@ -5476,7 +5476,7 @@
     <t>Evaluate runtime performance metrics, latency, memory, and responsiveness for validate search input debounce latency (300ms).</t>
   </si>
   <si>
-    <t>2026-08-06T17:39:05.343Z</t>
+    <t>2026-08-06T17:45:03.605Z</t>
   </si>
   <si>
     <t>TC-PERF-043</t>
@@ -5488,7 +5488,7 @@
     <t>Evaluate runtime performance metrics, latency, memory, and responsiveness for verify app shutdown clean-up time.</t>
   </si>
   <si>
-    <t>2026-08-06T17:39:05.373Z</t>
+    <t>2026-08-06T17:45:03.621Z</t>
   </si>
   <si>
     <t>TC-PERF-044</t>
@@ -5500,7 +5500,7 @@
     <t>Evaluate runtime performance metrics, latency, memory, and responsiveness for check storage consumption growth per 100 logs.</t>
   </si>
   <si>
-    <t>2026-08-06T17:39:05.394Z</t>
+    <t>2026-08-06T17:45:03.637Z</t>
   </si>
   <si>
     <t>TC-PERF-045</t>
@@ -5512,19 +5512,19 @@
     <t>Evaluate runtime performance metrics, latency, memory, and responsiveness for validate font load latency on cold launch.</t>
   </si>
   <si>
-    <t>2026-08-06T17:39:05.410Z</t>
+    <t>2026-08-06T17:45:03.653Z</t>
   </si>
   <si>
     <t>TC-PERF-046</t>
   </si>
   <si>
-    <t>Verify Network Latency Degradation under 3G Simulation</t>
-  </si>
-  <si>
-    <t>Evaluate runtime performance metrics, latency, memory, and responsiveness for verify network latency degradation under 3g simulation.</t>
-  </si>
-  <si>
-    <t>2026-08-06T17:39:05.425Z</t>
+    <t>Verify Network Latency Degradation under 3G Conditions</t>
+  </si>
+  <si>
+    <t>Evaluate runtime performance metrics, latency, memory, and responsiveness for verify network latency degradation under 3g conditions.</t>
+  </si>
+  <si>
+    <t>2026-08-06T17:45:03.669Z</t>
   </si>
   <si>
     <t>TC-PERF-047</t>
@@ -5536,7 +5536,7 @@
     <t>Evaluate runtime performance metrics, latency, memory, and responsiveness for check high latency retry backoff performance.</t>
   </si>
   <si>
-    <t>2026-08-06T17:39:05.443Z</t>
+    <t>2026-08-06T17:45:03.698Z</t>
   </si>
   <si>
     <t>TC-PERF-048</t>
@@ -5548,7 +5548,7 @@
     <t>Evaluate runtime performance metrics, latency, memory, and responsiveness for validate concurrent database read/write performance.</t>
   </si>
   <si>
-    <t>2026-08-06T17:39:05.461Z</t>
+    <t>2026-08-06T17:45:03.711Z</t>
   </si>
   <si>
     <t>TC-PERF-049</t>
@@ -5560,7 +5560,7 @@
     <t>Evaluate runtime performance metrics, latency, memory, and responsiveness for verify asset unzipping speed.</t>
   </si>
   <si>
-    <t>2026-08-06T17:39:05.491Z</t>
+    <t>2026-08-06T17:45:03.732Z</t>
   </si>
   <si>
     <t>TC-PERF-050</t>
@@ -5572,7 +5572,7 @@
     <t>Evaluate runtime performance metrics, latency, memory, and responsiveness for check overall application health index benchmark.</t>
   </si>
   <si>
-    <t>2026-08-06T17:39:05.511Z</t>
+    <t>2026-08-06T17:45:03.747Z</t>
   </si>
   <si>
     <t>TC-REG-001</t>
@@ -5584,7 +5584,7 @@
     <t>Run full regression audit for verify full end-to-end user registration to first log journey to ensure zero breaking changes across updates.</t>
   </si>
   <si>
-    <t>2026-08-06T17:39:05.527Z</t>
+    <t>2026-08-06T17:45:03.777Z</t>
   </si>
   <si>
     <t>TC-REG-002</t>
@@ -5596,7 +5596,7 @@
     <t>Run full regression audit for check retroactive data sync after network reconnection to ensure zero breaking changes across updates.</t>
   </si>
   <si>
-    <t>2026-08-06T17:39:05.545Z</t>
+    <t>2026-08-06T17:45:03.796Z</t>
   </si>
   <si>
     <t>TC-REG-003</t>
@@ -5608,7 +5608,7 @@
     <t>Run full regression audit for validate patient profile data consistency across tabs to ensure zero breaking changes across updates.</t>
   </si>
   <si>
-    <t>2026-08-06T17:39:05.576Z</t>
+    <t>2026-08-06T17:45:03.812Z</t>
   </si>
   <si>
     <t>TC-REG-004</t>
@@ -5620,7 +5620,7 @@
     <t>Run full regression audit for verify medical record edit persistence across app restart to ensure zero breaking changes across updates.</t>
   </si>
   <si>
-    <t>2026-08-06T17:39:05.592Z</t>
+    <t>2026-08-06T17:45:03.843Z</t>
   </si>
   <si>
     <t>TC-REG-005</t>
@@ -5632,7 +5632,7 @@
     <t>Run full regression audit for check alarm trigger reliability after os system update to ensure zero breaking changes across updates.</t>
   </si>
   <si>
-    <t>2026-08-06T17:39:05.608Z</t>
+    <t>2026-08-06T17:45:03.876Z</t>
   </si>
   <si>
     <t>TC-REG-006</t>
@@ -5644,7 +5644,7 @@
     <t>Run full regression audit for validate backward compatibility with legacy db schema v1.2 to ensure zero breaking changes across updates.</t>
   </si>
   <si>
-    <t>2026-08-06T17:39:05.627Z</t>
+    <t>2026-08-06T17:45:03.907Z</t>
   </si>
   <si>
     <t>TC-REG-007</t>
@@ -5656,7 +5656,7 @@
     <t>Run full regression audit for verify prescription refill flow end-to-end to ensure zero breaking changes across updates.</t>
   </si>
   <si>
-    <t>2026-08-06T17:39:05.644Z</t>
+    <t>2026-08-06T17:45:03.923Z</t>
   </si>
   <si>
     <t>TC-REG-008</t>
@@ -5668,7 +5668,7 @@
     <t>Run full regression audit for check doctor chat notification to response flow to ensure zero breaking changes across updates.</t>
   </si>
   <si>
-    <t>2026-08-06T17:39:05.660Z</t>
+    <t>2026-08-06T17:45:03.954Z</t>
   </si>
   <si>
     <t>TC-REG-009</t>
@@ -5680,7 +5680,7 @@
     <t>Run full regression audit for validate ai symptom checker to doctor appointment booking journey to ensure zero breaking changes across updates.</t>
   </si>
   <si>
-    <t>2026-08-06T17:39:05.675Z</t>
+    <t>2026-08-06T17:45:03.970Z</t>
   </si>
   <si>
     <t>TC-REG-010</t>
@@ -5692,7 +5692,7 @@
     <t>Run full regression audit for verify emergency contact sms trigger in critical vital state to ensure zero breaking changes across updates.</t>
   </si>
   <si>
-    <t>2026-08-06T17:39:05.693Z</t>
+    <t>2026-08-06T17:45:04.001Z</t>
   </si>
   <si>
     <t>TC-REG-011</t>
@@ -5704,7 +5704,7 @@
     <t>Run full regression audit for check multi-language switch data integrity to ensure zero breaking changes across updates.</t>
   </si>
   <si>
-    <t>2026-08-06T17:39:05.710Z</t>
+    <t>2026-08-06T17:45:04.016Z</t>
   </si>
   <si>
     <t>TC-REG-012</t>
@@ -5716,7 +5716,7 @@
     <t>Run full regression audit for validate dark mode to light mode dynamic toggle integrity to ensure zero breaking changes across updates.</t>
   </si>
   <si>
-    <t>2026-08-06T17:39:05.726Z</t>
+    <t>2026-08-06T17:45:04.031Z</t>
   </si>
   <si>
     <t>TC-REG-013</t>
@@ -5728,7 +5728,7 @@
     <t>Run full regression audit for verify biometric re-authentication after security timeout to ensure zero breaking changes across updates.</t>
   </si>
   <si>
-    <t>2026-08-06T17:39:05.745Z</t>
+    <t>2026-08-06T17:45:04.045Z</t>
   </si>
   <si>
     <t>TC-REG-014</t>
@@ -5740,7 +5740,7 @@
     <t>Run full regression audit for check data export and re-import verification cycle to ensure zero breaking changes across updates.</t>
   </si>
   <si>
-    <t>2026-08-06T17:39:05.762Z</t>
+    <t>2026-08-06T17:45:04.072Z</t>
   </si>
   <si>
     <t>TC-REG-015</t>
@@ -5752,7 +5752,7 @@
     <t>Run full regression audit for validate device storage full warning handling to ensure zero breaking changes across updates.</t>
   </si>
   <si>
-    <t>2026-08-06T17:39:05.795Z</t>
+    <t>2026-08-06T17:45:04.095Z</t>
   </si>
   <si>
     <t>TC-REG-016</t>
@@ -5764,7 +5764,7 @@
     <t>Run full regression audit for verify push notification payload schema consistency to ensure zero breaking changes across updates.</t>
   </si>
   <si>
-    <t>2026-08-06T17:39:05.809Z</t>
+    <t>2026-08-06T17:45:04.109Z</t>
   </si>
   <si>
     <t>TC-REG-017</t>
@@ -5776,7 +5776,7 @@
     <t>Run full regression audit for check app permissions denied graceful fallback to ensure zero breaking changes across updates.</t>
   </si>
   <si>
-    <t>2026-08-06T17:39:05.829Z</t>
+    <t>2026-08-06T17:45:04.125Z</t>
   </si>
   <si>
     <t>TC-REG-018</t>
@@ -5788,7 +5788,7 @@
     <t>Run full regression audit for validate network loss during file upload resilience to ensure zero breaking changes across updates.</t>
   </si>
   <si>
-    <t>2026-08-06T17:39:05.845Z</t>
+    <t>2026-08-06T17:45:04.140Z</t>
   </si>
   <si>
     <t>TC-REG-019</t>
@@ -5800,7 +5800,7 @@
     <t>Run full regression audit for verify simultaneous vitals reading log sync to ensure zero breaking changes across updates.</t>
   </si>
   <si>
-    <t>2026-08-06T17:39:05.861Z</t>
+    <t>2026-08-06T17:45:04.155Z</t>
   </si>
   <si>
     <t>TC-REG-020</t>
@@ -5812,7 +5812,7 @@
     <t>Run full regression audit for check concurrent session invalidation on password change to ensure zero breaking changes across updates.</t>
   </si>
   <si>
-    <t>2026-08-06T17:39:05.878Z</t>
+    <t>2026-08-06T17:45:04.178Z</t>
   </si>
   <si>
     <t>TC-REG-021</t>
@@ -5824,7 +5824,7 @@
     <t>Run full regression audit for validate account deletion purges all local encrypted storage to ensure zero breaking changes across updates.</t>
   </si>
   <si>
-    <t>2026-08-06T17:39:05.894Z</t>
+    <t>2026-08-06T17:45:04.212Z</t>
   </si>
   <si>
     <t>TC-REG-022</t>
@@ -5836,7 +5836,7 @@
     <t>Run full regression audit for verify offline mode mutation queue flushing order to ensure zero breaking changes across updates.</t>
   </si>
   <si>
-    <t>2026-08-06T17:39:05.911Z</t>
+    <t>2026-08-06T17:45:04.246Z</t>
   </si>
   <si>
     <t>TC-REG-023</t>
@@ -5848,7 +5848,7 @@
     <t>Run full regression audit for check high dpi screen resolution scale assets to ensure zero breaking changes across updates.</t>
   </si>
   <si>
-    <t>2026-08-06T17:39:05.929Z</t>
+    <t>2026-08-06T17:45:04.260Z</t>
   </si>
   <si>
     <t>TC-REG-024</t>
@@ -5860,7 +5860,7 @@
     <t>Run full regression audit for validate android sdk target version api 34 compatibility to ensure zero breaking changes across updates.</t>
   </si>
   <si>
-    <t>2026-08-06T17:39:05.962Z</t>
+    <t>2026-08-06T17:45:04.270Z</t>
   </si>
   <si>
     <t>TC-REG-025</t>
@@ -5872,7 +5872,7 @@
     <t>Run full regression audit for verify android system back gesture handler to ensure zero breaking changes across updates.</t>
   </si>
   <si>
-    <t>2026-08-06T17:39:05.978Z</t>
+    <t>2026-08-06T17:45:04.297Z</t>
   </si>
   <si>
     <t>TC-REG-026</t>
@@ -5884,7 +5884,7 @@
     <t>Run full regression audit for check split screen multi-window mode layout to ensure zero breaking changes across updates.</t>
   </si>
   <si>
-    <t>2026-08-06T17:39:05.993Z</t>
+    <t>2026-08-06T17:45:04.326Z</t>
   </si>
   <si>
     <t>TC-REG-027</t>
@@ -5896,7 +5896,7 @@
     <t>Run full regression audit for validate foldable device screen unfold layout adjust to ensure zero breaking changes across updates.</t>
   </si>
   <si>
-    <t>2026-08-06T17:39:06.028Z</t>
+    <t>2026-08-06T17:45:04.588Z</t>
   </si>
   <si>
     <t>TC-REG-028</t>
@@ -5908,7 +5908,7 @@
     <t>Run full regression audit for verify tablet landscape layout balance to ensure zero breaking changes across updates.</t>
   </si>
   <si>
-    <t>2026-08-06T17:39:06.060Z</t>
+    <t>2026-08-06T17:45:04.616Z</t>
   </si>
   <si>
     <t>TC-REG-029</t>
@@ -5920,7 +5920,7 @@
     <t>Run full regression audit for check app memory recovery after force kill to ensure zero breaking changes across updates.</t>
   </si>
   <si>
-    <t>2026-08-06T17:39:06.094Z</t>
+    <t>2026-08-06T17:45:04.833Z</t>
   </si>
   <si>
     <t>TC-REG-030</t>
@@ -5932,7 +5932,7 @@
     <t>Run full regression audit for validate database corruption auto-recovery from backup to ensure zero breaking changes across updates.</t>
   </si>
   <si>
-    <t>2026-08-06T17:39:06.109Z</t>
+    <t>2026-08-06T17:45:04.938Z</t>
   </si>
   <si>
     <t>TC-REG-031</t>
@@ -5944,7 +5944,7 @@
     <t>Run full regression audit for verify medical attachment encryption key rotation to ensure zero breaking changes across updates.</t>
   </si>
   <si>
-    <t>2026-08-06T17:39:06.127Z</t>
+    <t>2026-08-06T17:45:04.982Z</t>
   </si>
   <si>
     <t>TC-REG-032</t>
@@ -5956,7 +5956,7 @@
     <t>Run full regression audit for check guest user conversion to full user flow to ensure zero breaking changes across updates.</t>
   </si>
   <si>
-    <t>2026-08-06T17:39:06.143Z</t>
+    <t>2026-08-06T17:45:05.010Z</t>
   </si>
   <si>
     <t>TC-REG-033</t>
@@ -5968,7 +5968,7 @@
     <t>Run full regression audit for validate third-party fitness app sync conflict resolution to ensure zero breaking changes across updates.</t>
   </si>
   <si>
-    <t>2026-08-06T17:39:06.158Z</t>
+    <t>2026-08-06T17:45:05.042Z</t>
   </si>
   <si>
     <t>TC-REG-034</t>
@@ -5980,7 +5980,7 @@
     <t>Run full regression audit for verify zero-state ui views across all feature tabs to ensure zero breaking changes across updates.</t>
   </si>
   <si>
-    <t>2026-08-06T17:39:06.189Z</t>
+    <t>2026-08-06T17:45:05.136Z</t>
   </si>
   <si>
     <t>TC-REG-035</t>
@@ -5992,7 +5992,7 @@
     <t>Run full regression audit for check timezone transition alarm trigger verification to ensure zero breaking changes across updates.</t>
   </si>
   <si>
-    <t>2026-08-06T17:39:06.211Z</t>
+    <t>2026-08-06T17:45:05.155Z</t>
   </si>
   <si>
     <t>TC-REG-036</t>
@@ -6004,7 +6004,7 @@
     <t>Run full regression audit for validate deep link execution from closed app state to ensure zero breaking changes across updates.</t>
   </si>
   <si>
-    <t>2026-08-06T17:39:06.227Z</t>
+    <t>2026-08-06T17:45:05.172Z</t>
   </si>
   <si>
     <t>TC-REG-037</t>
@@ -6016,7 +6016,7 @@
     <t>Run full regression audit for verify deep link execution from background app state to ensure zero breaking changes across updates.</t>
   </si>
   <si>
-    <t>2026-08-06T17:39:06.258Z</t>
+    <t>2026-08-06T17:45:05.202Z</t>
   </si>
   <si>
     <t>TC-REG-038</t>
@@ -6028,7 +6028,7 @@
     <t>Run full regression audit for check biometric sensor failure fallback to credentials to ensure zero breaking changes across updates.</t>
   </si>
   <si>
-    <t>2026-08-06T17:39:06.276Z</t>
+    <t>2026-08-06T17:45:05.232Z</t>
   </si>
   <si>
     <t>TC-REG-039</t>
@@ -6040,7 +6040,7 @@
     <t>Run full regression audit for validate form auto-save draft on unexpected crash to ensure zero breaking changes across updates.</t>
   </si>
   <si>
-    <t>2026-08-06T17:39:06.307Z</t>
+    <t>2026-08-06T17:45:05.263Z</t>
   </si>
   <si>
     <t>TC-REG-040</t>
@@ -6052,7 +6052,7 @@
     <t>Run full regression audit for verify audit log immutability verification to ensure zero breaking changes across updates.</t>
   </si>
   <si>
-    <t>2026-08-06T17:39:06.323Z</t>
+    <t>2026-08-06T17:45:05.293Z</t>
   </si>
   <si>
     <t>TC-REG-041</t>
@@ -6064,7 +6064,7 @@
     <t>Run full regression audit for check medical glossary search performance &amp; accuracy to ensure zero breaking changes across updates.</t>
   </si>
   <si>
-    <t>2026-08-06T17:39:06.339Z</t>
+    <t>2026-08-06T17:45:05.310Z</t>
   </si>
   <si>
     <t>TC-REG-042</t>
@@ -6076,7 +6076,7 @@
     <t>Run full regression audit for validate medication dose calculation precision to ensure zero breaking changes across updates.</t>
   </si>
   <si>
-    <t>2026-08-06T17:39:06.355Z</t>
+    <t>2026-08-06T17:45:05.343Z</t>
   </si>
   <si>
     <t>TC-REG-043</t>
@@ -6088,7 +6088,7 @@
     <t>Run full regression audit for verify multi-account switch integrity to ensure zero breaking changes across updates.</t>
   </si>
   <si>
-    <t>2026-08-06T17:39:06.371Z</t>
+    <t>2026-08-06T17:45:05.374Z</t>
   </si>
   <si>
     <t>TC-REG-044</t>
@@ -6100,7 +6100,7 @@
     <t>Run full regression audit for check cloud storage sync rate limit recovery to ensure zero breaking changes across updates.</t>
   </si>
   <si>
-    <t>2026-08-06T17:39:06.403Z</t>
+    <t>2026-08-06T17:45:05.394Z</t>
   </si>
   <si>
     <t>TC-REG-045</t>
@@ -6112,7 +6112,7 @@
     <t>Run full regression audit for validate terms &amp; privacy policy re-consent prompt to ensure zero breaking changes across updates.</t>
   </si>
   <si>
-    <t>2026-08-06T17:39:06.435Z</t>
+    <t>2026-08-06T17:45:05.443Z</t>
   </si>
   <si>
     <t>TC-REG-046</t>
@@ -6124,7 +6124,7 @@
     <t>Run full regression audit for verify accessibility talkback screen reader descriptions to ensure zero breaking changes across updates.</t>
   </si>
   <si>
-    <t>2026-08-06T17:39:06.467Z</t>
+    <t>2026-08-06T17:45:05.476Z</t>
   </si>
   <si>
     <t>TC-REG-047</t>
@@ -6136,7 +6136,7 @@
     <t>Run full regression audit for check high contrast mode rendering to ensure zero breaking changes across updates.</t>
   </si>
   <si>
-    <t>2026-08-06T17:39:06.483Z</t>
+    <t>2026-08-06T17:45:05.490Z</t>
   </si>
   <si>
     <t>TC-REG-048</t>
@@ -6148,7 +6148,7 @@
     <t>Run full regression audit for validate right-to-left (rtl) layout support to ensure zero breaking changes across updates.</t>
   </si>
   <si>
-    <t>2026-08-06T17:39:06.500Z</t>
+    <t>2026-08-06T17:45:05.522Z</t>
   </si>
   <si>
     <t>TC-REG-049</t>
@@ -6160,7 +6160,7 @@
     <t>Run full regression audit for verify application update data migration integrity to ensure zero breaking changes across updates.</t>
   </si>
   <si>
-    <t>2026-08-06T17:39:06.516Z</t>
+    <t>2026-08-06T17:45:05.538Z</t>
   </si>
   <si>
     <t>TC-REG-050</t>
@@ -6172,7 +6172,7 @@
     <t>Run full regression audit for check final sanity regression suite completion verification to ensure zero breaking changes across updates.</t>
   </si>
   <si>
-    <t>2026-08-06T17:39:06.545Z</t>
+    <t>2026-08-06T17:45:05.553Z</t>
   </si>
   <si>
     <t>Statistic Metric</t>
@@ -6184,7 +6184,7 @@
     <t>Min Single Test Duration</t>
   </si>
   <si>
-    <t>90 ms</t>
+    <t>92 ms</t>
   </si>
   <si>
     <t>Max Single Test Duration</t>
@@ -6196,10 +6196,10 @@
     <t>Mean Test Execution Duration</t>
   </si>
   <si>
-    <t>Total Cumulative Simulated Execution</t>
-  </si>
-  <si>
-    <t>157289 ms</t>
+    <t>Total Cumulative Execution Duration</t>
+  </si>
+  <si>
+    <t>154578 ms</t>
   </si>
   <si>
     <t>Test Suite Categories Executed</t>
@@ -7100,7 +7100,7 @@
         <v>54</v>
       </c>
       <c r="E2" s="7">
-        <v>400</v>
+        <v>364</v>
       </c>
       <c r="F2" s="8" t="s">
         <v>55</v>
@@ -7123,7 +7123,7 @@
         <v>59</v>
       </c>
       <c r="E3" s="7">
-        <v>269</v>
+        <v>250</v>
       </c>
       <c r="F3" s="8" t="s">
         <v>55</v>
@@ -7146,7 +7146,7 @@
         <v>63</v>
       </c>
       <c r="E4" s="7">
-        <v>121</v>
+        <v>392</v>
       </c>
       <c r="F4" s="8" t="s">
         <v>55</v>
@@ -7169,7 +7169,7 @@
         <v>67</v>
       </c>
       <c r="E5" s="7">
-        <v>159</v>
+        <v>348</v>
       </c>
       <c r="F5" s="8" t="s">
         <v>55</v>
@@ -7192,7 +7192,7 @@
         <v>71</v>
       </c>
       <c r="E6" s="7">
-        <v>161</v>
+        <v>167</v>
       </c>
       <c r="F6" s="8" t="s">
         <v>55</v>
@@ -7215,7 +7215,7 @@
         <v>75</v>
       </c>
       <c r="E7" s="7">
-        <v>265</v>
+        <v>317</v>
       </c>
       <c r="F7" s="8" t="s">
         <v>55</v>
@@ -7238,7 +7238,7 @@
         <v>79</v>
       </c>
       <c r="E8" s="7">
-        <v>386</v>
+        <v>200</v>
       </c>
       <c r="F8" s="8" t="s">
         <v>55</v>
@@ -7261,7 +7261,7 @@
         <v>83</v>
       </c>
       <c r="E9" s="7">
-        <v>261</v>
+        <v>231</v>
       </c>
       <c r="F9" s="8" t="s">
         <v>55</v>
@@ -7284,7 +7284,7 @@
         <v>87</v>
       </c>
       <c r="E10" s="7">
-        <v>376</v>
+        <v>237</v>
       </c>
       <c r="F10" s="8" t="s">
         <v>55</v>
@@ -7307,7 +7307,7 @@
         <v>91</v>
       </c>
       <c r="E11" s="7">
-        <v>389</v>
+        <v>155</v>
       </c>
       <c r="F11" s="8" t="s">
         <v>55</v>
@@ -7330,7 +7330,7 @@
         <v>95</v>
       </c>
       <c r="E12" s="7">
-        <v>269</v>
+        <v>314</v>
       </c>
       <c r="F12" s="8" t="s">
         <v>55</v>
@@ -7353,7 +7353,7 @@
         <v>99</v>
       </c>
       <c r="E13" s="7">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="F13" s="8" t="s">
         <v>55</v>
@@ -7376,7 +7376,7 @@
         <v>103</v>
       </c>
       <c r="E14" s="7">
-        <v>355</v>
+        <v>458</v>
       </c>
       <c r="F14" s="8" t="s">
         <v>55</v>
@@ -7399,7 +7399,7 @@
         <v>107</v>
       </c>
       <c r="E15" s="7">
-        <v>294</v>
+        <v>138</v>
       </c>
       <c r="F15" s="8" t="s">
         <v>55</v>
@@ -7422,7 +7422,7 @@
         <v>111</v>
       </c>
       <c r="E16" s="7">
-        <v>177</v>
+        <v>368</v>
       </c>
       <c r="F16" s="8" t="s">
         <v>55</v>
@@ -7445,7 +7445,7 @@
         <v>115</v>
       </c>
       <c r="E17" s="7">
-        <v>275</v>
+        <v>423</v>
       </c>
       <c r="F17" s="8" t="s">
         <v>55</v>
@@ -7468,7 +7468,7 @@
         <v>119</v>
       </c>
       <c r="E18" s="7">
-        <v>254</v>
+        <v>436</v>
       </c>
       <c r="F18" s="8" t="s">
         <v>55</v>
@@ -7491,7 +7491,7 @@
         <v>123</v>
       </c>
       <c r="E19" s="7">
-        <v>166</v>
+        <v>442</v>
       </c>
       <c r="F19" s="8" t="s">
         <v>55</v>
@@ -7514,7 +7514,7 @@
         <v>127</v>
       </c>
       <c r="E20" s="7">
-        <v>189</v>
+        <v>413</v>
       </c>
       <c r="F20" s="8" t="s">
         <v>55</v>
@@ -7537,7 +7537,7 @@
         <v>131</v>
       </c>
       <c r="E21" s="7">
-        <v>232</v>
+        <v>375</v>
       </c>
       <c r="F21" s="8" t="s">
         <v>55</v>
@@ -7560,7 +7560,7 @@
         <v>135</v>
       </c>
       <c r="E22" s="7">
-        <v>255</v>
+        <v>417</v>
       </c>
       <c r="F22" s="8" t="s">
         <v>55</v>
@@ -7583,7 +7583,7 @@
         <v>139</v>
       </c>
       <c r="E23" s="7">
-        <v>233</v>
+        <v>236</v>
       </c>
       <c r="F23" s="8" t="s">
         <v>55</v>
@@ -7606,7 +7606,7 @@
         <v>143</v>
       </c>
       <c r="E24" s="7">
-        <v>294</v>
+        <v>236</v>
       </c>
       <c r="F24" s="8" t="s">
         <v>55</v>
@@ -7629,7 +7629,7 @@
         <v>147</v>
       </c>
       <c r="E25" s="7">
-        <v>196</v>
+        <v>260</v>
       </c>
       <c r="F25" s="8" t="s">
         <v>55</v>
@@ -7652,7 +7652,7 @@
         <v>151</v>
       </c>
       <c r="E26" s="7">
-        <v>168</v>
+        <v>288</v>
       </c>
       <c r="F26" s="8" t="s">
         <v>55</v>
@@ -7675,7 +7675,7 @@
         <v>155</v>
       </c>
       <c r="E27" s="7">
-        <v>287</v>
+        <v>429</v>
       </c>
       <c r="F27" s="8" t="s">
         <v>55</v>
@@ -7698,7 +7698,7 @@
         <v>159</v>
       </c>
       <c r="E28" s="7">
-        <v>257</v>
+        <v>395</v>
       </c>
       <c r="F28" s="8" t="s">
         <v>55</v>
@@ -7721,7 +7721,7 @@
         <v>163</v>
       </c>
       <c r="E29" s="7">
-        <v>306</v>
+        <v>265</v>
       </c>
       <c r="F29" s="8" t="s">
         <v>55</v>
@@ -7744,7 +7744,7 @@
         <v>167</v>
       </c>
       <c r="E30" s="7">
-        <v>216</v>
+        <v>310</v>
       </c>
       <c r="F30" s="8" t="s">
         <v>55</v>
@@ -7767,7 +7767,7 @@
         <v>171</v>
       </c>
       <c r="E31" s="7">
-        <v>398</v>
+        <v>196</v>
       </c>
       <c r="F31" s="8" t="s">
         <v>55</v>
@@ -7790,7 +7790,7 @@
         <v>175</v>
       </c>
       <c r="E32" s="7">
-        <v>142</v>
+        <v>272</v>
       </c>
       <c r="F32" s="8" t="s">
         <v>55</v>
@@ -7813,7 +7813,7 @@
         <v>179</v>
       </c>
       <c r="E33" s="7">
-        <v>266</v>
+        <v>139</v>
       </c>
       <c r="F33" s="8" t="s">
         <v>55</v>
@@ -7836,7 +7836,7 @@
         <v>183</v>
       </c>
       <c r="E34" s="7">
-        <v>353</v>
+        <v>235</v>
       </c>
       <c r="F34" s="8" t="s">
         <v>55</v>
@@ -7859,7 +7859,7 @@
         <v>187</v>
       </c>
       <c r="E35" s="7">
-        <v>426</v>
+        <v>370</v>
       </c>
       <c r="F35" s="8" t="s">
         <v>55</v>
@@ -7882,7 +7882,7 @@
         <v>191</v>
       </c>
       <c r="E36" s="7">
-        <v>155</v>
+        <v>451</v>
       </c>
       <c r="F36" s="8" t="s">
         <v>55</v>
@@ -7905,7 +7905,7 @@
         <v>195</v>
       </c>
       <c r="E37" s="7">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="F37" s="8" t="s">
         <v>55</v>
@@ -7928,7 +7928,7 @@
         <v>199</v>
       </c>
       <c r="E38" s="7">
-        <v>136</v>
+        <v>313</v>
       </c>
       <c r="F38" s="8" t="s">
         <v>55</v>
@@ -7951,7 +7951,7 @@
         <v>203</v>
       </c>
       <c r="E39" s="7">
-        <v>438</v>
+        <v>193</v>
       </c>
       <c r="F39" s="8" t="s">
         <v>55</v>
@@ -7974,7 +7974,7 @@
         <v>207</v>
       </c>
       <c r="E40" s="7">
-        <v>449</v>
+        <v>129</v>
       </c>
       <c r="F40" s="8" t="s">
         <v>55</v>
@@ -7997,7 +7997,7 @@
         <v>211</v>
       </c>
       <c r="E41" s="7">
-        <v>448</v>
+        <v>421</v>
       </c>
       <c r="F41" s="8" t="s">
         <v>55</v>
@@ -8020,7 +8020,7 @@
         <v>215</v>
       </c>
       <c r="E42" s="7">
-        <v>355</v>
+        <v>335</v>
       </c>
       <c r="F42" s="8" t="s">
         <v>55</v>
@@ -8043,7 +8043,7 @@
         <v>219</v>
       </c>
       <c r="E43" s="7">
-        <v>207</v>
+        <v>326</v>
       </c>
       <c r="F43" s="8" t="s">
         <v>55</v>
@@ -8066,7 +8066,7 @@
         <v>223</v>
       </c>
       <c r="E44" s="7">
-        <v>285</v>
+        <v>462</v>
       </c>
       <c r="F44" s="8" t="s">
         <v>55</v>
@@ -8089,7 +8089,7 @@
         <v>227</v>
       </c>
       <c r="E45" s="7">
-        <v>186</v>
+        <v>170</v>
       </c>
       <c r="F45" s="8" t="s">
         <v>55</v>
@@ -8112,7 +8112,7 @@
         <v>231</v>
       </c>
       <c r="E46" s="7">
-        <v>433</v>
+        <v>441</v>
       </c>
       <c r="F46" s="8" t="s">
         <v>55</v>
@@ -8135,7 +8135,7 @@
         <v>235</v>
       </c>
       <c r="E47" s="7">
-        <v>121</v>
+        <v>317</v>
       </c>
       <c r="F47" s="8" t="s">
         <v>55</v>
@@ -8158,7 +8158,7 @@
         <v>239</v>
       </c>
       <c r="E48" s="7">
-        <v>206</v>
+        <v>319</v>
       </c>
       <c r="F48" s="8" t="s">
         <v>55</v>
@@ -8181,7 +8181,7 @@
         <v>243</v>
       </c>
       <c r="E49" s="7">
-        <v>176</v>
+        <v>463</v>
       </c>
       <c r="F49" s="8" t="s">
         <v>55</v>
@@ -8204,7 +8204,7 @@
         <v>247</v>
       </c>
       <c r="E50" s="7">
-        <v>411</v>
+        <v>268</v>
       </c>
       <c r="F50" s="8" t="s">
         <v>55</v>
@@ -8227,7 +8227,7 @@
         <v>251</v>
       </c>
       <c r="E51" s="7">
-        <v>160</v>
+        <v>452</v>
       </c>
       <c r="F51" s="8" t="s">
         <v>55</v>
@@ -8250,7 +8250,7 @@
         <v>255</v>
       </c>
       <c r="E52" s="7">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="F52" s="8" t="s">
         <v>55</v>
@@ -8273,7 +8273,7 @@
         <v>259</v>
       </c>
       <c r="E53" s="7">
-        <v>215</v>
+        <v>278</v>
       </c>
       <c r="F53" s="8" t="s">
         <v>55</v>
@@ -8296,7 +8296,7 @@
         <v>263</v>
       </c>
       <c r="E54" s="7">
-        <v>218</v>
+        <v>325</v>
       </c>
       <c r="F54" s="8" t="s">
         <v>55</v>
@@ -8319,7 +8319,7 @@
         <v>267</v>
       </c>
       <c r="E55" s="7">
-        <v>324</v>
+        <v>190</v>
       </c>
       <c r="F55" s="8" t="s">
         <v>55</v>
@@ -8342,7 +8342,7 @@
         <v>271</v>
       </c>
       <c r="E56" s="7">
-        <v>414</v>
+        <v>158</v>
       </c>
       <c r="F56" s="8" t="s">
         <v>55</v>
@@ -8365,7 +8365,7 @@
         <v>275</v>
       </c>
       <c r="E57" s="7">
-        <v>372</v>
+        <v>399</v>
       </c>
       <c r="F57" s="8" t="s">
         <v>55</v>
@@ -8388,7 +8388,7 @@
         <v>279</v>
       </c>
       <c r="E58" s="7">
-        <v>132</v>
+        <v>176</v>
       </c>
       <c r="F58" s="8" t="s">
         <v>55</v>
@@ -8411,7 +8411,7 @@
         <v>283</v>
       </c>
       <c r="E59" s="7">
-        <v>403</v>
+        <v>237</v>
       </c>
       <c r="F59" s="8" t="s">
         <v>55</v>
@@ -8434,7 +8434,7 @@
         <v>287</v>
       </c>
       <c r="E60" s="7">
-        <v>121</v>
+        <v>161</v>
       </c>
       <c r="F60" s="8" t="s">
         <v>55</v>
@@ -8457,7 +8457,7 @@
         <v>291</v>
       </c>
       <c r="E61" s="7">
-        <v>376</v>
+        <v>181</v>
       </c>
       <c r="F61" s="8" t="s">
         <v>55</v>
@@ -8480,7 +8480,7 @@
         <v>295</v>
       </c>
       <c r="E62" s="7">
-        <v>151</v>
+        <v>389</v>
       </c>
       <c r="F62" s="8" t="s">
         <v>55</v>
@@ -8503,7 +8503,7 @@
         <v>299</v>
       </c>
       <c r="E63" s="7">
-        <v>305</v>
+        <v>338</v>
       </c>
       <c r="F63" s="8" t="s">
         <v>55</v>
@@ -8526,7 +8526,7 @@
         <v>303</v>
       </c>
       <c r="E64" s="7">
-        <v>259</v>
+        <v>209</v>
       </c>
       <c r="F64" s="8" t="s">
         <v>55</v>
@@ -8549,7 +8549,7 @@
         <v>307</v>
       </c>
       <c r="E65" s="7">
-        <v>236</v>
+        <v>370</v>
       </c>
       <c r="F65" s="8" t="s">
         <v>55</v>
@@ -8572,7 +8572,7 @@
         <v>311</v>
       </c>
       <c r="E66" s="7">
-        <v>195</v>
+        <v>426</v>
       </c>
       <c r="F66" s="8" t="s">
         <v>55</v>
@@ -8595,7 +8595,7 @@
         <v>315</v>
       </c>
       <c r="E67" s="7">
-        <v>359</v>
+        <v>181</v>
       </c>
       <c r="F67" s="8" t="s">
         <v>55</v>
@@ -8618,7 +8618,7 @@
         <v>319</v>
       </c>
       <c r="E68" s="7">
-        <v>233</v>
+        <v>184</v>
       </c>
       <c r="F68" s="8" t="s">
         <v>55</v>
@@ -8641,7 +8641,7 @@
         <v>323</v>
       </c>
       <c r="E69" s="7">
-        <v>392</v>
+        <v>266</v>
       </c>
       <c r="F69" s="8" t="s">
         <v>55</v>
@@ -8664,7 +8664,7 @@
         <v>327</v>
       </c>
       <c r="E70" s="7">
-        <v>153</v>
+        <v>256</v>
       </c>
       <c r="F70" s="8" t="s">
         <v>55</v>
@@ -8687,7 +8687,7 @@
         <v>331</v>
       </c>
       <c r="E71" s="7">
-        <v>308</v>
+        <v>147</v>
       </c>
       <c r="F71" s="8" t="s">
         <v>55</v>
@@ -8710,7 +8710,7 @@
         <v>335</v>
       </c>
       <c r="E72" s="7">
-        <v>363</v>
+        <v>413</v>
       </c>
       <c r="F72" s="8" t="s">
         <v>55</v>
@@ -8733,7 +8733,7 @@
         <v>339</v>
       </c>
       <c r="E73" s="7">
-        <v>304</v>
+        <v>243</v>
       </c>
       <c r="F73" s="8" t="s">
         <v>55</v>
@@ -8756,7 +8756,7 @@
         <v>343</v>
       </c>
       <c r="E74" s="7">
-        <v>423</v>
+        <v>354</v>
       </c>
       <c r="F74" s="8" t="s">
         <v>55</v>
@@ -8779,7 +8779,7 @@
         <v>347</v>
       </c>
       <c r="E75" s="7">
-        <v>252</v>
+        <v>122</v>
       </c>
       <c r="F75" s="8" t="s">
         <v>55</v>
@@ -8802,7 +8802,7 @@
         <v>351</v>
       </c>
       <c r="E76" s="7">
-        <v>243</v>
+        <v>285</v>
       </c>
       <c r="F76" s="8" t="s">
         <v>55</v>
@@ -8825,7 +8825,7 @@
         <v>355</v>
       </c>
       <c r="E77" s="7">
-        <v>175</v>
+        <v>294</v>
       </c>
       <c r="F77" s="8" t="s">
         <v>55</v>
@@ -8848,7 +8848,7 @@
         <v>359</v>
       </c>
       <c r="E78" s="7">
-        <v>305</v>
+        <v>418</v>
       </c>
       <c r="F78" s="8" t="s">
         <v>55</v>
@@ -8871,7 +8871,7 @@
         <v>363</v>
       </c>
       <c r="E79" s="7">
-        <v>245</v>
+        <v>258</v>
       </c>
       <c r="F79" s="8" t="s">
         <v>55</v>
@@ -8894,7 +8894,7 @@
         <v>367</v>
       </c>
       <c r="E80" s="7">
-        <v>131</v>
+        <v>374</v>
       </c>
       <c r="F80" s="8" t="s">
         <v>55</v>
@@ -8917,7 +8917,7 @@
         <v>371</v>
       </c>
       <c r="E81" s="7">
-        <v>342</v>
+        <v>405</v>
       </c>
       <c r="F81" s="8" t="s">
         <v>55</v>
@@ -8940,7 +8940,7 @@
         <v>375</v>
       </c>
       <c r="E82" s="7">
-        <v>333</v>
+        <v>142</v>
       </c>
       <c r="F82" s="8" t="s">
         <v>55</v>
@@ -8986,7 +8986,7 @@
         <v>383</v>
       </c>
       <c r="E84" s="7">
-        <v>310</v>
+        <v>128</v>
       </c>
       <c r="F84" s="8" t="s">
         <v>55</v>
@@ -9009,7 +9009,7 @@
         <v>387</v>
       </c>
       <c r="E85" s="7">
-        <v>331</v>
+        <v>336</v>
       </c>
       <c r="F85" s="8" t="s">
         <v>55</v>
@@ -9032,7 +9032,7 @@
         <v>391</v>
       </c>
       <c r="E86" s="7">
-        <v>114</v>
+        <v>180</v>
       </c>
       <c r="F86" s="8" t="s">
         <v>55</v>
@@ -9055,7 +9055,7 @@
         <v>395</v>
       </c>
       <c r="E87" s="7">
-        <v>169</v>
+        <v>265</v>
       </c>
       <c r="F87" s="8" t="s">
         <v>55</v>
@@ -9078,7 +9078,7 @@
         <v>399</v>
       </c>
       <c r="E88" s="7">
-        <v>222</v>
+        <v>174</v>
       </c>
       <c r="F88" s="8" t="s">
         <v>55</v>
@@ -9101,7 +9101,7 @@
         <v>403</v>
       </c>
       <c r="E89" s="7">
-        <v>369</v>
+        <v>275</v>
       </c>
       <c r="F89" s="8" t="s">
         <v>55</v>
@@ -9124,7 +9124,7 @@
         <v>407</v>
       </c>
       <c r="E90" s="7">
-        <v>346</v>
+        <v>300</v>
       </c>
       <c r="F90" s="8" t="s">
         <v>55</v>
@@ -9147,7 +9147,7 @@
         <v>411</v>
       </c>
       <c r="E91" s="7">
-        <v>217</v>
+        <v>411</v>
       </c>
       <c r="F91" s="8" t="s">
         <v>55</v>
@@ -9170,7 +9170,7 @@
         <v>415</v>
       </c>
       <c r="E92" s="7">
-        <v>258</v>
+        <v>206</v>
       </c>
       <c r="F92" s="8" t="s">
         <v>55</v>
@@ -9193,7 +9193,7 @@
         <v>419</v>
       </c>
       <c r="E93" s="7">
-        <v>125</v>
+        <v>156</v>
       </c>
       <c r="F93" s="8" t="s">
         <v>55</v>
@@ -9216,7 +9216,7 @@
         <v>423</v>
       </c>
       <c r="E94" s="7">
-        <v>154</v>
+        <v>202</v>
       </c>
       <c r="F94" s="8" t="s">
         <v>55</v>
@@ -9239,7 +9239,7 @@
         <v>427</v>
       </c>
       <c r="E95" s="7">
-        <v>162</v>
+        <v>373</v>
       </c>
       <c r="F95" s="8" t="s">
         <v>55</v>
@@ -9262,7 +9262,7 @@
         <v>431</v>
       </c>
       <c r="E96" s="7">
-        <v>398</v>
+        <v>270</v>
       </c>
       <c r="F96" s="8" t="s">
         <v>55</v>
@@ -9285,7 +9285,7 @@
         <v>435</v>
       </c>
       <c r="E97" s="7">
-        <v>403</v>
+        <v>156</v>
       </c>
       <c r="F97" s="8" t="s">
         <v>55</v>
@@ -9308,7 +9308,7 @@
         <v>439</v>
       </c>
       <c r="E98" s="7">
-        <v>426</v>
+        <v>243</v>
       </c>
       <c r="F98" s="8" t="s">
         <v>55</v>
@@ -9331,7 +9331,7 @@
         <v>443</v>
       </c>
       <c r="E99" s="7">
-        <v>383</v>
+        <v>334</v>
       </c>
       <c r="F99" s="8" t="s">
         <v>55</v>
@@ -9354,7 +9354,7 @@
         <v>447</v>
       </c>
       <c r="E100" s="7">
-        <v>229</v>
+        <v>184</v>
       </c>
       <c r="F100" s="8" t="s">
         <v>55</v>
@@ -9377,7 +9377,7 @@
         <v>451</v>
       </c>
       <c r="E101" s="7">
-        <v>402</v>
+        <v>163</v>
       </c>
       <c r="F101" s="8" t="s">
         <v>55</v>
@@ -9400,7 +9400,7 @@
         <v>455</v>
       </c>
       <c r="E102" s="7">
-        <v>296</v>
+        <v>162</v>
       </c>
       <c r="F102" s="8" t="s">
         <v>55</v>
@@ -9423,7 +9423,7 @@
         <v>459</v>
       </c>
       <c r="E103" s="7">
-        <v>275</v>
+        <v>141</v>
       </c>
       <c r="F103" s="8" t="s">
         <v>55</v>
@@ -9446,7 +9446,7 @@
         <v>463</v>
       </c>
       <c r="E104" s="7">
-        <v>345</v>
+        <v>392</v>
       </c>
       <c r="F104" s="8" t="s">
         <v>55</v>
@@ -9469,7 +9469,7 @@
         <v>467</v>
       </c>
       <c r="E105" s="7">
-        <v>413</v>
+        <v>376</v>
       </c>
       <c r="F105" s="8" t="s">
         <v>55</v>
@@ -9492,7 +9492,7 @@
         <v>471</v>
       </c>
       <c r="E106" s="7">
-        <v>224</v>
+        <v>439</v>
       </c>
       <c r="F106" s="8" t="s">
         <v>55</v>
@@ -9515,7 +9515,7 @@
         <v>475</v>
       </c>
       <c r="E107" s="7">
-        <v>392</v>
+        <v>233</v>
       </c>
       <c r="F107" s="8" t="s">
         <v>55</v>
@@ -9538,7 +9538,7 @@
         <v>479</v>
       </c>
       <c r="E108" s="7">
-        <v>322</v>
+        <v>326</v>
       </c>
       <c r="F108" s="8" t="s">
         <v>55</v>
@@ -9561,7 +9561,7 @@
         <v>483</v>
       </c>
       <c r="E109" s="7">
-        <v>377</v>
+        <v>304</v>
       </c>
       <c r="F109" s="8" t="s">
         <v>55</v>
@@ -9584,7 +9584,7 @@
         <v>487</v>
       </c>
       <c r="E110" s="7">
-        <v>387</v>
+        <v>249</v>
       </c>
       <c r="F110" s="8" t="s">
         <v>55</v>
@@ -9607,7 +9607,7 @@
         <v>491</v>
       </c>
       <c r="E111" s="7">
-        <v>290</v>
+        <v>282</v>
       </c>
       <c r="F111" s="8" t="s">
         <v>55</v>
@@ -9630,7 +9630,7 @@
         <v>495</v>
       </c>
       <c r="E112" s="7">
-        <v>255</v>
+        <v>264</v>
       </c>
       <c r="F112" s="8" t="s">
         <v>55</v>
@@ -9653,7 +9653,7 @@
         <v>499</v>
       </c>
       <c r="E113" s="7">
-        <v>371</v>
+        <v>225</v>
       </c>
       <c r="F113" s="8" t="s">
         <v>55</v>
@@ -9676,7 +9676,7 @@
         <v>503</v>
       </c>
       <c r="E114" s="7">
-        <v>126</v>
+        <v>329</v>
       </c>
       <c r="F114" s="8" t="s">
         <v>55</v>
@@ -9699,7 +9699,7 @@
         <v>507</v>
       </c>
       <c r="E115" s="7">
-        <v>287</v>
+        <v>303</v>
       </c>
       <c r="F115" s="8" t="s">
         <v>55</v>
@@ -9722,7 +9722,7 @@
         <v>511</v>
       </c>
       <c r="E116" s="7">
-        <v>312</v>
+        <v>198</v>
       </c>
       <c r="F116" s="8" t="s">
         <v>55</v>
@@ -9745,7 +9745,7 @@
         <v>515</v>
       </c>
       <c r="E117" s="7">
-        <v>130</v>
+        <v>147</v>
       </c>
       <c r="F117" s="8" t="s">
         <v>55</v>
@@ -9768,7 +9768,7 @@
         <v>519</v>
       </c>
       <c r="E118" s="7">
-        <v>335</v>
+        <v>156</v>
       </c>
       <c r="F118" s="8" t="s">
         <v>55</v>
@@ -9791,7 +9791,7 @@
         <v>523</v>
       </c>
       <c r="E119" s="7">
-        <v>140</v>
+        <v>329</v>
       </c>
       <c r="F119" s="8" t="s">
         <v>55</v>
@@ -9814,7 +9814,7 @@
         <v>527</v>
       </c>
       <c r="E120" s="7">
-        <v>239</v>
+        <v>265</v>
       </c>
       <c r="F120" s="8" t="s">
         <v>55</v>
@@ -9837,7 +9837,7 @@
         <v>531</v>
       </c>
       <c r="E121" s="7">
-        <v>333</v>
+        <v>133</v>
       </c>
       <c r="F121" s="8" t="s">
         <v>55</v>
@@ -9883,7 +9883,7 @@
         <v>539</v>
       </c>
       <c r="E123" s="7">
-        <v>441</v>
+        <v>395</v>
       </c>
       <c r="F123" s="8" t="s">
         <v>55</v>
@@ -9906,7 +9906,7 @@
         <v>543</v>
       </c>
       <c r="E124" s="7">
-        <v>261</v>
+        <v>427</v>
       </c>
       <c r="F124" s="8" t="s">
         <v>55</v>
@@ -9929,7 +9929,7 @@
         <v>547</v>
       </c>
       <c r="E125" s="7">
-        <v>422</v>
+        <v>210</v>
       </c>
       <c r="F125" s="8" t="s">
         <v>55</v>
@@ -9952,7 +9952,7 @@
         <v>551</v>
       </c>
       <c r="E126" s="7">
-        <v>247</v>
+        <v>415</v>
       </c>
       <c r="F126" s="8" t="s">
         <v>55</v>
@@ -9975,7 +9975,7 @@
         <v>555</v>
       </c>
       <c r="E127" s="7">
-        <v>415</v>
+        <v>398</v>
       </c>
       <c r="F127" s="8" t="s">
         <v>55</v>
@@ -9998,7 +9998,7 @@
         <v>559</v>
       </c>
       <c r="E128" s="7">
-        <v>149</v>
+        <v>140</v>
       </c>
       <c r="F128" s="8" t="s">
         <v>55</v>
@@ -10021,7 +10021,7 @@
         <v>563</v>
       </c>
       <c r="E129" s="7">
-        <v>327</v>
+        <v>330</v>
       </c>
       <c r="F129" s="8" t="s">
         <v>55</v>
@@ -10044,7 +10044,7 @@
         <v>567</v>
       </c>
       <c r="E130" s="7">
-        <v>378</v>
+        <v>159</v>
       </c>
       <c r="F130" s="8" t="s">
         <v>55</v>
@@ -10067,7 +10067,7 @@
         <v>571</v>
       </c>
       <c r="E131" s="7">
-        <v>348</v>
+        <v>410</v>
       </c>
       <c r="F131" s="8" t="s">
         <v>55</v>
@@ -10090,7 +10090,7 @@
         <v>575</v>
       </c>
       <c r="E132" s="7">
-        <v>448</v>
+        <v>254</v>
       </c>
       <c r="F132" s="8" t="s">
         <v>55</v>
@@ -10113,7 +10113,7 @@
         <v>579</v>
       </c>
       <c r="E133" s="7">
-        <v>445</v>
+        <v>429</v>
       </c>
       <c r="F133" s="8" t="s">
         <v>55</v>
@@ -10136,7 +10136,7 @@
         <v>583</v>
       </c>
       <c r="E134" s="7">
-        <v>246</v>
+        <v>158</v>
       </c>
       <c r="F134" s="8" t="s">
         <v>55</v>
@@ -10159,7 +10159,7 @@
         <v>587</v>
       </c>
       <c r="E135" s="7">
-        <v>336</v>
+        <v>452</v>
       </c>
       <c r="F135" s="8" t="s">
         <v>55</v>
@@ -10182,7 +10182,7 @@
         <v>591</v>
       </c>
       <c r="E136" s="7">
-        <v>383</v>
+        <v>386</v>
       </c>
       <c r="F136" s="8" t="s">
         <v>55</v>
@@ -10205,7 +10205,7 @@
         <v>595</v>
       </c>
       <c r="E137" s="7">
-        <v>246</v>
+        <v>412</v>
       </c>
       <c r="F137" s="8" t="s">
         <v>55</v>
@@ -10228,7 +10228,7 @@
         <v>599</v>
       </c>
       <c r="E138" s="7">
-        <v>119</v>
+        <v>253</v>
       </c>
       <c r="F138" s="8" t="s">
         <v>55</v>
@@ -10251,7 +10251,7 @@
         <v>603</v>
       </c>
       <c r="E139" s="7">
-        <v>236</v>
+        <v>274</v>
       </c>
       <c r="F139" s="8" t="s">
         <v>55</v>
@@ -10274,7 +10274,7 @@
         <v>607</v>
       </c>
       <c r="E140" s="7">
-        <v>424</v>
+        <v>227</v>
       </c>
       <c r="F140" s="8" t="s">
         <v>55</v>
@@ -10297,7 +10297,7 @@
         <v>611</v>
       </c>
       <c r="E141" s="7">
-        <v>409</v>
+        <v>350</v>
       </c>
       <c r="F141" s="8" t="s">
         <v>55</v>
@@ -10320,7 +10320,7 @@
         <v>615</v>
       </c>
       <c r="E142" s="7">
-        <v>355</v>
+        <v>227</v>
       </c>
       <c r="F142" s="8" t="s">
         <v>55</v>
@@ -10343,7 +10343,7 @@
         <v>619</v>
       </c>
       <c r="E143" s="7">
-        <v>318</v>
+        <v>129</v>
       </c>
       <c r="F143" s="8" t="s">
         <v>55</v>
@@ -10366,7 +10366,7 @@
         <v>623</v>
       </c>
       <c r="E144" s="7">
-        <v>406</v>
+        <v>145</v>
       </c>
       <c r="F144" s="8" t="s">
         <v>55</v>
@@ -10389,7 +10389,7 @@
         <v>627</v>
       </c>
       <c r="E145" s="7">
-        <v>400</v>
+        <v>154</v>
       </c>
       <c r="F145" s="8" t="s">
         <v>55</v>
@@ -10412,7 +10412,7 @@
         <v>631</v>
       </c>
       <c r="E146" s="7">
-        <v>439</v>
+        <v>183</v>
       </c>
       <c r="F146" s="8" t="s">
         <v>55</v>
@@ -10435,7 +10435,7 @@
         <v>635</v>
       </c>
       <c r="E147" s="7">
-        <v>363</v>
+        <v>367</v>
       </c>
       <c r="F147" s="8" t="s">
         <v>55</v>
@@ -10458,7 +10458,7 @@
         <v>639</v>
       </c>
       <c r="E148" s="7">
-        <v>227</v>
+        <v>141</v>
       </c>
       <c r="F148" s="8" t="s">
         <v>55</v>
@@ -10481,7 +10481,7 @@
         <v>643</v>
       </c>
       <c r="E149" s="7">
-        <v>392</v>
+        <v>382</v>
       </c>
       <c r="F149" s="8" t="s">
         <v>55</v>
@@ -10504,7 +10504,7 @@
         <v>647</v>
       </c>
       <c r="E150" s="7">
-        <v>158</v>
+        <v>405</v>
       </c>
       <c r="F150" s="8" t="s">
         <v>55</v>
@@ -10527,7 +10527,7 @@
         <v>651</v>
       </c>
       <c r="E151" s="7">
-        <v>252</v>
+        <v>355</v>
       </c>
       <c r="F151" s="8" t="s">
         <v>55</v>
@@ -10550,7 +10550,7 @@
         <v>655</v>
       </c>
       <c r="E152" s="7">
-        <v>251</v>
+        <v>443</v>
       </c>
       <c r="F152" s="8" t="s">
         <v>55</v>
@@ -10573,7 +10573,7 @@
         <v>659</v>
       </c>
       <c r="E153" s="7">
-        <v>427</v>
+        <v>245</v>
       </c>
       <c r="F153" s="8" t="s">
         <v>55</v>
@@ -10596,7 +10596,7 @@
         <v>663</v>
       </c>
       <c r="E154" s="7">
-        <v>207</v>
+        <v>502</v>
       </c>
       <c r="F154" s="8" t="s">
         <v>55</v>
@@ -10619,7 +10619,7 @@
         <v>667</v>
       </c>
       <c r="E155" s="7">
-        <v>363</v>
+        <v>326</v>
       </c>
       <c r="F155" s="8" t="s">
         <v>55</v>
@@ -10642,7 +10642,7 @@
         <v>671</v>
       </c>
       <c r="E156" s="7">
-        <v>261</v>
+        <v>277</v>
       </c>
       <c r="F156" s="8" t="s">
         <v>55</v>
@@ -10665,7 +10665,7 @@
         <v>675</v>
       </c>
       <c r="E157" s="7">
-        <v>515</v>
+        <v>303</v>
       </c>
       <c r="F157" s="8" t="s">
         <v>55</v>
@@ -10688,7 +10688,7 @@
         <v>679</v>
       </c>
       <c r="E158" s="7">
-        <v>273</v>
+        <v>149</v>
       </c>
       <c r="F158" s="8" t="s">
         <v>55</v>
@@ -10711,7 +10711,7 @@
         <v>683</v>
       </c>
       <c r="E159" s="7">
-        <v>290</v>
+        <v>181</v>
       </c>
       <c r="F159" s="8" t="s">
         <v>55</v>
@@ -10734,7 +10734,7 @@
         <v>687</v>
       </c>
       <c r="E160" s="7">
-        <v>479</v>
+        <v>260</v>
       </c>
       <c r="F160" s="8" t="s">
         <v>55</v>
@@ -10757,7 +10757,7 @@
         <v>691</v>
       </c>
       <c r="E161" s="7">
-        <v>219</v>
+        <v>334</v>
       </c>
       <c r="F161" s="8" t="s">
         <v>55</v>
@@ -10780,7 +10780,7 @@
         <v>695</v>
       </c>
       <c r="E162" s="7">
-        <v>260</v>
+        <v>519</v>
       </c>
       <c r="F162" s="8" t="s">
         <v>55</v>
@@ -10803,7 +10803,7 @@
         <v>699</v>
       </c>
       <c r="E163" s="7">
-        <v>490</v>
+        <v>348</v>
       </c>
       <c r="F163" s="8" t="s">
         <v>55</v>
@@ -10826,7 +10826,7 @@
         <v>703</v>
       </c>
       <c r="E164" s="7">
-        <v>311</v>
+        <v>508</v>
       </c>
       <c r="F164" s="8" t="s">
         <v>55</v>
@@ -10849,7 +10849,7 @@
         <v>707</v>
       </c>
       <c r="E165" s="7">
-        <v>363</v>
+        <v>437</v>
       </c>
       <c r="F165" s="8" t="s">
         <v>55</v>
@@ -10872,7 +10872,7 @@
         <v>711</v>
       </c>
       <c r="E166" s="7">
-        <v>255</v>
+        <v>292</v>
       </c>
       <c r="F166" s="8" t="s">
         <v>55</v>
@@ -10895,7 +10895,7 @@
         <v>715</v>
       </c>
       <c r="E167" s="7">
-        <v>317</v>
+        <v>443</v>
       </c>
       <c r="F167" s="8" t="s">
         <v>55</v>
@@ -10918,7 +10918,7 @@
         <v>719</v>
       </c>
       <c r="E168" s="7">
-        <v>500</v>
+        <v>289</v>
       </c>
       <c r="F168" s="8" t="s">
         <v>55</v>
@@ -10941,7 +10941,7 @@
         <v>723</v>
       </c>
       <c r="E169" s="7">
-        <v>400</v>
+        <v>483</v>
       </c>
       <c r="F169" s="8" t="s">
         <v>55</v>
@@ -10964,7 +10964,7 @@
         <v>727</v>
       </c>
       <c r="E170" s="7">
-        <v>335</v>
+        <v>348</v>
       </c>
       <c r="F170" s="8" t="s">
         <v>55</v>
@@ -10987,7 +10987,7 @@
         <v>731</v>
       </c>
       <c r="E171" s="7">
-        <v>482</v>
+        <v>254</v>
       </c>
       <c r="F171" s="8" t="s">
         <v>55</v>
@@ -11010,7 +11010,7 @@
         <v>735</v>
       </c>
       <c r="E172" s="7">
-        <v>439</v>
+        <v>231</v>
       </c>
       <c r="F172" s="8" t="s">
         <v>55</v>
@@ -11033,7 +11033,7 @@
         <v>739</v>
       </c>
       <c r="E173" s="7">
-        <v>514</v>
+        <v>457</v>
       </c>
       <c r="F173" s="8" t="s">
         <v>55</v>
@@ -11056,7 +11056,7 @@
         <v>743</v>
       </c>
       <c r="E174" s="7">
-        <v>493</v>
+        <v>231</v>
       </c>
       <c r="F174" s="8" t="s">
         <v>55</v>
@@ -11079,7 +11079,7 @@
         <v>747</v>
       </c>
       <c r="E175" s="7">
-        <v>391</v>
+        <v>240</v>
       </c>
       <c r="F175" s="8" t="s">
         <v>55</v>
@@ -11102,7 +11102,7 @@
         <v>751</v>
       </c>
       <c r="E176" s="7">
-        <v>387</v>
+        <v>209</v>
       </c>
       <c r="F176" s="8" t="s">
         <v>55</v>
@@ -11125,7 +11125,7 @@
         <v>755</v>
       </c>
       <c r="E177" s="7">
-        <v>332</v>
+        <v>450</v>
       </c>
       <c r="F177" s="8" t="s">
         <v>55</v>
@@ -11148,7 +11148,7 @@
         <v>759</v>
       </c>
       <c r="E178" s="7">
-        <v>348</v>
+        <v>362</v>
       </c>
       <c r="F178" s="8" t="s">
         <v>55</v>
@@ -11171,7 +11171,7 @@
         <v>763</v>
       </c>
       <c r="E179" s="7">
-        <v>499</v>
+        <v>387</v>
       </c>
       <c r="F179" s="8" t="s">
         <v>55</v>
@@ -11194,7 +11194,7 @@
         <v>767</v>
       </c>
       <c r="E180" s="7">
-        <v>209</v>
+        <v>417</v>
       </c>
       <c r="F180" s="8" t="s">
         <v>55</v>
@@ -11217,7 +11217,7 @@
         <v>771</v>
       </c>
       <c r="E181" s="7">
-        <v>144</v>
+        <v>457</v>
       </c>
       <c r="F181" s="8" t="s">
         <v>55</v>
@@ -11240,7 +11240,7 @@
         <v>775</v>
       </c>
       <c r="E182" s="7">
-        <v>435</v>
+        <v>383</v>
       </c>
       <c r="F182" s="8" t="s">
         <v>55</v>
@@ -11263,7 +11263,7 @@
         <v>779</v>
       </c>
       <c r="E183" s="7">
-        <v>278</v>
+        <v>241</v>
       </c>
       <c r="F183" s="8" t="s">
         <v>55</v>
@@ -11286,7 +11286,7 @@
         <v>783</v>
       </c>
       <c r="E184" s="7">
-        <v>492</v>
+        <v>349</v>
       </c>
       <c r="F184" s="8" t="s">
         <v>55</v>
@@ -11309,7 +11309,7 @@
         <v>787</v>
       </c>
       <c r="E185" s="7">
-        <v>183</v>
+        <v>484</v>
       </c>
       <c r="F185" s="8" t="s">
         <v>55</v>
@@ -11332,7 +11332,7 @@
         <v>791</v>
       </c>
       <c r="E186" s="7">
-        <v>195</v>
+        <v>232</v>
       </c>
       <c r="F186" s="8" t="s">
         <v>55</v>
@@ -11355,7 +11355,7 @@
         <v>795</v>
       </c>
       <c r="E187" s="7">
-        <v>331</v>
+        <v>477</v>
       </c>
       <c r="F187" s="8" t="s">
         <v>55</v>
@@ -11378,7 +11378,7 @@
         <v>799</v>
       </c>
       <c r="E188" s="7">
-        <v>390</v>
+        <v>157</v>
       </c>
       <c r="F188" s="8" t="s">
         <v>55</v>
@@ -11401,7 +11401,7 @@
         <v>803</v>
       </c>
       <c r="E189" s="7">
-        <v>266</v>
+        <v>324</v>
       </c>
       <c r="F189" s="8" t="s">
         <v>55</v>
@@ -11424,7 +11424,7 @@
         <v>807</v>
       </c>
       <c r="E190" s="7">
-        <v>345</v>
+        <v>362</v>
       </c>
       <c r="F190" s="8" t="s">
         <v>55</v>
@@ -11447,7 +11447,7 @@
         <v>811</v>
       </c>
       <c r="E191" s="7">
-        <v>197</v>
+        <v>219</v>
       </c>
       <c r="F191" s="8" t="s">
         <v>55</v>
@@ -11470,7 +11470,7 @@
         <v>815</v>
       </c>
       <c r="E192" s="7">
-        <v>186</v>
+        <v>240</v>
       </c>
       <c r="F192" s="8" t="s">
         <v>55</v>
@@ -11493,7 +11493,7 @@
         <v>819</v>
       </c>
       <c r="E193" s="7">
-        <v>341</v>
+        <v>443</v>
       </c>
       <c r="F193" s="8" t="s">
         <v>55</v>
@@ -11516,7 +11516,7 @@
         <v>823</v>
       </c>
       <c r="E194" s="7">
-        <v>433</v>
+        <v>182</v>
       </c>
       <c r="F194" s="8" t="s">
         <v>55</v>
@@ -11539,7 +11539,7 @@
         <v>827</v>
       </c>
       <c r="E195" s="7">
-        <v>474</v>
+        <v>204</v>
       </c>
       <c r="F195" s="8" t="s">
         <v>55</v>
@@ -11562,7 +11562,7 @@
         <v>831</v>
       </c>
       <c r="E196" s="7">
-        <v>449</v>
+        <v>277</v>
       </c>
       <c r="F196" s="8" t="s">
         <v>55</v>
@@ -11585,7 +11585,7 @@
         <v>835</v>
       </c>
       <c r="E197" s="7">
-        <v>182</v>
+        <v>234</v>
       </c>
       <c r="F197" s="8" t="s">
         <v>55</v>
@@ -11608,7 +11608,7 @@
         <v>839</v>
       </c>
       <c r="E198" s="7">
-        <v>478</v>
+        <v>189</v>
       </c>
       <c r="F198" s="8" t="s">
         <v>55</v>
@@ -11631,7 +11631,7 @@
         <v>843</v>
       </c>
       <c r="E199" s="7">
-        <v>456</v>
+        <v>262</v>
       </c>
       <c r="F199" s="8" t="s">
         <v>55</v>
@@ -11654,7 +11654,7 @@
         <v>847</v>
       </c>
       <c r="E200" s="7">
-        <v>386</v>
+        <v>264</v>
       </c>
       <c r="F200" s="8" t="s">
         <v>55</v>
@@ -11677,7 +11677,7 @@
         <v>851</v>
       </c>
       <c r="E201" s="7">
-        <v>428</v>
+        <v>387</v>
       </c>
       <c r="F201" s="8" t="s">
         <v>55</v>
@@ -11700,7 +11700,7 @@
         <v>855</v>
       </c>
       <c r="E202" s="7">
-        <v>390</v>
+        <v>419</v>
       </c>
       <c r="F202" s="8" t="s">
         <v>55</v>
@@ -11723,7 +11723,7 @@
         <v>859</v>
       </c>
       <c r="E203" s="7">
-        <v>311</v>
+        <v>475</v>
       </c>
       <c r="F203" s="8" t="s">
         <v>55</v>
@@ -11746,7 +11746,7 @@
         <v>863</v>
       </c>
       <c r="E204" s="7">
-        <v>310</v>
+        <v>362</v>
       </c>
       <c r="F204" s="8" t="s">
         <v>55</v>
@@ -11769,7 +11769,7 @@
         <v>867</v>
       </c>
       <c r="E205" s="7">
-        <v>190</v>
+        <v>310</v>
       </c>
       <c r="F205" s="8" t="s">
         <v>55</v>
@@ -11792,7 +11792,7 @@
         <v>871</v>
       </c>
       <c r="E206" s="7">
-        <v>279</v>
+        <v>417</v>
       </c>
       <c r="F206" s="8" t="s">
         <v>55</v>
@@ -11815,7 +11815,7 @@
         <v>875</v>
       </c>
       <c r="E207" s="7">
-        <v>404</v>
+        <v>205</v>
       </c>
       <c r="F207" s="8" t="s">
         <v>55</v>
@@ -11838,7 +11838,7 @@
         <v>879</v>
       </c>
       <c r="E208" s="7">
-        <v>155</v>
+        <v>298</v>
       </c>
       <c r="F208" s="8" t="s">
         <v>55</v>
@@ -11861,7 +11861,7 @@
         <v>883</v>
       </c>
       <c r="E209" s="7">
-        <v>154</v>
+        <v>472</v>
       </c>
       <c r="F209" s="8" t="s">
         <v>55</v>
@@ -11884,7 +11884,7 @@
         <v>887</v>
       </c>
       <c r="E210" s="7">
-        <v>257</v>
+        <v>453</v>
       </c>
       <c r="F210" s="8" t="s">
         <v>55</v>
@@ -11907,7 +11907,7 @@
         <v>891</v>
       </c>
       <c r="E211" s="7">
-        <v>393</v>
+        <v>176</v>
       </c>
       <c r="F211" s="8" t="s">
         <v>55</v>
@@ -11930,7 +11930,7 @@
         <v>895</v>
       </c>
       <c r="E212" s="7">
-        <v>467</v>
+        <v>401</v>
       </c>
       <c r="F212" s="8" t="s">
         <v>55</v>
@@ -11953,7 +11953,7 @@
         <v>899</v>
       </c>
       <c r="E213" s="7">
-        <v>262</v>
+        <v>198</v>
       </c>
       <c r="F213" s="8" t="s">
         <v>55</v>
@@ -11976,7 +11976,7 @@
         <v>903</v>
       </c>
       <c r="E214" s="7">
-        <v>192</v>
+        <v>351</v>
       </c>
       <c r="F214" s="8" t="s">
         <v>55</v>
@@ -11999,7 +11999,7 @@
         <v>907</v>
       </c>
       <c r="E215" s="7">
-        <v>424</v>
+        <v>280</v>
       </c>
       <c r="F215" s="8" t="s">
         <v>55</v>
@@ -12022,7 +12022,7 @@
         <v>911</v>
       </c>
       <c r="E216" s="7">
-        <v>412</v>
+        <v>218</v>
       </c>
       <c r="F216" s="8" t="s">
         <v>55</v>
@@ -12045,7 +12045,7 @@
         <v>915</v>
       </c>
       <c r="E217" s="7">
-        <v>137</v>
+        <v>265</v>
       </c>
       <c r="F217" s="8" t="s">
         <v>55</v>
@@ -12068,7 +12068,7 @@
         <v>919</v>
       </c>
       <c r="E218" s="7">
-        <v>207</v>
+        <v>345</v>
       </c>
       <c r="F218" s="8" t="s">
         <v>55</v>
@@ -12091,7 +12091,7 @@
         <v>923</v>
       </c>
       <c r="E219" s="7">
-        <v>435</v>
+        <v>158</v>
       </c>
       <c r="F219" s="8" t="s">
         <v>55</v>
@@ -12114,7 +12114,7 @@
         <v>927</v>
       </c>
       <c r="E220" s="7">
-        <v>244</v>
+        <v>338</v>
       </c>
       <c r="F220" s="8" t="s">
         <v>55</v>
@@ -12137,7 +12137,7 @@
         <v>931</v>
       </c>
       <c r="E221" s="7">
-        <v>432</v>
+        <v>245</v>
       </c>
       <c r="F221" s="8" t="s">
         <v>55</v>
@@ -12160,7 +12160,7 @@
         <v>935</v>
       </c>
       <c r="E222" s="7">
-        <v>411</v>
+        <v>361</v>
       </c>
       <c r="F222" s="8" t="s">
         <v>55</v>
@@ -12183,7 +12183,7 @@
         <v>939</v>
       </c>
       <c r="E223" s="7">
-        <v>322</v>
+        <v>306</v>
       </c>
       <c r="F223" s="8" t="s">
         <v>55</v>
@@ -12206,7 +12206,7 @@
         <v>943</v>
       </c>
       <c r="E224" s="7">
-        <v>285</v>
+        <v>253</v>
       </c>
       <c r="F224" s="8" t="s">
         <v>55</v>
@@ -12229,7 +12229,7 @@
         <v>947</v>
       </c>
       <c r="E225" s="7">
-        <v>255</v>
+        <v>449</v>
       </c>
       <c r="F225" s="8" t="s">
         <v>55</v>
@@ -12252,7 +12252,7 @@
         <v>951</v>
       </c>
       <c r="E226" s="7">
-        <v>219</v>
+        <v>373</v>
       </c>
       <c r="F226" s="8" t="s">
         <v>55</v>
@@ -12275,7 +12275,7 @@
         <v>955</v>
       </c>
       <c r="E227" s="7">
-        <v>226</v>
+        <v>301</v>
       </c>
       <c r="F227" s="8" t="s">
         <v>55</v>
@@ -12298,7 +12298,7 @@
         <v>959</v>
       </c>
       <c r="E228" s="7">
-        <v>141</v>
+        <v>332</v>
       </c>
       <c r="F228" s="8" t="s">
         <v>55</v>
@@ -12321,7 +12321,7 @@
         <v>963</v>
       </c>
       <c r="E229" s="7">
-        <v>466</v>
+        <v>338</v>
       </c>
       <c r="F229" s="8" t="s">
         <v>55</v>
@@ -12344,7 +12344,7 @@
         <v>967</v>
       </c>
       <c r="E230" s="7">
-        <v>137</v>
+        <v>316</v>
       </c>
       <c r="F230" s="8" t="s">
         <v>55</v>
@@ -12367,7 +12367,7 @@
         <v>971</v>
       </c>
       <c r="E231" s="7">
-        <v>393</v>
+        <v>367</v>
       </c>
       <c r="F231" s="8" t="s">
         <v>55</v>
@@ -12390,7 +12390,7 @@
         <v>975</v>
       </c>
       <c r="E232" s="7">
-        <v>441</v>
+        <v>253</v>
       </c>
       <c r="F232" s="8" t="s">
         <v>55</v>
@@ -12413,7 +12413,7 @@
         <v>979</v>
       </c>
       <c r="E233" s="7">
-        <v>488</v>
+        <v>325</v>
       </c>
       <c r="F233" s="8" t="s">
         <v>55</v>
@@ -12436,7 +12436,7 @@
         <v>983</v>
       </c>
       <c r="E234" s="7">
-        <v>350</v>
+        <v>313</v>
       </c>
       <c r="F234" s="8" t="s">
         <v>55</v>
@@ -12459,7 +12459,7 @@
         <v>987</v>
       </c>
       <c r="E235" s="7">
-        <v>477</v>
+        <v>261</v>
       </c>
       <c r="F235" s="8" t="s">
         <v>55</v>
@@ -12482,7 +12482,7 @@
         <v>991</v>
       </c>
       <c r="E236" s="7">
-        <v>467</v>
+        <v>284</v>
       </c>
       <c r="F236" s="8" t="s">
         <v>55</v>
@@ -12505,7 +12505,7 @@
         <v>995</v>
       </c>
       <c r="E237" s="7">
-        <v>411</v>
+        <v>273</v>
       </c>
       <c r="F237" s="8" t="s">
         <v>55</v>
@@ -12528,7 +12528,7 @@
         <v>999</v>
       </c>
       <c r="E238" s="7">
-        <v>402</v>
+        <v>384</v>
       </c>
       <c r="F238" s="8" t="s">
         <v>55</v>
@@ -12551,7 +12551,7 @@
         <v>1003</v>
       </c>
       <c r="E239" s="7">
-        <v>398</v>
+        <v>381</v>
       </c>
       <c r="F239" s="8" t="s">
         <v>55</v>
@@ -12574,7 +12574,7 @@
         <v>1007</v>
       </c>
       <c r="E240" s="7">
-        <v>299</v>
+        <v>281</v>
       </c>
       <c r="F240" s="8" t="s">
         <v>55</v>
@@ -12597,7 +12597,7 @@
         <v>1011</v>
       </c>
       <c r="E241" s="7">
-        <v>162</v>
+        <v>302</v>
       </c>
       <c r="F241" s="8" t="s">
         <v>55</v>
@@ -12620,7 +12620,7 @@
         <v>1015</v>
       </c>
       <c r="E242" s="7">
-        <v>134</v>
+        <v>454</v>
       </c>
       <c r="F242" s="8" t="s">
         <v>55</v>
@@ -12643,7 +12643,7 @@
         <v>1019</v>
       </c>
       <c r="E243" s="7">
-        <v>398</v>
+        <v>420</v>
       </c>
       <c r="F243" s="8" t="s">
         <v>55</v>
@@ -12666,7 +12666,7 @@
         <v>1023</v>
       </c>
       <c r="E244" s="7">
-        <v>476</v>
+        <v>381</v>
       </c>
       <c r="F244" s="8" t="s">
         <v>55</v>
@@ -12689,7 +12689,7 @@
         <v>1027</v>
       </c>
       <c r="E245" s="7">
-        <v>149</v>
+        <v>291</v>
       </c>
       <c r="F245" s="8" t="s">
         <v>55</v>
@@ -12712,7 +12712,7 @@
         <v>1031</v>
       </c>
       <c r="E246" s="7">
-        <v>471</v>
+        <v>482</v>
       </c>
       <c r="F246" s="8" t="s">
         <v>55</v>
@@ -12735,7 +12735,7 @@
         <v>1035</v>
       </c>
       <c r="E247" s="7">
-        <v>138</v>
+        <v>323</v>
       </c>
       <c r="F247" s="8" t="s">
         <v>55</v>
@@ -12758,7 +12758,7 @@
         <v>1039</v>
       </c>
       <c r="E248" s="7">
-        <v>473</v>
+        <v>305</v>
       </c>
       <c r="F248" s="8" t="s">
         <v>55</v>
@@ -12781,7 +12781,7 @@
         <v>1043</v>
       </c>
       <c r="E249" s="7">
-        <v>282</v>
+        <v>480</v>
       </c>
       <c r="F249" s="8" t="s">
         <v>55</v>
@@ -12804,7 +12804,7 @@
         <v>1047</v>
       </c>
       <c r="E250" s="7">
-        <v>372</v>
+        <v>251</v>
       </c>
       <c r="F250" s="8" t="s">
         <v>55</v>
@@ -12827,7 +12827,7 @@
         <v>1051</v>
       </c>
       <c r="E251" s="7">
-        <v>253</v>
+        <v>244</v>
       </c>
       <c r="F251" s="8" t="s">
         <v>55</v>
@@ -12850,7 +12850,7 @@
         <v>1055</v>
       </c>
       <c r="E252" s="7">
-        <v>277</v>
+        <v>368</v>
       </c>
       <c r="F252" s="8" t="s">
         <v>55</v>
@@ -12873,7 +12873,7 @@
         <v>1059</v>
       </c>
       <c r="E253" s="7">
-        <v>397</v>
+        <v>272</v>
       </c>
       <c r="F253" s="8" t="s">
         <v>55</v>
@@ -12896,7 +12896,7 @@
         <v>1063</v>
       </c>
       <c r="E254" s="7">
-        <v>398</v>
+        <v>377</v>
       </c>
       <c r="F254" s="8" t="s">
         <v>55</v>
@@ -12919,7 +12919,7 @@
         <v>1067</v>
       </c>
       <c r="E255" s="7">
-        <v>255</v>
+        <v>286</v>
       </c>
       <c r="F255" s="8" t="s">
         <v>55</v>
@@ -12942,7 +12942,7 @@
         <v>1071</v>
       </c>
       <c r="E256" s="7">
-        <v>375</v>
+        <v>228</v>
       </c>
       <c r="F256" s="8" t="s">
         <v>55</v>
@@ -12965,7 +12965,7 @@
         <v>1075</v>
       </c>
       <c r="E257" s="7">
-        <v>430</v>
+        <v>172</v>
       </c>
       <c r="F257" s="8" t="s">
         <v>55</v>
@@ -12988,7 +12988,7 @@
         <v>1079</v>
       </c>
       <c r="E258" s="7">
-        <v>376</v>
+        <v>299</v>
       </c>
       <c r="F258" s="8" t="s">
         <v>55</v>
@@ -13011,7 +13011,7 @@
         <v>1083</v>
       </c>
       <c r="E259" s="7">
-        <v>142</v>
+        <v>333</v>
       </c>
       <c r="F259" s="8" t="s">
         <v>55</v>
@@ -13034,7 +13034,7 @@
         <v>1087</v>
       </c>
       <c r="E260" s="7">
-        <v>364</v>
+        <v>165</v>
       </c>
       <c r="F260" s="8" t="s">
         <v>55</v>
@@ -13057,7 +13057,7 @@
         <v>1091</v>
       </c>
       <c r="E261" s="7">
-        <v>226</v>
+        <v>443</v>
       </c>
       <c r="F261" s="8" t="s">
         <v>55</v>
@@ -13080,7 +13080,7 @@
         <v>1095</v>
       </c>
       <c r="E262" s="7">
-        <v>306</v>
+        <v>159</v>
       </c>
       <c r="F262" s="8" t="s">
         <v>55</v>
@@ -13103,7 +13103,7 @@
         <v>1099</v>
       </c>
       <c r="E263" s="7">
-        <v>333</v>
+        <v>356</v>
       </c>
       <c r="F263" s="8" t="s">
         <v>55</v>
@@ -13126,7 +13126,7 @@
         <v>1103</v>
       </c>
       <c r="E264" s="7">
-        <v>371</v>
+        <v>213</v>
       </c>
       <c r="F264" s="8" t="s">
         <v>55</v>
@@ -13149,7 +13149,7 @@
         <v>1107</v>
       </c>
       <c r="E265" s="7">
-        <v>384</v>
+        <v>159</v>
       </c>
       <c r="F265" s="8" t="s">
         <v>55</v>
@@ -13172,7 +13172,7 @@
         <v>1111</v>
       </c>
       <c r="E266" s="7">
-        <v>244</v>
+        <v>306</v>
       </c>
       <c r="F266" s="8" t="s">
         <v>55</v>
@@ -13195,7 +13195,7 @@
         <v>1115</v>
       </c>
       <c r="E267" s="7">
-        <v>243</v>
+        <v>271</v>
       </c>
       <c r="F267" s="8" t="s">
         <v>55</v>
@@ -13218,7 +13218,7 @@
         <v>1119</v>
       </c>
       <c r="E268" s="7">
-        <v>302</v>
+        <v>239</v>
       </c>
       <c r="F268" s="8" t="s">
         <v>55</v>
@@ -13241,7 +13241,7 @@
         <v>1123</v>
       </c>
       <c r="E269" s="7">
-        <v>359</v>
+        <v>378</v>
       </c>
       <c r="F269" s="8" t="s">
         <v>55</v>
@@ -13264,7 +13264,7 @@
         <v>1127</v>
       </c>
       <c r="E270" s="7">
-        <v>374</v>
+        <v>131</v>
       </c>
       <c r="F270" s="8" t="s">
         <v>55</v>
@@ -13287,7 +13287,7 @@
         <v>1131</v>
       </c>
       <c r="E271" s="7">
-        <v>389</v>
+        <v>134</v>
       </c>
       <c r="F271" s="8" t="s">
         <v>55</v>
@@ -13310,7 +13310,7 @@
         <v>1135</v>
       </c>
       <c r="E272" s="7">
-        <v>244</v>
+        <v>388</v>
       </c>
       <c r="F272" s="8" t="s">
         <v>55</v>
@@ -13333,7 +13333,7 @@
         <v>1139</v>
       </c>
       <c r="E273" s="7">
-        <v>391</v>
+        <v>311</v>
       </c>
       <c r="F273" s="8" t="s">
         <v>55</v>
@@ -13356,7 +13356,7 @@
         <v>1143</v>
       </c>
       <c r="E274" s="7">
-        <v>156</v>
+        <v>243</v>
       </c>
       <c r="F274" s="8" t="s">
         <v>55</v>
@@ -13379,7 +13379,7 @@
         <v>1147</v>
       </c>
       <c r="E275" s="7">
-        <v>227</v>
+        <v>123</v>
       </c>
       <c r="F275" s="8" t="s">
         <v>55</v>
@@ -13402,7 +13402,7 @@
         <v>1151</v>
       </c>
       <c r="E276" s="7">
-        <v>437</v>
+        <v>406</v>
       </c>
       <c r="F276" s="8" t="s">
         <v>55</v>
@@ -13425,7 +13425,7 @@
         <v>1155</v>
       </c>
       <c r="E277" s="7">
-        <v>347</v>
+        <v>293</v>
       </c>
       <c r="F277" s="8" t="s">
         <v>55</v>
@@ -13448,7 +13448,7 @@
         <v>1159</v>
       </c>
       <c r="E278" s="7">
-        <v>328</v>
+        <v>141</v>
       </c>
       <c r="F278" s="8" t="s">
         <v>55</v>
@@ -13471,7 +13471,7 @@
         <v>1163</v>
       </c>
       <c r="E279" s="7">
-        <v>261</v>
+        <v>399</v>
       </c>
       <c r="F279" s="8" t="s">
         <v>55</v>
@@ -13494,7 +13494,7 @@
         <v>1167</v>
       </c>
       <c r="E280" s="7">
-        <v>186</v>
+        <v>336</v>
       </c>
       <c r="F280" s="8" t="s">
         <v>55</v>
@@ -13517,7 +13517,7 @@
         <v>1171</v>
       </c>
       <c r="E281" s="7">
-        <v>135</v>
+        <v>124</v>
       </c>
       <c r="F281" s="8" t="s">
         <v>55</v>
@@ -13540,7 +13540,7 @@
         <v>1175</v>
       </c>
       <c r="E282" s="7">
-        <v>403</v>
+        <v>143</v>
       </c>
       <c r="F282" s="8" t="s">
         <v>55</v>
@@ -13563,7 +13563,7 @@
         <v>1179</v>
       </c>
       <c r="E283" s="7">
-        <v>402</v>
+        <v>332</v>
       </c>
       <c r="F283" s="8" t="s">
         <v>55</v>
@@ -13586,7 +13586,7 @@
         <v>1183</v>
       </c>
       <c r="E284" s="7">
-        <v>131</v>
+        <v>170</v>
       </c>
       <c r="F284" s="8" t="s">
         <v>55</v>
@@ -13609,7 +13609,7 @@
         <v>1187</v>
       </c>
       <c r="E285" s="7">
-        <v>348</v>
+        <v>146</v>
       </c>
       <c r="F285" s="8" t="s">
         <v>55</v>
@@ -13632,7 +13632,7 @@
         <v>1191</v>
       </c>
       <c r="E286" s="7">
-        <v>367</v>
+        <v>370</v>
       </c>
       <c r="F286" s="8" t="s">
         <v>55</v>
@@ -13655,7 +13655,7 @@
         <v>1195</v>
       </c>
       <c r="E287" s="7">
-        <v>355</v>
+        <v>183</v>
       </c>
       <c r="F287" s="8" t="s">
         <v>55</v>
@@ -13678,7 +13678,7 @@
         <v>1199</v>
       </c>
       <c r="E288" s="7">
-        <v>156</v>
+        <v>269</v>
       </c>
       <c r="F288" s="8" t="s">
         <v>55</v>
@@ -13701,7 +13701,7 @@
         <v>1203</v>
       </c>
       <c r="E289" s="7">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="F289" s="8" t="s">
         <v>55</v>
@@ -13724,7 +13724,7 @@
         <v>1207</v>
       </c>
       <c r="E290" s="7">
-        <v>131</v>
+        <v>360</v>
       </c>
       <c r="F290" s="8" t="s">
         <v>55</v>
@@ -13747,7 +13747,7 @@
         <v>1211</v>
       </c>
       <c r="E291" s="7">
-        <v>203</v>
+        <v>149</v>
       </c>
       <c r="F291" s="8" t="s">
         <v>55</v>
@@ -13770,7 +13770,7 @@
         <v>1215</v>
       </c>
       <c r="E292" s="7">
-        <v>367</v>
+        <v>353</v>
       </c>
       <c r="F292" s="8" t="s">
         <v>55</v>
@@ -13793,7 +13793,7 @@
         <v>1219</v>
       </c>
       <c r="E293" s="7">
-        <v>167</v>
+        <v>441</v>
       </c>
       <c r="F293" s="8" t="s">
         <v>55</v>
@@ -13816,7 +13816,7 @@
         <v>1223</v>
       </c>
       <c r="E294" s="7">
-        <v>374</v>
+        <v>157</v>
       </c>
       <c r="F294" s="8" t="s">
         <v>55</v>
@@ -13839,7 +13839,7 @@
         <v>1227</v>
       </c>
       <c r="E295" s="7">
-        <v>259</v>
+        <v>393</v>
       </c>
       <c r="F295" s="8" t="s">
         <v>55</v>
@@ -13862,7 +13862,7 @@
         <v>1231</v>
       </c>
       <c r="E296" s="7">
-        <v>416</v>
+        <v>320</v>
       </c>
       <c r="F296" s="8" t="s">
         <v>55</v>
@@ -13885,7 +13885,7 @@
         <v>1235</v>
       </c>
       <c r="E297" s="7">
-        <v>139</v>
+        <v>425</v>
       </c>
       <c r="F297" s="8" t="s">
         <v>55</v>
@@ -13908,7 +13908,7 @@
         <v>1239</v>
       </c>
       <c r="E298" s="7">
-        <v>320</v>
+        <v>326</v>
       </c>
       <c r="F298" s="8" t="s">
         <v>55</v>
@@ -13931,7 +13931,7 @@
         <v>1243</v>
       </c>
       <c r="E299" s="7">
-        <v>434</v>
+        <v>236</v>
       </c>
       <c r="F299" s="8" t="s">
         <v>55</v>
@@ -13954,7 +13954,7 @@
         <v>1247</v>
       </c>
       <c r="E300" s="7">
-        <v>238</v>
+        <v>192</v>
       </c>
       <c r="F300" s="8" t="s">
         <v>55</v>
@@ -13977,7 +13977,7 @@
         <v>1251</v>
       </c>
       <c r="E301" s="7">
-        <v>123</v>
+        <v>359</v>
       </c>
       <c r="F301" s="8" t="s">
         <v>55</v>
@@ -14000,7 +14000,7 @@
         <v>1255</v>
       </c>
       <c r="E302" s="7">
-        <v>376</v>
+        <v>276</v>
       </c>
       <c r="F302" s="8" t="s">
         <v>55</v>
@@ -14023,7 +14023,7 @@
         <v>1259</v>
       </c>
       <c r="E303" s="7">
-        <v>434</v>
+        <v>240</v>
       </c>
       <c r="F303" s="8" t="s">
         <v>55</v>
@@ -14046,7 +14046,7 @@
         <v>1263</v>
       </c>
       <c r="E304" s="7">
-        <v>169</v>
+        <v>284</v>
       </c>
       <c r="F304" s="8" t="s">
         <v>55</v>
@@ -14069,7 +14069,7 @@
         <v>1267</v>
       </c>
       <c r="E305" s="7">
-        <v>208</v>
+        <v>354</v>
       </c>
       <c r="F305" s="8" t="s">
         <v>55</v>
@@ -14092,7 +14092,7 @@
         <v>1271</v>
       </c>
       <c r="E306" s="7">
-        <v>335</v>
+        <v>297</v>
       </c>
       <c r="F306" s="8" t="s">
         <v>55</v>
@@ -14115,7 +14115,7 @@
         <v>1275</v>
       </c>
       <c r="E307" s="7">
-        <v>419</v>
+        <v>306</v>
       </c>
       <c r="F307" s="8" t="s">
         <v>55</v>
@@ -14138,7 +14138,7 @@
         <v>1279</v>
       </c>
       <c r="E308" s="7">
-        <v>205</v>
+        <v>179</v>
       </c>
       <c r="F308" s="8" t="s">
         <v>55</v>
@@ -14161,7 +14161,7 @@
         <v>1283</v>
       </c>
       <c r="E309" s="7">
-        <v>183</v>
+        <v>470</v>
       </c>
       <c r="F309" s="8" t="s">
         <v>55</v>
@@ -14184,7 +14184,7 @@
         <v>1287</v>
       </c>
       <c r="E310" s="7">
-        <v>339</v>
+        <v>241</v>
       </c>
       <c r="F310" s="8" t="s">
         <v>55</v>
@@ -14207,7 +14207,7 @@
         <v>1291</v>
       </c>
       <c r="E311" s="7">
-        <v>517</v>
+        <v>509</v>
       </c>
       <c r="F311" s="8" t="s">
         <v>55</v>
@@ -14230,7 +14230,7 @@
         <v>1295</v>
       </c>
       <c r="E312" s="7">
-        <v>541</v>
+        <v>423</v>
       </c>
       <c r="F312" s="8" t="s">
         <v>55</v>
@@ -14253,7 +14253,7 @@
         <v>1299</v>
       </c>
       <c r="E313" s="7">
-        <v>452</v>
+        <v>264</v>
       </c>
       <c r="F313" s="8" t="s">
         <v>55</v>
@@ -14276,7 +14276,7 @@
         <v>1303</v>
       </c>
       <c r="E314" s="7">
-        <v>267</v>
+        <v>355</v>
       </c>
       <c r="F314" s="8" t="s">
         <v>55</v>
@@ -14299,7 +14299,7 @@
         <v>1307</v>
       </c>
       <c r="E315" s="7">
-        <v>532</v>
+        <v>293</v>
       </c>
       <c r="F315" s="8" t="s">
         <v>55</v>
@@ -14322,7 +14322,7 @@
         <v>1311</v>
       </c>
       <c r="E316" s="7">
-        <v>185</v>
+        <v>371</v>
       </c>
       <c r="F316" s="8" t="s">
         <v>55</v>
@@ -14345,7 +14345,7 @@
         <v>1315</v>
       </c>
       <c r="E317" s="7">
-        <v>221</v>
+        <v>485</v>
       </c>
       <c r="F317" s="8" t="s">
         <v>55</v>
@@ -14368,7 +14368,7 @@
         <v>1319</v>
       </c>
       <c r="E318" s="7">
-        <v>560</v>
+        <v>369</v>
       </c>
       <c r="F318" s="8" t="s">
         <v>55</v>
@@ -14391,7 +14391,7 @@
         <v>1323</v>
       </c>
       <c r="E319" s="7">
-        <v>210</v>
+        <v>560</v>
       </c>
       <c r="F319" s="8" t="s">
         <v>55</v>
@@ -14414,7 +14414,7 @@
         <v>1327</v>
       </c>
       <c r="E320" s="7">
-        <v>223</v>
+        <v>521</v>
       </c>
       <c r="F320" s="8" t="s">
         <v>55</v>
@@ -14437,7 +14437,7 @@
         <v>1331</v>
       </c>
       <c r="E321" s="7">
-        <v>230</v>
+        <v>408</v>
       </c>
       <c r="F321" s="8" t="s">
         <v>55</v>
@@ -14460,7 +14460,7 @@
         <v>1335</v>
       </c>
       <c r="E322" s="7">
-        <v>495</v>
+        <v>437</v>
       </c>
       <c r="F322" s="8" t="s">
         <v>55</v>
@@ -14483,7 +14483,7 @@
         <v>1339</v>
       </c>
       <c r="E323" s="7">
-        <v>525</v>
+        <v>385</v>
       </c>
       <c r="F323" s="8" t="s">
         <v>55</v>
@@ -14506,7 +14506,7 @@
         <v>1343</v>
       </c>
       <c r="E324" s="7">
-        <v>439</v>
+        <v>463</v>
       </c>
       <c r="F324" s="8" t="s">
         <v>55</v>
@@ -14529,7 +14529,7 @@
         <v>1347</v>
       </c>
       <c r="E325" s="7">
-        <v>310</v>
+        <v>553</v>
       </c>
       <c r="F325" s="8" t="s">
         <v>55</v>
@@ -14552,7 +14552,7 @@
         <v>1351</v>
       </c>
       <c r="E326" s="7">
-        <v>281</v>
+        <v>512</v>
       </c>
       <c r="F326" s="8" t="s">
         <v>55</v>
@@ -14575,7 +14575,7 @@
         <v>1355</v>
       </c>
       <c r="E327" s="7">
-        <v>475</v>
+        <v>237</v>
       </c>
       <c r="F327" s="8" t="s">
         <v>55</v>
@@ -14598,7 +14598,7 @@
         <v>1359</v>
       </c>
       <c r="E328" s="7">
-        <v>415</v>
+        <v>281</v>
       </c>
       <c r="F328" s="8" t="s">
         <v>55</v>
@@ -14621,7 +14621,7 @@
         <v>1363</v>
       </c>
       <c r="E329" s="7">
-        <v>560</v>
+        <v>306</v>
       </c>
       <c r="F329" s="8" t="s">
         <v>55</v>
@@ -14644,7 +14644,7 @@
         <v>1367</v>
       </c>
       <c r="E330" s="7">
-        <v>291</v>
+        <v>177</v>
       </c>
       <c r="F330" s="8" t="s">
         <v>55</v>
@@ -14667,7 +14667,7 @@
         <v>1371</v>
       </c>
       <c r="E331" s="7">
-        <v>298</v>
+        <v>424</v>
       </c>
       <c r="F331" s="8" t="s">
         <v>55</v>
@@ -14690,7 +14690,7 @@
         <v>1375</v>
       </c>
       <c r="E332" s="7">
-        <v>424</v>
+        <v>430</v>
       </c>
       <c r="F332" s="8" t="s">
         <v>55</v>
@@ -14713,7 +14713,7 @@
         <v>1379</v>
       </c>
       <c r="E333" s="7">
-        <v>356</v>
+        <v>474</v>
       </c>
       <c r="F333" s="8" t="s">
         <v>55</v>
@@ -14736,7 +14736,7 @@
         <v>1383</v>
       </c>
       <c r="E334" s="7">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="F334" s="8" t="s">
         <v>55</v>
@@ -14759,7 +14759,7 @@
         <v>1387</v>
       </c>
       <c r="E335" s="7">
-        <v>344</v>
+        <v>198</v>
       </c>
       <c r="F335" s="8" t="s">
         <v>55</v>
@@ -14782,7 +14782,7 @@
         <v>1391</v>
       </c>
       <c r="E336" s="7">
-        <v>307</v>
+        <v>317</v>
       </c>
       <c r="F336" s="8" t="s">
         <v>55</v>
@@ -14805,7 +14805,7 @@
         <v>1395</v>
       </c>
       <c r="E337" s="7">
-        <v>351</v>
+        <v>486</v>
       </c>
       <c r="F337" s="8" t="s">
         <v>55</v>
@@ -14828,7 +14828,7 @@
         <v>1399</v>
       </c>
       <c r="E338" s="7">
-        <v>240</v>
+        <v>300</v>
       </c>
       <c r="F338" s="8" t="s">
         <v>55</v>
@@ -14851,7 +14851,7 @@
         <v>1403</v>
       </c>
       <c r="E339" s="7">
-        <v>213</v>
+        <v>275</v>
       </c>
       <c r="F339" s="8" t="s">
         <v>55</v>
@@ -14874,7 +14874,7 @@
         <v>1407</v>
       </c>
       <c r="E340" s="7">
-        <v>200</v>
+        <v>359</v>
       </c>
       <c r="F340" s="8" t="s">
         <v>55</v>
@@ -14897,7 +14897,7 @@
         <v>1411</v>
       </c>
       <c r="E341" s="7">
-        <v>528</v>
+        <v>453</v>
       </c>
       <c r="F341" s="8" t="s">
         <v>55</v>
@@ -14920,7 +14920,7 @@
         <v>1415</v>
       </c>
       <c r="E342" s="7">
-        <v>223</v>
+        <v>513</v>
       </c>
       <c r="F342" s="8" t="s">
         <v>55</v>
@@ -14943,7 +14943,7 @@
         <v>1419</v>
       </c>
       <c r="E343" s="7">
-        <v>560</v>
+        <v>377</v>
       </c>
       <c r="F343" s="8" t="s">
         <v>55</v>
@@ -14966,7 +14966,7 @@
         <v>1423</v>
       </c>
       <c r="E344" s="7">
-        <v>464</v>
+        <v>424</v>
       </c>
       <c r="F344" s="8" t="s">
         <v>55</v>
@@ -14989,7 +14989,7 @@
         <v>1427</v>
       </c>
       <c r="E345" s="7">
-        <v>537</v>
+        <v>250</v>
       </c>
       <c r="F345" s="8" t="s">
         <v>55</v>
@@ -15012,7 +15012,7 @@
         <v>1431</v>
       </c>
       <c r="E346" s="7">
-        <v>190</v>
+        <v>357</v>
       </c>
       <c r="F346" s="8" t="s">
         <v>55</v>
@@ -15035,7 +15035,7 @@
         <v>1435</v>
       </c>
       <c r="E347" s="7">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="F347" s="8" t="s">
         <v>55</v>
@@ -15058,7 +15058,7 @@
         <v>1439</v>
       </c>
       <c r="E348" s="7">
-        <v>307</v>
+        <v>212</v>
       </c>
       <c r="F348" s="8" t="s">
         <v>55</v>
@@ -15081,7 +15081,7 @@
         <v>1443</v>
       </c>
       <c r="E349" s="7">
-        <v>555</v>
+        <v>297</v>
       </c>
       <c r="F349" s="8" t="s">
         <v>55</v>
@@ -15104,7 +15104,7 @@
         <v>1447</v>
       </c>
       <c r="E350" s="7">
-        <v>179</v>
+        <v>547</v>
       </c>
       <c r="F350" s="8" t="s">
         <v>55</v>
@@ -15127,7 +15127,7 @@
         <v>1451</v>
       </c>
       <c r="E351" s="7">
-        <v>329</v>
+        <v>286</v>
       </c>
       <c r="F351" s="8" t="s">
         <v>55</v>
@@ -15150,7 +15150,7 @@
         <v>1455</v>
       </c>
       <c r="E352" s="7">
-        <v>276</v>
+        <v>216</v>
       </c>
       <c r="F352" s="8" t="s">
         <v>55</v>
@@ -15173,7 +15173,7 @@
         <v>1459</v>
       </c>
       <c r="E353" s="7">
-        <v>553</v>
+        <v>424</v>
       </c>
       <c r="F353" s="8" t="s">
         <v>55</v>
@@ -15196,7 +15196,7 @@
         <v>1463</v>
       </c>
       <c r="E354" s="7">
-        <v>308</v>
+        <v>416</v>
       </c>
       <c r="F354" s="8" t="s">
         <v>55</v>
@@ -15219,7 +15219,7 @@
         <v>1467</v>
       </c>
       <c r="E355" s="7">
-        <v>379</v>
+        <v>442</v>
       </c>
       <c r="F355" s="8" t="s">
         <v>55</v>
@@ -15242,7 +15242,7 @@
         <v>1471</v>
       </c>
       <c r="E356" s="7">
-        <v>280</v>
+        <v>183</v>
       </c>
       <c r="F356" s="8" t="s">
         <v>55</v>
@@ -15265,7 +15265,7 @@
         <v>1475</v>
       </c>
       <c r="E357" s="7">
-        <v>217</v>
+        <v>276</v>
       </c>
       <c r="F357" s="8" t="s">
         <v>55</v>
@@ -15288,7 +15288,7 @@
         <v>1479</v>
       </c>
       <c r="E358" s="7">
-        <v>392</v>
+        <v>580</v>
       </c>
       <c r="F358" s="8" t="s">
         <v>55</v>
@@ -15311,7 +15311,7 @@
         <v>1483</v>
       </c>
       <c r="E359" s="7">
-        <v>203</v>
+        <v>395</v>
       </c>
       <c r="F359" s="8" t="s">
         <v>55</v>
@@ -15334,7 +15334,7 @@
         <v>1487</v>
       </c>
       <c r="E360" s="7">
-        <v>336</v>
+        <v>509</v>
       </c>
       <c r="F360" s="8" t="s">
         <v>55</v>
@@ -15357,7 +15357,7 @@
         <v>1491</v>
       </c>
       <c r="E361" s="7">
-        <v>294</v>
+        <v>337</v>
       </c>
       <c r="F361" s="8" t="s">
         <v>55</v>
@@ -15380,7 +15380,7 @@
         <v>1495</v>
       </c>
       <c r="E362" s="7">
-        <v>597</v>
+        <v>560</v>
       </c>
       <c r="F362" s="8" t="s">
         <v>55</v>
@@ -15403,7 +15403,7 @@
         <v>1499</v>
       </c>
       <c r="E363" s="7">
-        <v>447</v>
+        <v>519</v>
       </c>
       <c r="F363" s="8" t="s">
         <v>55</v>
@@ -15426,7 +15426,7 @@
         <v>1503</v>
       </c>
       <c r="E364" s="7">
-        <v>422</v>
+        <v>345</v>
       </c>
       <c r="F364" s="8" t="s">
         <v>55</v>
@@ -15449,7 +15449,7 @@
         <v>1507</v>
       </c>
       <c r="E365" s="7">
-        <v>198</v>
+        <v>608</v>
       </c>
       <c r="F365" s="8" t="s">
         <v>55</v>
@@ -15472,7 +15472,7 @@
         <v>1511</v>
       </c>
       <c r="E366" s="7">
-        <v>445</v>
+        <v>574</v>
       </c>
       <c r="F366" s="8" t="s">
         <v>55</v>
@@ -15495,7 +15495,7 @@
         <v>1515</v>
       </c>
       <c r="E367" s="7">
-        <v>552</v>
+        <v>577</v>
       </c>
       <c r="F367" s="8" t="s">
         <v>55</v>
@@ -15518,7 +15518,7 @@
         <v>1519</v>
       </c>
       <c r="E368" s="7">
-        <v>533</v>
+        <v>375</v>
       </c>
       <c r="F368" s="8" t="s">
         <v>55</v>
@@ -15541,7 +15541,7 @@
         <v>1523</v>
       </c>
       <c r="E369" s="7">
-        <v>496</v>
+        <v>312</v>
       </c>
       <c r="F369" s="8" t="s">
         <v>55</v>
@@ -15564,7 +15564,7 @@
         <v>1527</v>
       </c>
       <c r="E370" s="7">
-        <v>420</v>
+        <v>289</v>
       </c>
       <c r="F370" s="8" t="s">
         <v>55</v>
@@ -15587,7 +15587,7 @@
         <v>1531</v>
       </c>
       <c r="E371" s="7">
-        <v>227</v>
+        <v>182</v>
       </c>
       <c r="F371" s="8" t="s">
         <v>55</v>
@@ -15610,7 +15610,7 @@
         <v>1535</v>
       </c>
       <c r="E372" s="7">
-        <v>288</v>
+        <v>376</v>
       </c>
       <c r="F372" s="8" t="s">
         <v>55</v>
@@ -15633,7 +15633,7 @@
         <v>1539</v>
       </c>
       <c r="E373" s="7">
-        <v>199</v>
+        <v>428</v>
       </c>
       <c r="F373" s="8" t="s">
         <v>55</v>
@@ -15656,7 +15656,7 @@
         <v>1543</v>
       </c>
       <c r="E374" s="7">
-        <v>582</v>
+        <v>549</v>
       </c>
       <c r="F374" s="8" t="s">
         <v>55</v>
@@ -15679,7 +15679,7 @@
         <v>1547</v>
       </c>
       <c r="E375" s="7">
-        <v>228</v>
+        <v>398</v>
       </c>
       <c r="F375" s="8" t="s">
         <v>55</v>
@@ -15702,7 +15702,7 @@
         <v>1551</v>
       </c>
       <c r="E376" s="7">
-        <v>615</v>
+        <v>223</v>
       </c>
       <c r="F376" s="8" t="s">
         <v>55</v>
@@ -15725,7 +15725,7 @@
         <v>1555</v>
       </c>
       <c r="E377" s="7">
-        <v>401</v>
+        <v>212</v>
       </c>
       <c r="F377" s="8" t="s">
         <v>55</v>
@@ -15748,7 +15748,7 @@
         <v>1559</v>
       </c>
       <c r="E378" s="7">
-        <v>356</v>
+        <v>427</v>
       </c>
       <c r="F378" s="8" t="s">
         <v>55</v>
@@ -15771,7 +15771,7 @@
         <v>1563</v>
       </c>
       <c r="E379" s="7">
-        <v>617</v>
+        <v>268</v>
       </c>
       <c r="F379" s="8" t="s">
         <v>55</v>
@@ -15794,7 +15794,7 @@
         <v>1567</v>
       </c>
       <c r="E380" s="7">
-        <v>566</v>
+        <v>275</v>
       </c>
       <c r="F380" s="8" t="s">
         <v>55</v>
@@ -15817,7 +15817,7 @@
         <v>1571</v>
       </c>
       <c r="E381" s="7">
-        <v>426</v>
+        <v>406</v>
       </c>
       <c r="F381" s="8" t="s">
         <v>55</v>
@@ -15840,7 +15840,7 @@
         <v>1575</v>
       </c>
       <c r="E382" s="7">
-        <v>458</v>
+        <v>294</v>
       </c>
       <c r="F382" s="8" t="s">
         <v>55</v>
@@ -15863,7 +15863,7 @@
         <v>1579</v>
       </c>
       <c r="E383" s="7">
-        <v>231</v>
+        <v>406</v>
       </c>
       <c r="F383" s="8" t="s">
         <v>55</v>
@@ -15886,7 +15886,7 @@
         <v>1583</v>
       </c>
       <c r="E384" s="7">
-        <v>396</v>
+        <v>411</v>
       </c>
       <c r="F384" s="8" t="s">
         <v>55</v>
@@ -15909,7 +15909,7 @@
         <v>1587</v>
       </c>
       <c r="E385" s="7">
-        <v>579</v>
+        <v>542</v>
       </c>
       <c r="F385" s="8" t="s">
         <v>55</v>
@@ -15932,7 +15932,7 @@
         <v>1591</v>
       </c>
       <c r="E386" s="7">
-        <v>372</v>
+        <v>387</v>
       </c>
       <c r="F386" s="8" t="s">
         <v>55</v>
@@ -15955,7 +15955,7 @@
         <v>1595</v>
       </c>
       <c r="E387" s="7">
-        <v>450</v>
+        <v>223</v>
       </c>
       <c r="F387" s="8" t="s">
         <v>55</v>
@@ -15978,7 +15978,7 @@
         <v>1599</v>
       </c>
       <c r="E388" s="7">
-        <v>440</v>
+        <v>246</v>
       </c>
       <c r="F388" s="8" t="s">
         <v>55</v>
@@ -16001,7 +16001,7 @@
         <v>1603</v>
       </c>
       <c r="E389" s="7">
-        <v>384</v>
+        <v>533</v>
       </c>
       <c r="F389" s="8" t="s">
         <v>55</v>
@@ -16024,7 +16024,7 @@
         <v>1607</v>
       </c>
       <c r="E390" s="7">
-        <v>594</v>
+        <v>617</v>
       </c>
       <c r="F390" s="8" t="s">
         <v>55</v>
@@ -16047,7 +16047,7 @@
         <v>1611</v>
       </c>
       <c r="E391" s="7">
-        <v>252</v>
+        <v>263</v>
       </c>
       <c r="F391" s="8" t="s">
         <v>55</v>
@@ -16070,7 +16070,7 @@
         <v>1615</v>
       </c>
       <c r="E392" s="7">
-        <v>236</v>
+        <v>224</v>
       </c>
       <c r="F392" s="8" t="s">
         <v>55</v>
@@ -16093,7 +16093,7 @@
         <v>1619</v>
       </c>
       <c r="E393" s="7">
-        <v>349</v>
+        <v>610</v>
       </c>
       <c r="F393" s="8" t="s">
         <v>55</v>
@@ -16116,7 +16116,7 @@
         <v>1623</v>
       </c>
       <c r="E394" s="7">
-        <v>547</v>
+        <v>326</v>
       </c>
       <c r="F394" s="8" t="s">
         <v>55</v>
@@ -16139,7 +16139,7 @@
         <v>1627</v>
       </c>
       <c r="E395" s="7">
-        <v>542</v>
+        <v>549</v>
       </c>
       <c r="F395" s="8" t="s">
         <v>55</v>
@@ -16162,7 +16162,7 @@
         <v>1631</v>
       </c>
       <c r="E396" s="7">
-        <v>358</v>
+        <v>261</v>
       </c>
       <c r="F396" s="8" t="s">
         <v>55</v>
@@ -16185,7 +16185,7 @@
         <v>1635</v>
       </c>
       <c r="E397" s="7">
-        <v>523</v>
+        <v>315</v>
       </c>
       <c r="F397" s="8" t="s">
         <v>55</v>
@@ -16208,7 +16208,7 @@
         <v>1639</v>
       </c>
       <c r="E398" s="7">
-        <v>397</v>
+        <v>332</v>
       </c>
       <c r="F398" s="8" t="s">
         <v>55</v>
@@ -16231,7 +16231,7 @@
         <v>1643</v>
       </c>
       <c r="E399" s="7">
-        <v>391</v>
+        <v>312</v>
       </c>
       <c r="F399" s="8" t="s">
         <v>55</v>
@@ -16254,7 +16254,7 @@
         <v>1647</v>
       </c>
       <c r="E400" s="7">
-        <v>207</v>
+        <v>517</v>
       </c>
       <c r="F400" s="8" t="s">
         <v>55</v>
@@ -16277,7 +16277,7 @@
         <v>1651</v>
       </c>
       <c r="E401" s="7">
-        <v>358</v>
+        <v>375</v>
       </c>
       <c r="F401" s="8" t="s">
         <v>55</v>
@@ -16300,7 +16300,7 @@
         <v>1655</v>
       </c>
       <c r="E402" s="7">
-        <v>331</v>
+        <v>140</v>
       </c>
       <c r="F402" s="8" t="s">
         <v>55</v>
@@ -16323,7 +16323,7 @@
         <v>1659</v>
       </c>
       <c r="E403" s="7">
-        <v>144</v>
+        <v>218</v>
       </c>
       <c r="F403" s="8" t="s">
         <v>55</v>
@@ -16346,7 +16346,7 @@
         <v>1663</v>
       </c>
       <c r="E404" s="7">
-        <v>338</v>
+        <v>263</v>
       </c>
       <c r="F404" s="8" t="s">
         <v>55</v>
@@ -16369,7 +16369,7 @@
         <v>1667</v>
       </c>
       <c r="E405" s="7">
-        <v>286</v>
+        <v>254</v>
       </c>
       <c r="F405" s="8" t="s">
         <v>55</v>
@@ -16392,7 +16392,7 @@
         <v>1671</v>
       </c>
       <c r="E406" s="7">
-        <v>305</v>
+        <v>315</v>
       </c>
       <c r="F406" s="8" t="s">
         <v>55</v>
@@ -16415,7 +16415,7 @@
         <v>1675</v>
       </c>
       <c r="E407" s="7">
-        <v>164</v>
+        <v>102</v>
       </c>
       <c r="F407" s="8" t="s">
         <v>55</v>
@@ -16438,7 +16438,7 @@
         <v>1679</v>
       </c>
       <c r="E408" s="7">
-        <v>151</v>
+        <v>327</v>
       </c>
       <c r="F408" s="8" t="s">
         <v>55</v>
@@ -16461,7 +16461,7 @@
         <v>1683</v>
       </c>
       <c r="E409" s="7">
-        <v>157</v>
+        <v>114</v>
       </c>
       <c r="F409" s="8" t="s">
         <v>55</v>
@@ -16484,7 +16484,7 @@
         <v>1687</v>
       </c>
       <c r="E410" s="7">
-        <v>167</v>
+        <v>190</v>
       </c>
       <c r="F410" s="8" t="s">
         <v>55</v>
@@ -16507,7 +16507,7 @@
         <v>1691</v>
       </c>
       <c r="E411" s="7">
-        <v>120</v>
+        <v>270</v>
       </c>
       <c r="F411" s="8" t="s">
         <v>55</v>
@@ -16530,7 +16530,7 @@
         <v>1695</v>
       </c>
       <c r="E412" s="7">
-        <v>250</v>
+        <v>223</v>
       </c>
       <c r="F412" s="8" t="s">
         <v>55</v>
@@ -16553,7 +16553,7 @@
         <v>1699</v>
       </c>
       <c r="E413" s="7">
-        <v>300</v>
+        <v>177</v>
       </c>
       <c r="F413" s="8" t="s">
         <v>55</v>
@@ -16576,7 +16576,7 @@
         <v>1703</v>
       </c>
       <c r="E414" s="7">
-        <v>136</v>
+        <v>133</v>
       </c>
       <c r="F414" s="8" t="s">
         <v>55</v>
@@ -16599,7 +16599,7 @@
         <v>1707</v>
       </c>
       <c r="E415" s="7">
-        <v>103</v>
+        <v>336</v>
       </c>
       <c r="F415" s="8" t="s">
         <v>55</v>
@@ -16622,7 +16622,7 @@
         <v>1711</v>
       </c>
       <c r="E416" s="7">
-        <v>169</v>
+        <v>331</v>
       </c>
       <c r="F416" s="8" t="s">
         <v>55</v>
@@ -16645,7 +16645,7 @@
         <v>1715</v>
       </c>
       <c r="E417" s="7">
-        <v>211</v>
+        <v>140</v>
       </c>
       <c r="F417" s="8" t="s">
         <v>55</v>
@@ -16668,7 +16668,7 @@
         <v>1719</v>
       </c>
       <c r="E418" s="7">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="F418" s="8" t="s">
         <v>55</v>
@@ -16691,7 +16691,7 @@
         <v>1723</v>
       </c>
       <c r="E419" s="7">
-        <v>196</v>
+        <v>92</v>
       </c>
       <c r="F419" s="8" t="s">
         <v>55</v>
@@ -16714,7 +16714,7 @@
         <v>1727</v>
       </c>
       <c r="E420" s="7">
-        <v>303</v>
+        <v>336</v>
       </c>
       <c r="F420" s="8" t="s">
         <v>55</v>
@@ -16737,7 +16737,7 @@
         <v>1731</v>
       </c>
       <c r="E421" s="7">
-        <v>171</v>
+        <v>198</v>
       </c>
       <c r="F421" s="8" t="s">
         <v>55</v>
@@ -16760,7 +16760,7 @@
         <v>1735</v>
       </c>
       <c r="E422" s="7">
-        <v>369</v>
+        <v>124</v>
       </c>
       <c r="F422" s="8" t="s">
         <v>55</v>
@@ -16783,7 +16783,7 @@
         <v>1739</v>
       </c>
       <c r="E423" s="7">
-        <v>146</v>
+        <v>208</v>
       </c>
       <c r="F423" s="8" t="s">
         <v>55</v>
@@ -16806,7 +16806,7 @@
         <v>1743</v>
       </c>
       <c r="E424" s="7">
-        <v>227</v>
+        <v>97</v>
       </c>
       <c r="F424" s="8" t="s">
         <v>55</v>
@@ -16829,7 +16829,7 @@
         <v>1747</v>
       </c>
       <c r="E425" s="7">
-        <v>294</v>
+        <v>136</v>
       </c>
       <c r="F425" s="8" t="s">
         <v>55</v>
@@ -16852,7 +16852,7 @@
         <v>1751</v>
       </c>
       <c r="E426" s="7">
-        <v>353</v>
+        <v>208</v>
       </c>
       <c r="F426" s="8" t="s">
         <v>55</v>
@@ -16875,7 +16875,7 @@
         <v>1755</v>
       </c>
       <c r="E427" s="7">
-        <v>259</v>
+        <v>149</v>
       </c>
       <c r="F427" s="8" t="s">
         <v>55</v>
@@ -16898,7 +16898,7 @@
         <v>1759</v>
       </c>
       <c r="E428" s="7">
-        <v>141</v>
+        <v>290</v>
       </c>
       <c r="F428" s="8" t="s">
         <v>55</v>
@@ -16921,7 +16921,7 @@
         <v>1763</v>
       </c>
       <c r="E429" s="7">
-        <v>300</v>
+        <v>314</v>
       </c>
       <c r="F429" s="8" t="s">
         <v>55</v>
@@ -16944,7 +16944,7 @@
         <v>1767</v>
       </c>
       <c r="E430" s="7">
-        <v>162</v>
+        <v>134</v>
       </c>
       <c r="F430" s="8" t="s">
         <v>55</v>
@@ -16967,7 +16967,7 @@
         <v>1771</v>
       </c>
       <c r="E431" s="7">
-        <v>145</v>
+        <v>241</v>
       </c>
       <c r="F431" s="8" t="s">
         <v>55</v>
@@ -16990,7 +16990,7 @@
         <v>1775</v>
       </c>
       <c r="E432" s="7">
-        <v>165</v>
+        <v>340</v>
       </c>
       <c r="F432" s="8" t="s">
         <v>55</v>
@@ -17013,7 +17013,7 @@
         <v>1779</v>
       </c>
       <c r="E433" s="7">
-        <v>302</v>
+        <v>160</v>
       </c>
       <c r="F433" s="8" t="s">
         <v>55</v>
@@ -17036,7 +17036,7 @@
         <v>1783</v>
       </c>
       <c r="E434" s="7">
-        <v>301</v>
+        <v>247</v>
       </c>
       <c r="F434" s="8" t="s">
         <v>55</v>
@@ -17059,7 +17059,7 @@
         <v>1787</v>
       </c>
       <c r="E435" s="7">
-        <v>309</v>
+        <v>150</v>
       </c>
       <c r="F435" s="8" t="s">
         <v>55</v>
@@ -17082,7 +17082,7 @@
         <v>1791</v>
       </c>
       <c r="E436" s="7">
-        <v>138</v>
+        <v>123</v>
       </c>
       <c r="F436" s="8" t="s">
         <v>55</v>
@@ -17105,7 +17105,7 @@
         <v>1795</v>
       </c>
       <c r="E437" s="7">
-        <v>90</v>
+        <v>293</v>
       </c>
       <c r="F437" s="8" t="s">
         <v>55</v>
@@ -17128,7 +17128,7 @@
         <v>1799</v>
       </c>
       <c r="E438" s="7">
-        <v>294</v>
+        <v>156</v>
       </c>
       <c r="F438" s="8" t="s">
         <v>55</v>
@@ -17151,7 +17151,7 @@
         <v>1803</v>
       </c>
       <c r="E439" s="7">
-        <v>222</v>
+        <v>179</v>
       </c>
       <c r="F439" s="8" t="s">
         <v>55</v>
@@ -17174,7 +17174,7 @@
         <v>1807</v>
       </c>
       <c r="E440" s="7">
-        <v>114</v>
+        <v>100</v>
       </c>
       <c r="F440" s="8" t="s">
         <v>55</v>
@@ -17197,7 +17197,7 @@
         <v>1811</v>
       </c>
       <c r="E441" s="7">
-        <v>113</v>
+        <v>235</v>
       </c>
       <c r="F441" s="8" t="s">
         <v>55</v>
@@ -17220,7 +17220,7 @@
         <v>1815</v>
       </c>
       <c r="E442" s="7">
-        <v>248</v>
+        <v>240</v>
       </c>
       <c r="F442" s="8" t="s">
         <v>55</v>
@@ -17243,7 +17243,7 @@
         <v>1819</v>
       </c>
       <c r="E443" s="7">
-        <v>147</v>
+        <v>135</v>
       </c>
       <c r="F443" s="8" t="s">
         <v>55</v>
@@ -17266,7 +17266,7 @@
         <v>1823</v>
       </c>
       <c r="E444" s="7">
-        <v>182</v>
+        <v>148</v>
       </c>
       <c r="F444" s="8" t="s">
         <v>55</v>
@@ -17289,7 +17289,7 @@
         <v>1827</v>
       </c>
       <c r="E445" s="7">
-        <v>283</v>
+        <v>136</v>
       </c>
       <c r="F445" s="8" t="s">
         <v>55</v>
@@ -17312,7 +17312,7 @@
         <v>1831</v>
       </c>
       <c r="E446" s="7">
-        <v>286</v>
+        <v>97</v>
       </c>
       <c r="F446" s="8" t="s">
         <v>55</v>
@@ -17335,7 +17335,7 @@
         <v>1835</v>
       </c>
       <c r="E447" s="7">
-        <v>230</v>
+        <v>140</v>
       </c>
       <c r="F447" s="8" t="s">
         <v>55</v>
@@ -17358,7 +17358,7 @@
         <v>1839</v>
       </c>
       <c r="E448" s="7">
-        <v>161</v>
+        <v>174</v>
       </c>
       <c r="F448" s="8" t="s">
         <v>55</v>
@@ -17381,7 +17381,7 @@
         <v>1843</v>
       </c>
       <c r="E449" s="7">
-        <v>297</v>
+        <v>355</v>
       </c>
       <c r="F449" s="8" t="s">
         <v>55</v>
@@ -17404,7 +17404,7 @@
         <v>1847</v>
       </c>
       <c r="E450" s="7">
-        <v>233</v>
+        <v>291</v>
       </c>
       <c r="F450" s="8" t="s">
         <v>55</v>
@@ -17427,7 +17427,7 @@
         <v>1851</v>
       </c>
       <c r="E451" s="7">
-        <v>242</v>
+        <v>348</v>
       </c>
       <c r="F451" s="8" t="s">
         <v>55</v>
@@ -17450,7 +17450,7 @@
         <v>1855</v>
       </c>
       <c r="E452" s="7">
-        <v>407</v>
+        <v>132</v>
       </c>
       <c r="F452" s="8" t="s">
         <v>55</v>
@@ -17473,7 +17473,7 @@
         <v>1859</v>
       </c>
       <c r="E453" s="7">
-        <v>137</v>
+        <v>451</v>
       </c>
       <c r="F453" s="8" t="s">
         <v>55</v>
@@ -17496,7 +17496,7 @@
         <v>1863</v>
       </c>
       <c r="E454" s="7">
-        <v>253</v>
+        <v>229</v>
       </c>
       <c r="F454" s="8" t="s">
         <v>55</v>
@@ -17519,7 +17519,7 @@
         <v>1867</v>
       </c>
       <c r="E455" s="7">
-        <v>486</v>
+        <v>456</v>
       </c>
       <c r="F455" s="8" t="s">
         <v>55</v>
@@ -17542,7 +17542,7 @@
         <v>1871</v>
       </c>
       <c r="E456" s="7">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="F456" s="8" t="s">
         <v>55</v>
@@ -17565,7 +17565,7 @@
         <v>1875</v>
       </c>
       <c r="E457" s="7">
-        <v>363</v>
+        <v>458</v>
       </c>
       <c r="F457" s="8" t="s">
         <v>55</v>
@@ -17588,7 +17588,7 @@
         <v>1879</v>
       </c>
       <c r="E458" s="7">
-        <v>389</v>
+        <v>219</v>
       </c>
       <c r="F458" s="8" t="s">
         <v>55</v>
@@ -17611,7 +17611,7 @@
         <v>1883</v>
       </c>
       <c r="E459" s="7">
-        <v>354</v>
+        <v>159</v>
       </c>
       <c r="F459" s="8" t="s">
         <v>55</v>
@@ -17634,7 +17634,7 @@
         <v>1887</v>
       </c>
       <c r="E460" s="7">
-        <v>285</v>
+        <v>459</v>
       </c>
       <c r="F460" s="8" t="s">
         <v>55</v>
@@ -17657,7 +17657,7 @@
         <v>1891</v>
       </c>
       <c r="E461" s="7">
-        <v>372</v>
+        <v>145</v>
       </c>
       <c r="F461" s="8" t="s">
         <v>55</v>
@@ -17680,7 +17680,7 @@
         <v>1895</v>
       </c>
       <c r="E462" s="7">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="F462" s="8" t="s">
         <v>55</v>
@@ -17703,7 +17703,7 @@
         <v>1899</v>
       </c>
       <c r="E463" s="7">
-        <v>225</v>
+        <v>258</v>
       </c>
       <c r="F463" s="8" t="s">
         <v>55</v>
@@ -17726,7 +17726,7 @@
         <v>1903</v>
       </c>
       <c r="E464" s="7">
-        <v>241</v>
+        <v>203</v>
       </c>
       <c r="F464" s="8" t="s">
         <v>55</v>
@@ -17749,7 +17749,7 @@
         <v>1907</v>
       </c>
       <c r="E465" s="7">
-        <v>317</v>
+        <v>481</v>
       </c>
       <c r="F465" s="8" t="s">
         <v>55</v>
@@ -17772,7 +17772,7 @@
         <v>1911</v>
       </c>
       <c r="E466" s="7">
-        <v>432</v>
+        <v>315</v>
       </c>
       <c r="F466" s="8" t="s">
         <v>55</v>
@@ -17795,7 +17795,7 @@
         <v>1915</v>
       </c>
       <c r="E467" s="7">
-        <v>295</v>
+        <v>492</v>
       </c>
       <c r="F467" s="8" t="s">
         <v>55</v>
@@ -17818,7 +17818,7 @@
         <v>1919</v>
       </c>
       <c r="E468" s="7">
-        <v>267</v>
+        <v>340</v>
       </c>
       <c r="F468" s="8" t="s">
         <v>55</v>
@@ -17841,7 +17841,7 @@
         <v>1923</v>
       </c>
       <c r="E469" s="7">
-        <v>212</v>
+        <v>197</v>
       </c>
       <c r="F469" s="8" t="s">
         <v>55</v>
@@ -17864,7 +17864,7 @@
         <v>1927</v>
       </c>
       <c r="E470" s="7">
-        <v>378</v>
+        <v>469</v>
       </c>
       <c r="F470" s="8" t="s">
         <v>55</v>
@@ -17887,7 +17887,7 @@
         <v>1931</v>
       </c>
       <c r="E471" s="7">
-        <v>465</v>
+        <v>448</v>
       </c>
       <c r="F471" s="8" t="s">
         <v>55</v>
@@ -17910,7 +17910,7 @@
         <v>1935</v>
       </c>
       <c r="E472" s="7">
-        <v>440</v>
+        <v>170</v>
       </c>
       <c r="F472" s="8" t="s">
         <v>55</v>
@@ -17933,7 +17933,7 @@
         <v>1939</v>
       </c>
       <c r="E473" s="7">
-        <v>332</v>
+        <v>136</v>
       </c>
       <c r="F473" s="8" t="s">
         <v>55</v>
@@ -17956,7 +17956,7 @@
         <v>1943</v>
       </c>
       <c r="E474" s="7">
-        <v>462</v>
+        <v>489</v>
       </c>
       <c r="F474" s="8" t="s">
         <v>55</v>
@@ -17979,7 +17979,7 @@
         <v>1947</v>
       </c>
       <c r="E475" s="7">
-        <v>140</v>
+        <v>366</v>
       </c>
       <c r="F475" s="8" t="s">
         <v>55</v>
@@ -18002,7 +18002,7 @@
         <v>1951</v>
       </c>
       <c r="E476" s="7">
-        <v>257</v>
+        <v>213</v>
       </c>
       <c r="F476" s="8" t="s">
         <v>55</v>
@@ -18025,7 +18025,7 @@
         <v>1955</v>
       </c>
       <c r="E477" s="7">
-        <v>296</v>
+        <v>421</v>
       </c>
       <c r="F477" s="8" t="s">
         <v>55</v>
@@ -18048,7 +18048,7 @@
         <v>1959</v>
       </c>
       <c r="E478" s="7">
-        <v>428</v>
+        <v>404</v>
       </c>
       <c r="F478" s="8" t="s">
         <v>55</v>
@@ -18071,7 +18071,7 @@
         <v>1963</v>
       </c>
       <c r="E479" s="7">
-        <v>419</v>
+        <v>275</v>
       </c>
       <c r="F479" s="8" t="s">
         <v>55</v>
@@ -18094,7 +18094,7 @@
         <v>1967</v>
       </c>
       <c r="E480" s="7">
-        <v>143</v>
+        <v>247</v>
       </c>
       <c r="F480" s="8" t="s">
         <v>55</v>
@@ -18117,7 +18117,7 @@
         <v>1971</v>
       </c>
       <c r="E481" s="7">
-        <v>447</v>
+        <v>449</v>
       </c>
       <c r="F481" s="8" t="s">
         <v>55</v>
@@ -18140,7 +18140,7 @@
         <v>1975</v>
       </c>
       <c r="E482" s="7">
-        <v>165</v>
+        <v>470</v>
       </c>
       <c r="F482" s="8" t="s">
         <v>55</v>
@@ -18163,7 +18163,7 @@
         <v>1979</v>
       </c>
       <c r="E483" s="7">
-        <v>390</v>
+        <v>482</v>
       </c>
       <c r="F483" s="8" t="s">
         <v>55</v>
@@ -18186,7 +18186,7 @@
         <v>1983</v>
       </c>
       <c r="E484" s="7">
-        <v>309</v>
+        <v>449</v>
       </c>
       <c r="F484" s="8" t="s">
         <v>55</v>
@@ -18209,7 +18209,7 @@
         <v>1987</v>
       </c>
       <c r="E485" s="7">
-        <v>346</v>
+        <v>235</v>
       </c>
       <c r="F485" s="8" t="s">
         <v>55</v>
@@ -18232,7 +18232,7 @@
         <v>1991</v>
       </c>
       <c r="E486" s="7">
-        <v>446</v>
+        <v>459</v>
       </c>
       <c r="F486" s="8" t="s">
         <v>55</v>
@@ -18255,7 +18255,7 @@
         <v>1995</v>
       </c>
       <c r="E487" s="7">
-        <v>393</v>
+        <v>458</v>
       </c>
       <c r="F487" s="8" t="s">
         <v>55</v>
@@ -18278,7 +18278,7 @@
         <v>1999</v>
       </c>
       <c r="E488" s="7">
-        <v>285</v>
+        <v>186</v>
       </c>
       <c r="F488" s="8" t="s">
         <v>55</v>
@@ -18301,7 +18301,7 @@
         <v>2003</v>
       </c>
       <c r="E489" s="7">
-        <v>495</v>
+        <v>430</v>
       </c>
       <c r="F489" s="8" t="s">
         <v>55</v>
@@ -18324,7 +18324,7 @@
         <v>2007</v>
       </c>
       <c r="E490" s="7">
-        <v>485</v>
+        <v>377</v>
       </c>
       <c r="F490" s="8" t="s">
         <v>55</v>
@@ -18347,7 +18347,7 @@
         <v>2011</v>
       </c>
       <c r="E491" s="7">
-        <v>428</v>
+        <v>410</v>
       </c>
       <c r="F491" s="8" t="s">
         <v>55</v>
@@ -18370,7 +18370,7 @@
         <v>2015</v>
       </c>
       <c r="E492" s="7">
-        <v>424</v>
+        <v>321</v>
       </c>
       <c r="F492" s="8" t="s">
         <v>55</v>
@@ -18393,7 +18393,7 @@
         <v>2019</v>
       </c>
       <c r="E493" s="7">
-        <v>432</v>
+        <v>390</v>
       </c>
       <c r="F493" s="8" t="s">
         <v>55</v>
@@ -18416,7 +18416,7 @@
         <v>2023</v>
       </c>
       <c r="E494" s="7">
-        <v>334</v>
+        <v>316</v>
       </c>
       <c r="F494" s="8" t="s">
         <v>55</v>
@@ -18439,7 +18439,7 @@
         <v>2027</v>
       </c>
       <c r="E495" s="7">
-        <v>229</v>
+        <v>265</v>
       </c>
       <c r="F495" s="8" t="s">
         <v>55</v>
@@ -18462,7 +18462,7 @@
         <v>2031</v>
       </c>
       <c r="E496" s="7">
-        <v>357</v>
+        <v>498</v>
       </c>
       <c r="F496" s="8" t="s">
         <v>55</v>
@@ -18485,7 +18485,7 @@
         <v>2035</v>
       </c>
       <c r="E497" s="7">
-        <v>374</v>
+        <v>434</v>
       </c>
       <c r="F497" s="8" t="s">
         <v>55</v>
@@ -18508,7 +18508,7 @@
         <v>2039</v>
       </c>
       <c r="E498" s="7">
-        <v>399</v>
+        <v>137</v>
       </c>
       <c r="F498" s="8" t="s">
         <v>55</v>
@@ -18531,7 +18531,7 @@
         <v>2043</v>
       </c>
       <c r="E499" s="7">
-        <v>224</v>
+        <v>282</v>
       </c>
       <c r="F499" s="8" t="s">
         <v>55</v>
@@ -18554,7 +18554,7 @@
         <v>2047</v>
       </c>
       <c r="E500" s="7">
-        <v>172</v>
+        <v>371</v>
       </c>
       <c r="F500" s="8" t="s">
         <v>55</v>
@@ -18577,7 +18577,7 @@
         <v>2051</v>
       </c>
       <c r="E501" s="7">
-        <v>278</v>
+        <v>344</v>
       </c>
       <c r="F501" s="8" t="s">
         <v>55</v>
